--- a/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -3,15 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{B9455642-526F-4A08-9641-0084BA48857A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6EC84D-03DB-4168-8E19-623E98E75CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="140">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -259,12 +258,6 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699009</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>895 Retail Team 1 (Sepap Pusube (10573442) (Inherited))</t>
   </si>
   <si>
@@ -410,9 +403,6 @@
   </si>
   <si>
     <t>Test2</t>
-  </si>
-  <si>
-    <t>10699010</t>
   </si>
   <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
@@ -936,92 +926,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CN17"/>
-  <sheetFormatPr defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1796875" style="1" customWidth="1"/>
     <col min="11" max="11" width="15" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.453125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.90625" style="1" customWidth="1"/>
     <col min="14" max="14" width="16" style="1" customWidth="1"/>
     <col min="15" max="15" width="20" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.21875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="6.21875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.21875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="12.109375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="15.6640625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.21875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.109375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.5546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="22.21875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="16.5546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.6328125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.1796875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.36328125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.1796875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="12.08984375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15.6328125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.1796875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.08984375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="8.54296875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22.1796875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="16.54296875" style="1" customWidth="1"/>
     <col min="28" max="28" width="37" style="1" customWidth="1"/>
-    <col min="29" max="29" width="11.5546875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="21.44140625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="14.6640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="11.88671875" style="1" customWidth="1"/>
-    <col min="33" max="33" width="26.21875" style="1" customWidth="1"/>
-    <col min="34" max="34" width="23.21875" style="1" customWidth="1"/>
-    <col min="35" max="35" width="23.33203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="7.21875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="18.77734375" style="1" customWidth="1"/>
-    <col min="38" max="38" width="23.33203125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="23.109375" style="1" customWidth="1"/>
-    <col min="40" max="40" width="18.33203125" style="1" customWidth="1"/>
-    <col min="41" max="41" width="23.5546875" style="1" customWidth="1"/>
-    <col min="42" max="42" width="20.6640625" style="1" customWidth="1"/>
-    <col min="43" max="43" width="20.109375" style="1" customWidth="1"/>
-    <col min="44" max="44" width="10.6640625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="11.54296875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="21.453125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="14.6328125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="11.90625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="26.1796875" style="1" customWidth="1"/>
+    <col min="34" max="34" width="23.1796875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="23.36328125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="7.1796875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.81640625" style="1" customWidth="1"/>
+    <col min="38" max="38" width="23.36328125" style="1" customWidth="1"/>
+    <col min="39" max="39" width="23.08984375" style="1" customWidth="1"/>
+    <col min="40" max="40" width="18.36328125" style="1" customWidth="1"/>
+    <col min="41" max="41" width="23.54296875" style="1" customWidth="1"/>
+    <col min="42" max="42" width="20.6328125" style="1" customWidth="1"/>
+    <col min="43" max="43" width="20.08984375" style="1" customWidth="1"/>
+    <col min="44" max="44" width="10.6328125" style="1" customWidth="1"/>
     <col min="45" max="45" width="19" style="1" customWidth="1"/>
-    <col min="46" max="46" width="15.77734375" style="1" customWidth="1"/>
-    <col min="47" max="47" width="13.6640625" style="1" customWidth="1"/>
-    <col min="48" max="48" width="17.77734375" style="1" customWidth="1"/>
-    <col min="49" max="49" width="10.6640625" style="1" customWidth="1"/>
+    <col min="46" max="46" width="15.81640625" style="1" customWidth="1"/>
+    <col min="47" max="47" width="13.6328125" style="1" customWidth="1"/>
+    <col min="48" max="48" width="17.81640625" style="1" customWidth="1"/>
+    <col min="49" max="49" width="10.6328125" style="1" customWidth="1"/>
     <col min="50" max="50" width="19" style="1" customWidth="1"/>
-    <col min="51" max="51" width="14.33203125" style="1" customWidth="1"/>
-    <col min="52" max="52" width="13.6640625" style="1" customWidth="1"/>
-    <col min="53" max="53" width="17.77734375" style="1" customWidth="1"/>
-    <col min="54" max="54" width="8.5546875" style="1" customWidth="1"/>
-    <col min="55" max="55" width="13.6640625" style="1" customWidth="1"/>
-    <col min="56" max="56" width="12.5546875" style="1" customWidth="1"/>
-    <col min="57" max="57" width="14.5546875" style="1" customWidth="1"/>
-    <col min="58" max="58" width="18.88671875" style="1" customWidth="1"/>
-    <col min="59" max="59" width="12.33203125" style="1" customWidth="1"/>
+    <col min="51" max="51" width="14.36328125" style="1" customWidth="1"/>
+    <col min="52" max="52" width="13.6328125" style="1" customWidth="1"/>
+    <col min="53" max="53" width="17.81640625" style="1" customWidth="1"/>
+    <col min="54" max="54" width="8.54296875" style="1" customWidth="1"/>
+    <col min="55" max="55" width="13.6328125" style="1" customWidth="1"/>
+    <col min="56" max="56" width="12.54296875" style="1" customWidth="1"/>
+    <col min="57" max="57" width="14.54296875" style="1" customWidth="1"/>
+    <col min="58" max="58" width="18.90625" style="1" customWidth="1"/>
+    <col min="59" max="59" width="12.36328125" style="1" customWidth="1"/>
     <col min="60" max="60" width="15" style="1" customWidth="1"/>
     <col min="61" max="61" width="26" style="1" customWidth="1"/>
-    <col min="62" max="62" width="25.77734375" style="1" customWidth="1"/>
-    <col min="63" max="63" width="9.44140625" style="1" customWidth="1"/>
-    <col min="64" max="64" width="8.21875" style="1" customWidth="1"/>
-    <col min="65" max="65" width="8.33203125" style="1" customWidth="1"/>
-    <col min="66" max="66" width="17.88671875" style="1" customWidth="1"/>
-    <col min="67" max="67" width="22.88671875" style="1" customWidth="1"/>
-    <col min="68" max="68" width="15.109375" style="1" customWidth="1"/>
-    <col min="69" max="69" width="20.109375" style="1" customWidth="1"/>
-    <col min="70" max="70" width="19.6640625" style="1" customWidth="1"/>
-    <col min="71" max="71" width="29.88671875" style="1" customWidth="1"/>
-    <col min="72" max="72" width="23.44140625" style="1" customWidth="1"/>
-    <col min="73" max="73" width="26.77734375" style="1" customWidth="1"/>
-    <col min="74" max="74" width="30.6640625" style="1" customWidth="1"/>
-    <col min="75" max="75" width="31.5546875" style="1" customWidth="1"/>
-    <col min="76" max="76" width="28.109375" style="1" customWidth="1"/>
+    <col min="62" max="62" width="25.81640625" style="1" customWidth="1"/>
+    <col min="63" max="63" width="9.453125" style="1" customWidth="1"/>
+    <col min="64" max="64" width="8.1796875" style="1" customWidth="1"/>
+    <col min="65" max="65" width="8.36328125" style="1" customWidth="1"/>
+    <col min="66" max="66" width="17.90625" style="1" customWidth="1"/>
+    <col min="67" max="67" width="22.90625" style="1" customWidth="1"/>
+    <col min="68" max="68" width="15.08984375" style="1" customWidth="1"/>
+    <col min="69" max="69" width="20.08984375" style="1" customWidth="1"/>
+    <col min="70" max="70" width="19.6328125" style="1" customWidth="1"/>
+    <col min="71" max="71" width="29.90625" style="1" customWidth="1"/>
+    <col min="72" max="72" width="23.453125" style="1" customWidth="1"/>
+    <col min="73" max="73" width="26.81640625" style="1" customWidth="1"/>
+    <col min="74" max="74" width="30.6328125" style="1" customWidth="1"/>
+    <col min="75" max="75" width="31.54296875" style="1" customWidth="1"/>
+    <col min="76" max="76" width="28.08984375" style="1" customWidth="1"/>
     <col min="77" max="77" width="15" style="1" customWidth="1"/>
-    <col min="78" max="78" width="33.6640625" style="1" customWidth="1"/>
-    <col min="79" max="79" width="26.88671875" style="1" customWidth="1"/>
-    <col min="80" max="80" width="8.88671875" style="1" customWidth="1"/>
-    <col min="81" max="16384" width="8.88671875" style="1"/>
+    <col min="78" max="78" width="33.6328125" style="1" customWidth="1"/>
+    <col min="79" max="79" width="26.90625" style="1" customWidth="1"/>
+    <col min="80" max="80" width="8.90625" style="1" customWidth="1"/>
+    <col min="81" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1273,45 +1263,41 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="H2" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="J2" s="12" t="s">
         <v>82</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="K2" s="13">
         <v>45597</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N2" s="11">
         <v>1</v>
@@ -1320,68 +1306,68 @@
         <v>213111231</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="S2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="T2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="S2" s="12" t="s">
+      <c r="V2" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="T2" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="W2" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="X2" s="13">
         <f t="shared" ref="X2:X3" si="0">K2</f>
         <v>45597</v>
       </c>
       <c r="Y2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA2" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="AB2" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AC2" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AD2" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AE2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AF2" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>98</v>
       </c>
       <c r="AG2" s="16">
         <v>20</v>
       </c>
       <c r="AH2" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI2" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="AI2" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ2" s="12" t="s">
-        <v>101</v>
       </c>
       <c r="AK2" s="13" t="str">
         <f t="shared" ref="AK2:AK3" si="1">AH2</f>
@@ -1396,10 +1382,10 @@
         <v>45597</v>
       </c>
       <c r="AN2" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AO2" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AP2" s="11">
         <v>100</v>
@@ -1409,79 +1395,79 @@
         <v>45687</v>
       </c>
       <c r="AR2" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AS2" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT2" s="18">
+        <v>9461110759</v>
+      </c>
+      <c r="AU2" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV2" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="18">
-        <v>9361110759</v>
-      </c>
-      <c r="AU2" s="13" t="s">
+      <c r="AW2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX2" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="AV2" s="13" t="s">
+      <c r="AY2" s="19">
+        <v>142743023</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB2" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="AW2" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX2" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY2" s="19">
-        <v>141743023</v>
-      </c>
-      <c r="AZ2" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="BA2" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="BB2" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="BC2" s="13">
         <v>34284</v>
       </c>
       <c r="BD2" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="BE2" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF2" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG2" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="17" t="s">
+      <c r="BH2" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="BG2" s="11" t="s">
+      <c r="BI2" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="11" t="s">
+      <c r="BJ2" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="BI2" s="8" t="s">
+      <c r="BK2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="BL2" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="BJ2" s="17" t="s">
+      <c r="BM2" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="BK2" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BL2" s="14" t="s">
+      <c r="BN2" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="BM2" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="BN2" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="BO2" s="14">
         <v>2024</v>
       </c>
       <c r="BP2" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BQ2" s="14">
         <v>2021</v>
@@ -1490,72 +1476,68 @@
         <v>2024</v>
       </c>
       <c r="BS2" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="BT2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="BV2" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="14" t="s">
+      <c r="BW2" s="20" t="s">
         <v>120</v>
-      </c>
-      <c r="BU2" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BV2" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW2" s="20" t="s">
-        <v>122</v>
       </c>
       <c r="BX2" s="20">
         <v>213</v>
       </c>
       <c r="BY2" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="BZ2" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="CA2" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="BZ2" s="20" t="s">
+    </row>
+    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="CA2" s="20" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="10" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="E3" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="G3" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="H3" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>131</v>
-      </c>
       <c r="I3" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K3" s="13">
         <v>45597</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N3" s="11">
         <v>1</v>
@@ -1564,68 +1546,68 @@
         <v>213111231</v>
       </c>
       <c r="P3" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="S3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="T3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="U3" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="R3" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="S3" s="12" t="s">
+      <c r="V3" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="T3" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="U3" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="W3" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="X3" s="13">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z3" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA3" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="Z3" s="12" t="s">
+      <c r="AB3" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD3" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF3" s="8" t="s">
         <v>132</v>
-      </c>
-      <c r="AA3" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE3" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF3" s="8" t="s">
-        <v>135</v>
       </c>
       <c r="AG3" s="16">
         <v>40</v>
       </c>
       <c r="AH3" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI3" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ3" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="AI3" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ3" s="12" t="s">
-        <v>101</v>
       </c>
       <c r="AK3" s="13" t="str">
         <f t="shared" si="1"/>
@@ -1640,10 +1622,10 @@
         <v>45597</v>
       </c>
       <c r="AN3" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AO3" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AP3" s="11">
         <v>100</v>
@@ -1653,79 +1635,79 @@
         <v>45687</v>
       </c>
       <c r="AR3" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AS3" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT3" s="18">
+        <v>9461115170</v>
+      </c>
+      <c r="AU3" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV3" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="AT3" s="18">
-        <v>9361115170</v>
-      </c>
-      <c r="AU3" s="13" t="s">
+      <c r="AW3" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX3" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="AV3" s="13" t="s">
+      <c r="AY3" s="19">
+        <v>142733024</v>
+      </c>
+      <c r="AZ3" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA3" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB3" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="AW3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX3" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY3" s="19">
-        <v>141733024</v>
-      </c>
-      <c r="AZ3" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="BA3" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="BB3" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="BC3" s="13">
         <v>34284</v>
       </c>
       <c r="BD3" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="BE3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG3" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="BF3" s="17" t="s">
+      <c r="BH3" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="BG3" s="11" t="s">
+      <c r="BI3" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="BH3" s="11" t="s">
+      <c r="BJ3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="BI3" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="BJ3" s="17" t="s">
-        <v>114</v>
-      </c>
       <c r="BK3" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BL3" s="14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BM3" s="14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BN3" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="BO3" s="14">
         <v>2000</v>
       </c>
       <c r="BP3" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BQ3" s="14">
         <v>1995</v>
@@ -1734,34 +1716,34 @@
         <v>2000</v>
       </c>
       <c r="BS3" s="14" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="BT3" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="BU3" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BV3" s="20" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="BW3" s="20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="BX3" s="20">
         <v>201</v>
       </c>
       <c r="BY3" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="BZ3" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="CA3" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="BZ3" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA3" s="20" t="s">
-        <v>125</v>
-      </c>
     </row>
-    <row r="4" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1842,7 +1824,7 @@
       <c r="BZ4" s="20"/>
       <c r="CA4" s="20"/>
     </row>
-    <row r="5" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1923,7 +1905,7 @@
       <c r="BZ5" s="20"/>
       <c r="CA5" s="20"/>
     </row>
-    <row r="6" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2004,7 +1986,7 @@
       <c r="BZ6" s="20"/>
       <c r="CA6" s="20"/>
     </row>
-    <row r="7" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8"/>
       <c r="B7" s="21"/>
       <c r="C7" s="8"/>
@@ -2085,7 +2067,7 @@
       <c r="BZ7" s="20"/>
       <c r="CA7" s="20"/>
     </row>
-    <row r="8" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="8"/>
@@ -2166,7 +2148,7 @@
       <c r="BZ8" s="20"/>
       <c r="CA8" s="20"/>
     </row>
-    <row r="9" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8"/>
       <c r="B9" s="21"/>
       <c r="C9" s="8"/>
@@ -2247,7 +2229,7 @@
       <c r="BZ9" s="20"/>
       <c r="CA9" s="20"/>
     </row>
-    <row r="10" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2328,7 +2310,7 @@
       <c r="BZ10" s="20"/>
       <c r="CA10" s="20"/>
     </row>
-    <row r="11" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2409,7 +2391,7 @@
       <c r="BZ11" s="20"/>
       <c r="CA11" s="20"/>
     </row>
-    <row r="12" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="21"/>
       <c r="C12" s="8"/>
@@ -2490,7 +2472,7 @@
       <c r="BZ12" s="20"/>
       <c r="CA12" s="20"/>
     </row>
-    <row r="13" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8"/>
       <c r="B13" s="21"/>
       <c r="C13" s="8"/>
@@ -2571,7 +2553,7 @@
       <c r="BZ13" s="20"/>
       <c r="CA13" s="20"/>
     </row>
-    <row r="14" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8"/>
       <c r="B14" s="21"/>
       <c r="C14" s="8"/>
@@ -2652,7 +2634,7 @@
       <c r="BZ14" s="20"/>
       <c r="CA14" s="20"/>
     </row>
-    <row r="15" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="8"/>
@@ -2733,7 +2715,7 @@
       <c r="BZ15" s="20"/>
       <c r="CA15" s="20"/>
     </row>
-    <row r="16" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="8"/>
@@ -2814,7 +2796,7 @@
       <c r="BZ16" s="20"/>
       <c r="CA16" s="20"/>
     </row>
-    <row r="17" spans="46:51" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="46:51" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AT17" s="19"/>
       <c r="AY17" s="19"/>
     </row>

--- a/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -1,30 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{B9455642-526F-4A08-9641-0084BA48857A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -259,7 +244,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699009</t>
+    <t>10699224</t>
   </si>
   <si>
     <t>Passed</t>
@@ -271,10 +256,10 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>Otho</t>
-  </si>
-  <si>
-    <t>Kerluke</t>
+    <t>Johathan</t>
+  </si>
+  <si>
+    <t>Crist</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -412,22 +397,22 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699010</t>
+    <t>10699225</t>
   </si>
   <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Trantow</t>
+    <t>Linnea</t>
+  </si>
+  <si>
+    <t>Rowe</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 23256195</t>
+    <t>Auto 74531265</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -463,54 +448,54 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <u/>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -522,7 +507,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,28 +552,16 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -933,95 +906,94 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CN17"/>
-  <sheetFormatPr defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="109.7265625" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1796875" style="1" customWidth="1"/>
     <col min="11" max="11" width="15" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.453125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.90625" style="1" customWidth="1"/>
     <col min="14" max="14" width="16" style="1" customWidth="1"/>
     <col min="15" max="15" width="20" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.21875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="6.21875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.21875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="12.109375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="15.6640625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.21875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.109375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.5546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="22.21875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="16.5546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.6328125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.1796875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.36328125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.1796875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="12.08984375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15.6328125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.1796875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.08984375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="8.54296875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22.1796875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="16.54296875" style="1" customWidth="1"/>
     <col min="28" max="28" width="37" style="1" customWidth="1"/>
-    <col min="29" max="29" width="11.5546875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="21.44140625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="14.6640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="11.88671875" style="1" customWidth="1"/>
-    <col min="33" max="33" width="26.21875" style="1" customWidth="1"/>
-    <col min="34" max="34" width="23.21875" style="1" customWidth="1"/>
-    <col min="35" max="35" width="23.33203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="7.21875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="18.77734375" style="1" customWidth="1"/>
-    <col min="38" max="38" width="23.33203125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="23.109375" style="1" customWidth="1"/>
-    <col min="40" max="40" width="18.33203125" style="1" customWidth="1"/>
-    <col min="41" max="41" width="23.5546875" style="1" customWidth="1"/>
-    <col min="42" max="42" width="20.6640625" style="1" customWidth="1"/>
-    <col min="43" max="43" width="20.109375" style="1" customWidth="1"/>
-    <col min="44" max="44" width="10.6640625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="11.54296875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="21.453125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="14.6328125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="11.90625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="26.1796875" style="1" customWidth="1"/>
+    <col min="34" max="34" width="23.1796875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="23.36328125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="7.1796875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.81640625" style="1" customWidth="1"/>
+    <col min="38" max="38" width="23.36328125" style="1" customWidth="1"/>
+    <col min="39" max="39" width="23.08984375" style="1" customWidth="1"/>
+    <col min="40" max="40" width="18.36328125" style="1" customWidth="1"/>
+    <col min="41" max="41" width="23.54296875" style="1" customWidth="1"/>
+    <col min="42" max="42" width="20.6328125" style="1" customWidth="1"/>
+    <col min="43" max="43" width="20.08984375" style="1" customWidth="1"/>
+    <col min="44" max="44" width="10.6328125" style="1" customWidth="1"/>
     <col min="45" max="45" width="19" style="1" customWidth="1"/>
-    <col min="46" max="46" width="15.77734375" style="1" customWidth="1"/>
-    <col min="47" max="47" width="13.6640625" style="1" customWidth="1"/>
-    <col min="48" max="48" width="17.77734375" style="1" customWidth="1"/>
-    <col min="49" max="49" width="10.6640625" style="1" customWidth="1"/>
+    <col min="46" max="46" width="15.81640625" style="1" customWidth="1"/>
+    <col min="47" max="47" width="13.6328125" style="1" customWidth="1"/>
+    <col min="48" max="48" width="17.81640625" style="1" customWidth="1"/>
+    <col min="49" max="49" width="10.6328125" style="1" customWidth="1"/>
     <col min="50" max="50" width="19" style="1" customWidth="1"/>
-    <col min="51" max="51" width="14.33203125" style="1" customWidth="1"/>
-    <col min="52" max="52" width="13.6640625" style="1" customWidth="1"/>
-    <col min="53" max="53" width="17.77734375" style="1" customWidth="1"/>
-    <col min="54" max="54" width="8.5546875" style="1" customWidth="1"/>
-    <col min="55" max="55" width="13.6640625" style="1" customWidth="1"/>
-    <col min="56" max="56" width="12.5546875" style="1" customWidth="1"/>
-    <col min="57" max="57" width="14.5546875" style="1" customWidth="1"/>
-    <col min="58" max="58" width="18.88671875" style="1" customWidth="1"/>
-    <col min="59" max="59" width="12.33203125" style="1" customWidth="1"/>
+    <col min="51" max="51" width="14.36328125" style="1" customWidth="1"/>
+    <col min="52" max="52" width="13.6328125" style="1" customWidth="1"/>
+    <col min="53" max="53" width="17.81640625" style="1" customWidth="1"/>
+    <col min="54" max="54" width="8.54296875" style="1" customWidth="1"/>
+    <col min="55" max="55" width="13.6328125" style="1" customWidth="1"/>
+    <col min="56" max="56" width="12.54296875" style="1" customWidth="1"/>
+    <col min="57" max="57" width="14.54296875" style="1" customWidth="1"/>
+    <col min="58" max="58" width="18.90625" style="1" customWidth="1"/>
+    <col min="59" max="59" width="12.36328125" style="1" customWidth="1"/>
     <col min="60" max="60" width="15" style="1" customWidth="1"/>
     <col min="61" max="61" width="26" style="1" customWidth="1"/>
-    <col min="62" max="62" width="25.77734375" style="1" customWidth="1"/>
-    <col min="63" max="63" width="9.44140625" style="1" customWidth="1"/>
-    <col min="64" max="64" width="8.21875" style="1" customWidth="1"/>
-    <col min="65" max="65" width="8.33203125" style="1" customWidth="1"/>
-    <col min="66" max="66" width="17.88671875" style="1" customWidth="1"/>
-    <col min="67" max="67" width="22.88671875" style="1" customWidth="1"/>
-    <col min="68" max="68" width="15.109375" style="1" customWidth="1"/>
-    <col min="69" max="69" width="20.109375" style="1" customWidth="1"/>
-    <col min="70" max="70" width="19.6640625" style="1" customWidth="1"/>
-    <col min="71" max="71" width="29.88671875" style="1" customWidth="1"/>
-    <col min="72" max="72" width="23.44140625" style="1" customWidth="1"/>
-    <col min="73" max="73" width="26.77734375" style="1" customWidth="1"/>
-    <col min="74" max="74" width="30.6640625" style="1" customWidth="1"/>
-    <col min="75" max="75" width="31.5546875" style="1" customWidth="1"/>
-    <col min="76" max="76" width="28.109375" style="1" customWidth="1"/>
+    <col min="62" max="62" width="25.81640625" style="1" customWidth="1"/>
+    <col min="63" max="63" width="9.453125" style="1" customWidth="1"/>
+    <col min="64" max="64" width="8.1796875" style="1" customWidth="1"/>
+    <col min="65" max="65" width="8.36328125" style="1" customWidth="1"/>
+    <col min="66" max="66" width="17.90625" style="1" customWidth="1"/>
+    <col min="67" max="67" width="22.90625" style="1" customWidth="1"/>
+    <col min="68" max="68" width="15.08984375" style="1" customWidth="1"/>
+    <col min="69" max="69" width="20.08984375" style="1" customWidth="1"/>
+    <col min="70" max="70" width="19.6328125" style="1" customWidth="1"/>
+    <col min="71" max="71" width="29.90625" style="1" customWidth="1"/>
+    <col min="72" max="72" width="23.453125" style="1" customWidth="1"/>
+    <col min="73" max="73" width="26.81640625" style="1" customWidth="1"/>
+    <col min="74" max="74" width="30.6328125" style="1" customWidth="1"/>
+    <col min="75" max="75" width="31.54296875" style="1" customWidth="1"/>
+    <col min="76" max="76" width="28.08984375" style="1" customWidth="1"/>
     <col min="77" max="77" width="15" style="1" customWidth="1"/>
-    <col min="78" max="78" width="33.6640625" style="1" customWidth="1"/>
-    <col min="79" max="79" width="26.88671875" style="1" customWidth="1"/>
-    <col min="80" max="80" width="8.88671875" style="1" customWidth="1"/>
-    <col min="81" max="16384" width="8.88671875" style="1"/>
+    <col min="78" max="78" width="33.6328125" style="1" customWidth="1"/>
+    <col min="79" max="79" width="26.90625" style="1" customWidth="1"/>
+    <col min="80" max="16384" width="8.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:92" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1273,7 +1245,7 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
@@ -1383,9 +1355,9 @@
       <c r="AJ2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AK2" s="13" t="str">
+      <c r="AK2" s="13">
         <f t="shared" ref="AK2:AK3" si="1">AH2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL2" s="13">
         <f t="shared" ref="AL2:AL3" si="2">K2</f>
@@ -1415,7 +1387,7 @@
         <v>104</v>
       </c>
       <c r="AT2" s="18">
-        <v>9361110759</v>
+        <v>9461110780</v>
       </c>
       <c r="AU2" s="13" t="s">
         <v>105</v>
@@ -1430,7 +1402,7 @@
         <v>107</v>
       </c>
       <c r="AY2" s="19">
-        <v>141743023</v>
+        <v>142743080</v>
       </c>
       <c r="AZ2" s="13" t="s">
         <v>105</v>
@@ -1517,7 +1489,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>126</v>
       </c>
@@ -1627,9 +1599,9 @@
       <c r="AJ3" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AK3" s="13" t="str">
+      <c r="AK3" s="13">
         <f t="shared" si="1"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL3" s="13">
         <f t="shared" si="2"/>
@@ -1659,7 +1631,7 @@
         <v>104</v>
       </c>
       <c r="AT3" s="18">
-        <v>9361115170</v>
+        <v>9461115182</v>
       </c>
       <c r="AU3" s="13" t="s">
         <v>105</v>
@@ -1674,7 +1646,7 @@
         <v>107</v>
       </c>
       <c r="AY3" s="19">
-        <v>141733024</v>
+        <v>142733082</v>
       </c>
       <c r="AZ3" s="13" t="s">
         <v>105</v>
@@ -1761,7 +1733,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1842,7 +1814,7 @@
       <c r="BZ4" s="20"/>
       <c r="CA4" s="20"/>
     </row>
-    <row r="5" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1923,7 +1895,7 @@
       <c r="BZ5" s="20"/>
       <c r="CA5" s="20"/>
     </row>
-    <row r="6" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2004,7 +1976,7 @@
       <c r="BZ6" s="20"/>
       <c r="CA6" s="20"/>
     </row>
-    <row r="7" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="21"/>
       <c r="C7" s="8"/>
@@ -2085,7 +2057,7 @@
       <c r="BZ7" s="20"/>
       <c r="CA7" s="20"/>
     </row>
-    <row r="8" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="8"/>
@@ -2166,7 +2138,7 @@
       <c r="BZ8" s="20"/>
       <c r="CA8" s="20"/>
     </row>
-    <row r="9" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="21"/>
       <c r="C9" s="8"/>
@@ -2247,7 +2219,7 @@
       <c r="BZ9" s="20"/>
       <c r="CA9" s="20"/>
     </row>
-    <row r="10" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2328,7 +2300,7 @@
       <c r="BZ10" s="20"/>
       <c r="CA10" s="20"/>
     </row>
-    <row r="11" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2409,7 +2381,7 @@
       <c r="BZ11" s="20"/>
       <c r="CA11" s="20"/>
     </row>
-    <row r="12" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="21"/>
       <c r="C12" s="8"/>
@@ -2490,7 +2462,7 @@
       <c r="BZ12" s="20"/>
       <c r="CA12" s="20"/>
     </row>
-    <row r="13" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="21"/>
       <c r="C13" s="8"/>
@@ -2571,7 +2543,7 @@
       <c r="BZ13" s="20"/>
       <c r="CA13" s="20"/>
     </row>
-    <row r="14" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="21"/>
       <c r="C14" s="8"/>
@@ -2652,7 +2624,7 @@
       <c r="BZ14" s="20"/>
       <c r="CA14" s="20"/>
     </row>
-    <row r="15" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="8"/>
@@ -2733,7 +2705,7 @@
       <c r="BZ15" s="20"/>
       <c r="CA15" s="20"/>
     </row>
-    <row r="16" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="8"/>
@@ -2814,26 +2786,50 @@
       <c r="BZ16" s="20"/>
       <c r="CA16" s="20"/>
     </row>
-    <row r="17" spans="46:51" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.65" customHeight="1" spans="46:51" x14ac:dyDescent="0.25">
       <c r="AT17" s="19"/>
       <c r="AY17" s="19"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16 Y10:Y16 W10:W16 T10:T16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16 Y2:Y16 W2:W16 T2:T16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16 J10:J16" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16">
       <formula1>INDIRECT($D2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16 J2:J16" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16">
       <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J16">
+      <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J16">
+      <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W10:W16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y10:Y16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y16">
+      <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6EC84D-03DB-4168-8E19-623E98E75CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="143">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -258,16 +244,22 @@
     <t>Test1</t>
   </si>
   <si>
+    <t>10699518</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>895 Retail Team 1 (Sepap Pusube (10573442) (Inherited))</t>
   </si>
   <si>
     <t>Czechia</t>
   </si>
   <si>
-    <t>Otho</t>
-  </si>
-  <si>
-    <t>Kerluke</t>
+    <t>Virgil</t>
+  </si>
+  <si>
+    <t>Walker</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -405,19 +397,22 @@
     <t>Test2</t>
   </si>
   <si>
+    <t>10699519</t>
+  </si>
+  <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Trantow</t>
+    <t>Garnet</t>
+  </si>
+  <si>
+    <t>Kunde</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 23256195</t>
+    <t>Auto 96981989</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -453,54 +448,54 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <u/>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -512,7 +507,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -557,28 +552,16 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -923,13 +906,13 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CN17"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="109.7265625" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
     <col min="4" max="4" width="46.90625" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.90625" style="1" customWidth="1"/>
@@ -1007,11 +990,10 @@
     <col min="77" max="77" width="15" style="1" customWidth="1"/>
     <col min="78" max="78" width="33.6328125" style="1" customWidth="1"/>
     <col min="79" max="79" width="26.90625" style="1" customWidth="1"/>
-    <col min="80" max="80" width="8.90625" style="1" customWidth="1"/>
-    <col min="81" max="16384" width="8.90625" style="1"/>
+    <col min="80" max="16384" width="8.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" ht="18" customHeight="1" spans="1:92" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1263,41 +1245,45 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="8"/>
+      <c r="B2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D2" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K2" s="13">
         <v>45597</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N2" s="11">
         <v>1</v>
@@ -1306,72 +1292,72 @@
         <v>213111231</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="T2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="Q2" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" s="12" t="s">
+      <c r="U2" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="W2" s="12" t="s">
         <v>84</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>82</v>
       </c>
       <c r="X2" s="13">
         <f t="shared" ref="X2:X3" si="0">K2</f>
         <v>45597</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AA2" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AF2" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AG2" s="16">
         <v>20</v>
       </c>
       <c r="AH2" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AI2" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AJ2" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK2" s="13" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK2" s="13">
         <f t="shared" ref="AK2:AK3" si="1">AH2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL2" s="13">
         <f t="shared" ref="AL2:AL3" si="2">K2</f>
@@ -1382,10 +1368,10 @@
         <v>45597</v>
       </c>
       <c r="AN2" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AO2" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AP2" s="11">
         <v>100</v>
@@ -1395,79 +1381,79 @@
         <v>45687</v>
       </c>
       <c r="AR2" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AS2" s="17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AT2" s="18">
-        <v>9461110759</v>
+        <v>9461110901</v>
       </c>
       <c r="AU2" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AV2" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AW2" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX2" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY2" s="19">
+        <v>142743099</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AY2" s="19">
-        <v>142743023</v>
-      </c>
-      <c r="AZ2" s="13" t="s">
-        <v>103</v>
-      </c>
       <c r="BA2" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BB2" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BC2" s="13">
         <v>34284</v>
       </c>
       <c r="BD2" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="BE2" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BF2" s="17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BG2" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BH2" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BI2" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BJ2" s="17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BK2" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BL2" s="14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BM2" s="14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BN2" s="14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BO2" s="14">
         <v>2024</v>
       </c>
       <c r="BP2" s="14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BQ2" s="14">
         <v>2021</v>
@@ -1476,68 +1462,72 @@
         <v>2024</v>
       </c>
       <c r="BS2" s="14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BT2" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BU2" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BV2" s="20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BW2" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BX2" s="20">
         <v>213</v>
       </c>
       <c r="BY2" s="20" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BZ2" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="CA2" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="8"/>
+        <v>126</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D3" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K3" s="13">
         <v>45597</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N3" s="11">
         <v>1</v>
@@ -1546,72 +1536,72 @@
         <v>213111231</v>
       </c>
       <c r="P3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="T3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="Q3" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="R3" s="12" t="s">
+      <c r="U3" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="V3" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="W3" s="12" t="s">
         <v>84</v>
-      </c>
-      <c r="S3" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T3" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="U3" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="W3" s="12" t="s">
-        <v>82</v>
       </c>
       <c r="X3" s="13">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Z3" s="12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AG3" s="16">
         <v>40</v>
       </c>
       <c r="AH3" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AI3" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AJ3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK3" s="13" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK3" s="13">
         <f t="shared" si="1"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL3" s="13">
         <f t="shared" si="2"/>
@@ -1622,10 +1612,10 @@
         <v>45597</v>
       </c>
       <c r="AN3" s="12" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AO3" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AP3" s="11">
         <v>100</v>
@@ -1635,79 +1625,79 @@
         <v>45687</v>
       </c>
       <c r="AR3" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AS3" s="17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AT3" s="18">
-        <v>9461115170</v>
+        <v>9461110902</v>
       </c>
       <c r="AU3" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AV3" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AW3" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY3" s="19">
+        <v>152733400</v>
+      </c>
+      <c r="AZ3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AY3" s="19">
-        <v>142733024</v>
-      </c>
-      <c r="AZ3" s="13" t="s">
-        <v>103</v>
-      </c>
       <c r="BA3" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BB3" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BC3" s="13">
         <v>34284</v>
       </c>
       <c r="BD3" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="BE3" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BF3" s="17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BG3" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BH3" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BI3" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BJ3" s="17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BK3" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BL3" s="14" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BM3" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="BN3" s="14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BO3" s="14">
         <v>2000</v>
       </c>
       <c r="BP3" s="14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BQ3" s="14">
         <v>1995</v>
@@ -1716,34 +1706,34 @@
         <v>2000</v>
       </c>
       <c r="BS3" s="14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="BT3" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BU3" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BV3" s="20" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="BW3" s="20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="BX3" s="20">
         <v>201</v>
       </c>
       <c r="BY3" s="20" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BZ3" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="CA3" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1824,7 +1814,7 @@
       <c r="BZ4" s="20"/>
       <c r="CA4" s="20"/>
     </row>
-    <row r="5" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1905,7 +1895,7 @@
       <c r="BZ5" s="20"/>
       <c r="CA5" s="20"/>
     </row>
-    <row r="6" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1986,7 +1976,7 @@
       <c r="BZ6" s="20"/>
       <c r="CA6" s="20"/>
     </row>
-    <row r="7" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="21"/>
       <c r="C7" s="8"/>
@@ -2067,7 +2057,7 @@
       <c r="BZ7" s="20"/>
       <c r="CA7" s="20"/>
     </row>
-    <row r="8" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="8"/>
@@ -2148,7 +2138,7 @@
       <c r="BZ8" s="20"/>
       <c r="CA8" s="20"/>
     </row>
-    <row r="9" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="21"/>
       <c r="C9" s="8"/>
@@ -2229,7 +2219,7 @@
       <c r="BZ9" s="20"/>
       <c r="CA9" s="20"/>
     </row>
-    <row r="10" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2310,7 +2300,7 @@
       <c r="BZ10" s="20"/>
       <c r="CA10" s="20"/>
     </row>
-    <row r="11" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2391,7 +2381,7 @@
       <c r="BZ11" s="20"/>
       <c r="CA11" s="20"/>
     </row>
-    <row r="12" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="21"/>
       <c r="C12" s="8"/>
@@ -2472,7 +2462,7 @@
       <c r="BZ12" s="20"/>
       <c r="CA12" s="20"/>
     </row>
-    <row r="13" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="21"/>
       <c r="C13" s="8"/>
@@ -2553,7 +2543,7 @@
       <c r="BZ13" s="20"/>
       <c r="CA13" s="20"/>
     </row>
-    <row r="14" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="21"/>
       <c r="C14" s="8"/>
@@ -2634,7 +2624,7 @@
       <c r="BZ14" s="20"/>
       <c r="CA14" s="20"/>
     </row>
-    <row r="15" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="8"/>
@@ -2715,7 +2705,7 @@
       <c r="BZ15" s="20"/>
       <c r="CA15" s="20"/>
     </row>
-    <row r="16" spans="1:92" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="8"/>
@@ -2796,26 +2786,50 @@
       <c r="BZ16" s="20"/>
       <c r="CA16" s="20"/>
     </row>
-    <row r="17" spans="46:51" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" ht="15.65" customHeight="1" spans="46:51" x14ac:dyDescent="0.25">
       <c r="AT17" s="19"/>
       <c r="AY17" s="19"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16 Y10:Y16 W10:W16 T10:T16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16 Y2:Y16 W2:W16 T2:T16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16 J10:J16" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16">
       <formula1>INDIRECT($D2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16 J2:J16" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16">
       <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J16">
+      <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J16">
+      <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W10:W16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y10:Y16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y16">
+      <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{1098CD3E-4203-46DA-A374-6D842384574E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{B9455642-526F-4A08-9641-0084BA48857A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="143">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -259,7 +259,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698832</t>
+    <t>10699009</t>
   </si>
   <si>
     <t>Passed</t>
@@ -271,10 +271,10 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>CzNMng</t>
-  </si>
-  <si>
-    <t>DryrunPK17</t>
+    <t>Otho</t>
+  </si>
+  <si>
+    <t>Kerluke</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -412,16 +412,22 @@
     <t>Test2</t>
   </si>
   <si>
+    <t>10699010</t>
+  </si>
+  <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>CzMng</t>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Trantow</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 13819394</t>
+    <t>Auto 23256195</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -534,6 +540,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
@@ -541,11 +552,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -607,6 +613,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -620,7 +629,7 @@
     <xf numFmtId="14" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
@@ -642,9 +651,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1271,80 +1277,80 @@
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>76</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="13">
         <v>45597</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="11">
         <v>1</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="14">
         <v>213111231</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="R2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="S2" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="U2" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="V2" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="W2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="12">
+      <c r="X2" s="13">
         <f t="shared" ref="X2:X3" si="0">K2</f>
         <v>45597</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Y2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="Z2" s="12" t="s">
         <v>92</v>
       </c>
       <c r="AA2" s="8" t="s">
@@ -1356,402 +1362,402 @@
       <c r="AC2" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AD2" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AE2" s="11" t="s">
         <v>97</v>
       </c>
       <c r="AF2" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AG2" s="15">
+      <c r="AG2" s="16">
         <v>20</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AH2" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="AI2" s="11" t="s">
+      <c r="AI2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AJ2" s="11" t="s">
+      <c r="AJ2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AK2" s="12" t="str">
+      <c r="AK2" s="13" t="str">
         <f t="shared" ref="AK2:AK3" si="1">AH2</f>
         <v>N/A</v>
       </c>
-      <c r="AL2" s="12">
+      <c r="AL2" s="13">
         <f t="shared" ref="AL2:AL3" si="2">K2</f>
         <v>45597</v>
       </c>
-      <c r="AM2" s="12">
+      <c r="AM2" s="13">
         <f t="shared" ref="AM2:AM3" si="3">K2</f>
         <v>45597</v>
       </c>
-      <c r="AN2" s="11" t="s">
+      <c r="AN2" s="12" t="s">
         <v>102</v>
       </c>
       <c r="AO2" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="AP2" s="10">
+      <c r="AP2" s="11">
         <v>100</v>
       </c>
-      <c r="AQ2" s="12">
+      <c r="AQ2" s="13">
         <f t="shared" ref="AQ2:AQ3" si="4">K2+90</f>
         <v>45687</v>
       </c>
-      <c r="AR2" s="10" t="s">
+      <c r="AR2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AS2" s="16" t="s">
+      <c r="AS2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="17">
-        <v>9361115742</v>
-      </c>
-      <c r="AU2" s="12" t="s">
+      <c r="AT2" s="18">
+        <v>9361110759</v>
+      </c>
+      <c r="AU2" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AV2" s="12" t="s">
+      <c r="AV2" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="AW2" s="10" t="s">
+      <c r="AW2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AX2" s="16" t="s">
+      <c r="AX2" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="AY2" s="18">
-        <v>142062991</v>
-      </c>
-      <c r="AZ2" s="12" t="s">
+      <c r="AY2" s="19">
+        <v>141743023</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BA2" s="12" t="s">
+      <c r="BA2" s="13" t="s">
         <v>106</v>
       </c>
       <c r="BB2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="BC2" s="12">
+      <c r="BC2" s="13">
         <v>34284</v>
       </c>
-      <c r="BD2" s="16" t="s">
+      <c r="BD2" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="BE2" s="16" t="s">
+      <c r="BE2" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="16" t="s">
+      <c r="BF2" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="BG2" s="10" t="s">
+      <c r="BG2" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="10" t="s">
+      <c r="BH2" s="11" t="s">
         <v>112</v>
       </c>
       <c r="BI2" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="BJ2" s="16" t="s">
+      <c r="BJ2" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="BK2" s="13" t="s">
+      <c r="BK2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="BL2" s="13" t="s">
+      <c r="BL2" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="BM2" s="13" t="s">
+      <c r="BM2" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="BN2" s="13" t="s">
+      <c r="BN2" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="BO2" s="13">
+      <c r="BO2" s="14">
         <v>2024</v>
       </c>
-      <c r="BP2" s="13" t="s">
+      <c r="BP2" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="BQ2" s="13">
+      <c r="BQ2" s="14">
         <v>2021</v>
       </c>
-      <c r="BR2" s="13">
+      <c r="BR2" s="14">
         <v>2024</v>
       </c>
-      <c r="BS2" s="13" t="s">
+      <c r="BS2" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="13" t="s">
+      <c r="BT2" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="BU2" s="13" t="s">
+      <c r="BU2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="BV2" s="19" t="s">
+      <c r="BV2" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="BW2" s="19" t="s">
+      <c r="BW2" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="BX2" s="19">
+      <c r="BX2" s="20">
         <v>213</v>
       </c>
-      <c r="BY2" s="19" t="s">
+      <c r="BY2" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="BZ2" s="19" t="s">
+      <c r="BZ2" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="CA2" s="19" t="s">
+      <c r="CA2" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="21">
-        <v>10698834</v>
+      <c r="B3" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="G3" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="I3" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="13">
         <v>45597</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="11">
         <v>1</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="14">
         <v>213111231</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="S3" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="T3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="U3" s="12" t="s">
+      <c r="U3" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="V3" s="14" t="s">
+      <c r="V3" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="W3" s="11" t="s">
+      <c r="W3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="X3" s="12">
+      <c r="X3" s="13">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
-      <c r="Y3" s="11" t="s">
+      <c r="Y3" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="Z3" s="11" t="s">
-        <v>130</v>
+      <c r="Z3" s="12" t="s">
+        <v>132</v>
       </c>
       <c r="AA3" s="8" t="s">
         <v>93</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="AD3" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD3" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AE3" s="10" t="s">
+      <c r="AE3" s="11" t="s">
         <v>97</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="AG3" s="15">
+        <v>135</v>
+      </c>
+      <c r="AG3" s="16">
         <v>40</v>
       </c>
-      <c r="AH3" s="12" t="s">
+      <c r="AH3" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="AI3" s="11" t="s">
+      <c r="AI3" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AJ3" s="11" t="s">
+      <c r="AJ3" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AK3" s="12" t="str">
+      <c r="AK3" s="13" t="str">
         <f t="shared" si="1"/>
         <v>N/A</v>
       </c>
-      <c r="AL3" s="12">
+      <c r="AL3" s="13">
         <f t="shared" si="2"/>
         <v>45597</v>
       </c>
-      <c r="AM3" s="12">
+      <c r="AM3" s="13">
         <f t="shared" si="3"/>
         <v>45597</v>
       </c>
-      <c r="AN3" s="11" t="s">
-        <v>134</v>
+      <c r="AN3" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="AO3" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="AP3" s="10">
+        <v>137</v>
+      </c>
+      <c r="AP3" s="11">
         <v>100</v>
       </c>
-      <c r="AQ3" s="12">
+      <c r="AQ3" s="13">
         <f t="shared" si="4"/>
         <v>45687</v>
       </c>
-      <c r="AR3" s="10" t="s">
+      <c r="AR3" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AS3" s="16" t="s">
+      <c r="AS3" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="AT3" s="17">
-        <v>9361118690</v>
-      </c>
-      <c r="AU3" s="12" t="s">
+      <c r="AT3" s="18">
+        <v>9361115170</v>
+      </c>
+      <c r="AU3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AV3" s="12" t="s">
+      <c r="AV3" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="AW3" s="10" t="s">
+      <c r="AW3" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AX3" s="16" t="s">
+      <c r="AX3" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="AY3" s="18">
-        <v>142052992</v>
-      </c>
-      <c r="AZ3" s="12" t="s">
+      <c r="AY3" s="19">
+        <v>141733024</v>
+      </c>
+      <c r="AZ3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BA3" s="12" t="s">
+      <c r="BA3" s="13" t="s">
         <v>106</v>
       </c>
       <c r="BB3" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="BC3" s="12">
+      <c r="BC3" s="13">
         <v>34284</v>
       </c>
-      <c r="BD3" s="16" t="s">
+      <c r="BD3" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="BE3" s="16" t="s">
+      <c r="BE3" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="BF3" s="16" t="s">
+      <c r="BF3" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="BG3" s="10" t="s">
+      <c r="BG3" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="BH3" s="10" t="s">
+      <c r="BH3" s="11" t="s">
         <v>112</v>
       </c>
       <c r="BI3" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="BJ3" s="16" t="s">
+      <c r="BJ3" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="BK3" s="13" t="s">
+      <c r="BK3" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="BL3" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="BM3" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="BN3" s="13" t="s">
+      <c r="BL3" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="BM3" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="BN3" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="BO3" s="13">
+      <c r="BO3" s="14">
         <v>2000</v>
       </c>
-      <c r="BP3" s="13" t="s">
+      <c r="BP3" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="BQ3" s="13">
+      <c r="BQ3" s="14">
         <v>1995</v>
       </c>
-      <c r="BR3" s="13">
+      <c r="BR3" s="14">
         <v>2000</v>
       </c>
-      <c r="BS3" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="BT3" s="13" t="s">
+      <c r="BS3" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="BT3" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="BU3" s="13" t="s">
+      <c r="BU3" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="BV3" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="BW3" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="BX3" s="19">
+      <c r="BV3" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="BW3" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="BX3" s="20">
         <v>201</v>
       </c>
-      <c r="BY3" s="19" t="s">
+      <c r="BY3" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="BZ3" s="19" t="s">
+      <c r="BZ3" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="CA3" s="19" t="s">
+      <c r="CA3" s="20" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1759,1058 +1765,1058 @@
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="12"/>
       <c r="AA4" s="8"/>
       <c r="AB4" s="8"/>
       <c r="AC4" s="8"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10"/>
+      <c r="AD4" s="11"/>
+      <c r="AE4" s="11"/>
       <c r="AF4" s="8"/>
-      <c r="AG4" s="15"/>
-      <c r="AH4" s="12"/>
-      <c r="AI4" s="11"/>
-      <c r="AJ4" s="11"/>
-      <c r="AK4" s="12"/>
-      <c r="AL4" s="12"/>
-      <c r="AM4" s="12"/>
-      <c r="AN4" s="11"/>
+      <c r="AG4" s="16"/>
+      <c r="AH4" s="13"/>
+      <c r="AI4" s="12"/>
+      <c r="AJ4" s="12"/>
+      <c r="AK4" s="13"/>
+      <c r="AL4" s="13"/>
+      <c r="AM4" s="13"/>
+      <c r="AN4" s="12"/>
       <c r="AO4" s="8"/>
-      <c r="AP4" s="10"/>
-      <c r="AQ4" s="12"/>
-      <c r="AR4" s="10"/>
-      <c r="AS4" s="16"/>
-      <c r="AT4" s="17"/>
-      <c r="AU4" s="12"/>
-      <c r="AV4" s="12"/>
-      <c r="AW4" s="10"/>
-      <c r="AX4" s="16"/>
-      <c r="AY4" s="18"/>
-      <c r="AZ4" s="12"/>
-      <c r="BA4" s="12"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="13"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="17"/>
+      <c r="AT4" s="18"/>
+      <c r="AU4" s="13"/>
+      <c r="AV4" s="13"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="17"/>
+      <c r="AY4" s="19"/>
+      <c r="AZ4" s="13"/>
+      <c r="BA4" s="13"/>
       <c r="BB4" s="8"/>
-      <c r="BC4" s="12"/>
-      <c r="BD4" s="16"/>
-      <c r="BE4" s="16"/>
-      <c r="BF4" s="16"/>
-      <c r="BG4" s="10"/>
-      <c r="BH4" s="10"/>
+      <c r="BC4" s="13"/>
+      <c r="BD4" s="17"/>
+      <c r="BE4" s="17"/>
+      <c r="BF4" s="17"/>
+      <c r="BG4" s="11"/>
+      <c r="BH4" s="11"/>
       <c r="BI4" s="8"/>
-      <c r="BJ4" s="16"/>
-      <c r="BK4" s="13"/>
-      <c r="BL4" s="13"/>
-      <c r="BM4" s="13"/>
-      <c r="BN4" s="13"/>
-      <c r="BO4" s="13"/>
-      <c r="BP4" s="13"/>
-      <c r="BQ4" s="13"/>
-      <c r="BR4" s="13"/>
-      <c r="BS4" s="13"/>
-      <c r="BT4" s="13"/>
-      <c r="BU4" s="13"/>
-      <c r="BV4" s="19"/>
-      <c r="BW4" s="19"/>
-      <c r="BX4" s="19"/>
-      <c r="BY4" s="19"/>
-      <c r="BZ4" s="19"/>
-      <c r="CA4" s="19"/>
+      <c r="BJ4" s="17"/>
+      <c r="BK4" s="14"/>
+      <c r="BL4" s="14"/>
+      <c r="BM4" s="14"/>
+      <c r="BN4" s="14"/>
+      <c r="BO4" s="14"/>
+      <c r="BP4" s="14"/>
+      <c r="BQ4" s="14"/>
+      <c r="BR4" s="14"/>
+      <c r="BS4" s="14"/>
+      <c r="BT4" s="14"/>
+      <c r="BU4" s="14"/>
+      <c r="BV4" s="20"/>
+      <c r="BW4" s="20"/>
+      <c r="BX4" s="20"/>
+      <c r="BY4" s="20"/>
+      <c r="BZ4" s="20"/>
+      <c r="CA4" s="20"/>
     </row>
     <row r="5" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="11"/>
-      <c r="Z5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
       <c r="AC5" s="8"/>
-      <c r="AD5" s="10"/>
-      <c r="AE5" s="10"/>
+      <c r="AD5" s="11"/>
+      <c r="AE5" s="11"/>
       <c r="AF5" s="8"/>
-      <c r="AG5" s="15"/>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="11"/>
-      <c r="AJ5" s="11"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="12"/>
-      <c r="AM5" s="12"/>
-      <c r="AN5" s="11"/>
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="13"/>
+      <c r="AI5" s="12"/>
+      <c r="AJ5" s="12"/>
+      <c r="AK5" s="13"/>
+      <c r="AL5" s="13"/>
+      <c r="AM5" s="13"/>
+      <c r="AN5" s="12"/>
       <c r="AO5" s="8"/>
-      <c r="AP5" s="10"/>
-      <c r="AQ5" s="12"/>
-      <c r="AR5" s="10"/>
-      <c r="AS5" s="16"/>
-      <c r="AT5" s="17"/>
-      <c r="AU5" s="12"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="10"/>
-      <c r="AX5" s="16"/>
-      <c r="AY5" s="18"/>
-      <c r="AZ5" s="12"/>
-      <c r="BA5" s="12"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="13"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="17"/>
+      <c r="AT5" s="18"/>
+      <c r="AU5" s="13"/>
+      <c r="AV5" s="13"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="17"/>
+      <c r="AY5" s="19"/>
+      <c r="AZ5" s="13"/>
+      <c r="BA5" s="13"/>
       <c r="BB5" s="8"/>
-      <c r="BC5" s="12"/>
-      <c r="BD5" s="16"/>
-      <c r="BE5" s="16"/>
-      <c r="BF5" s="16"/>
-      <c r="BG5" s="10"/>
-      <c r="BH5" s="10"/>
+      <c r="BC5" s="13"/>
+      <c r="BD5" s="17"/>
+      <c r="BE5" s="17"/>
+      <c r="BF5" s="17"/>
+      <c r="BG5" s="11"/>
+      <c r="BH5" s="11"/>
       <c r="BI5" s="8"/>
-      <c r="BJ5" s="16"/>
-      <c r="BK5" s="13"/>
-      <c r="BL5" s="13"/>
-      <c r="BM5" s="13"/>
-      <c r="BN5" s="13"/>
-      <c r="BO5" s="13"/>
-      <c r="BP5" s="13"/>
-      <c r="BQ5" s="13"/>
-      <c r="BR5" s="13"/>
-      <c r="BS5" s="13"/>
-      <c r="BT5" s="13"/>
-      <c r="BU5" s="13"/>
-      <c r="BV5" s="19"/>
-      <c r="BW5" s="19"/>
-      <c r="BX5" s="19"/>
-      <c r="BY5" s="19"/>
-      <c r="BZ5" s="19"/>
-      <c r="CA5" s="19"/>
+      <c r="BJ5" s="17"/>
+      <c r="BK5" s="14"/>
+      <c r="BL5" s="14"/>
+      <c r="BM5" s="14"/>
+      <c r="BN5" s="14"/>
+      <c r="BO5" s="14"/>
+      <c r="BP5" s="14"/>
+      <c r="BQ5" s="14"/>
+      <c r="BR5" s="14"/>
+      <c r="BS5" s="14"/>
+      <c r="BT5" s="14"/>
+      <c r="BU5" s="14"/>
+      <c r="BV5" s="20"/>
+      <c r="BW5" s="20"/>
+      <c r="BX5" s="20"/>
+      <c r="BY5" s="20"/>
+      <c r="BZ5" s="20"/>
+      <c r="CA5" s="20"/>
     </row>
     <row r="6" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="11"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="11"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
-      <c r="AD6" s="10"/>
-      <c r="AE6" s="10"/>
+      <c r="AD6" s="11"/>
+      <c r="AE6" s="11"/>
       <c r="AF6" s="8"/>
-      <c r="AG6" s="15"/>
-      <c r="AH6" s="12"/>
-      <c r="AI6" s="11"/>
-      <c r="AJ6" s="11"/>
-      <c r="AK6" s="12"/>
-      <c r="AL6" s="12"/>
-      <c r="AM6" s="12"/>
-      <c r="AN6" s="11"/>
+      <c r="AG6" s="16"/>
+      <c r="AH6" s="13"/>
+      <c r="AI6" s="12"/>
+      <c r="AJ6" s="12"/>
+      <c r="AK6" s="13"/>
+      <c r="AL6" s="13"/>
+      <c r="AM6" s="13"/>
+      <c r="AN6" s="12"/>
       <c r="AO6" s="8"/>
-      <c r="AP6" s="10"/>
-      <c r="AQ6" s="12"/>
-      <c r="AR6" s="10"/>
-      <c r="AS6" s="16"/>
-      <c r="AT6" s="17"/>
-      <c r="AU6" s="12"/>
-      <c r="AV6" s="12"/>
-      <c r="AW6" s="10"/>
-      <c r="AX6" s="16"/>
-      <c r="AY6" s="18"/>
-      <c r="AZ6" s="12"/>
-      <c r="BA6" s="12"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="13"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="17"/>
+      <c r="AT6" s="18"/>
+      <c r="AU6" s="13"/>
+      <c r="AV6" s="13"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="17"/>
+      <c r="AY6" s="19"/>
+      <c r="AZ6" s="13"/>
+      <c r="BA6" s="13"/>
       <c r="BB6" s="8"/>
-      <c r="BC6" s="12"/>
-      <c r="BD6" s="16"/>
-      <c r="BE6" s="16"/>
-      <c r="BF6" s="16"/>
-      <c r="BG6" s="10"/>
-      <c r="BH6" s="10"/>
+      <c r="BC6" s="13"/>
+      <c r="BD6" s="17"/>
+      <c r="BE6" s="17"/>
+      <c r="BF6" s="17"/>
+      <c r="BG6" s="11"/>
+      <c r="BH6" s="11"/>
       <c r="BI6" s="8"/>
-      <c r="BJ6" s="16"/>
-      <c r="BK6" s="13"/>
-      <c r="BL6" s="13"/>
-      <c r="BM6" s="13"/>
-      <c r="BN6" s="13"/>
-      <c r="BO6" s="13"/>
-      <c r="BP6" s="13"/>
-      <c r="BQ6" s="13"/>
-      <c r="BR6" s="13"/>
-      <c r="BS6" s="13"/>
-      <c r="BT6" s="13"/>
-      <c r="BU6" s="13"/>
-      <c r="BV6" s="19"/>
-      <c r="BW6" s="19"/>
-      <c r="BX6" s="19"/>
-      <c r="BY6" s="19"/>
-      <c r="BZ6" s="19"/>
-      <c r="CA6" s="19"/>
+      <c r="BJ6" s="17"/>
+      <c r="BK6" s="14"/>
+      <c r="BL6" s="14"/>
+      <c r="BM6" s="14"/>
+      <c r="BN6" s="14"/>
+      <c r="BO6" s="14"/>
+      <c r="BP6" s="14"/>
+      <c r="BQ6" s="14"/>
+      <c r="BR6" s="14"/>
+      <c r="BS6" s="14"/>
+      <c r="BT6" s="14"/>
+      <c r="BU6" s="14"/>
+      <c r="BV6" s="20"/>
+      <c r="BW6" s="20"/>
+      <c r="BX6" s="20"/>
+      <c r="BY6" s="20"/>
+      <c r="BZ6" s="20"/>
+      <c r="CA6" s="20"/>
     </row>
     <row r="7" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
-      <c r="B7" s="20"/>
+      <c r="B7" s="21"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
       <c r="F7" s="8"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="11"/>
-      <c r="Z7" s="11"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
       <c r="AA7" s="8"/>
       <c r="AB7" s="8"/>
       <c r="AC7" s="8"/>
-      <c r="AD7" s="10"/>
-      <c r="AE7" s="10"/>
+      <c r="AD7" s="11"/>
+      <c r="AE7" s="11"/>
       <c r="AF7" s="8"/>
-      <c r="AG7" s="15"/>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="11"/>
-      <c r="AJ7" s="11"/>
-      <c r="AK7" s="12"/>
-      <c r="AL7" s="12"/>
-      <c r="AM7" s="12"/>
-      <c r="AN7" s="11"/>
+      <c r="AG7" s="16"/>
+      <c r="AH7" s="13"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="13"/>
+      <c r="AL7" s="13"/>
+      <c r="AM7" s="13"/>
+      <c r="AN7" s="12"/>
       <c r="AO7" s="8"/>
-      <c r="AP7" s="10"/>
-      <c r="AQ7" s="12"/>
-      <c r="AR7" s="10"/>
-      <c r="AS7" s="16"/>
-      <c r="AT7" s="17"/>
-      <c r="AU7" s="12"/>
-      <c r="AV7" s="12"/>
-      <c r="AW7" s="10"/>
-      <c r="AX7" s="16"/>
-      <c r="AY7" s="18"/>
-      <c r="AZ7" s="12"/>
-      <c r="BA7" s="12"/>
+      <c r="AP7" s="11"/>
+      <c r="AQ7" s="13"/>
+      <c r="AR7" s="11"/>
+      <c r="AS7" s="17"/>
+      <c r="AT7" s="18"/>
+      <c r="AU7" s="13"/>
+      <c r="AV7" s="13"/>
+      <c r="AW7" s="11"/>
+      <c r="AX7" s="17"/>
+      <c r="AY7" s="19"/>
+      <c r="AZ7" s="13"/>
+      <c r="BA7" s="13"/>
       <c r="BB7" s="8"/>
-      <c r="BC7" s="12"/>
-      <c r="BD7" s="16"/>
-      <c r="BE7" s="16"/>
-      <c r="BF7" s="16"/>
-      <c r="BG7" s="10"/>
-      <c r="BH7" s="10"/>
+      <c r="BC7" s="13"/>
+      <c r="BD7" s="17"/>
+      <c r="BE7" s="17"/>
+      <c r="BF7" s="17"/>
+      <c r="BG7" s="11"/>
+      <c r="BH7" s="11"/>
       <c r="BI7" s="8"/>
-      <c r="BJ7" s="16"/>
-      <c r="BK7" s="13"/>
-      <c r="BL7" s="13"/>
-      <c r="BM7" s="13"/>
-      <c r="BN7" s="13"/>
-      <c r="BO7" s="13"/>
-      <c r="BP7" s="13"/>
-      <c r="BQ7" s="13"/>
-      <c r="BR7" s="13"/>
-      <c r="BS7" s="13"/>
-      <c r="BT7" s="13"/>
-      <c r="BU7" s="13"/>
-      <c r="BV7" s="19"/>
-      <c r="BW7" s="19"/>
-      <c r="BX7" s="19"/>
-      <c r="BY7" s="19"/>
-      <c r="BZ7" s="19"/>
-      <c r="CA7" s="19"/>
+      <c r="BJ7" s="17"/>
+      <c r="BK7" s="14"/>
+      <c r="BL7" s="14"/>
+      <c r="BM7" s="14"/>
+      <c r="BN7" s="14"/>
+      <c r="BO7" s="14"/>
+      <c r="BP7" s="14"/>
+      <c r="BQ7" s="14"/>
+      <c r="BR7" s="14"/>
+      <c r="BS7" s="14"/>
+      <c r="BT7" s="14"/>
+      <c r="BU7" s="14"/>
+      <c r="BV7" s="20"/>
+      <c r="BW7" s="20"/>
+      <c r="BX7" s="20"/>
+      <c r="BY7" s="20"/>
+      <c r="BZ7" s="20"/>
+      <c r="CA7" s="20"/>
     </row>
     <row r="8" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
-      <c r="B8" s="21"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
       <c r="F8" s="8"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="11"/>
-      <c r="Z8" s="11"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
       <c r="AC8" s="8"/>
-      <c r="AD8" s="10"/>
-      <c r="AE8" s="10"/>
+      <c r="AD8" s="11"/>
+      <c r="AE8" s="11"/>
       <c r="AF8" s="8"/>
-      <c r="AG8" s="15"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="11"/>
-      <c r="AJ8" s="11"/>
-      <c r="AK8" s="12"/>
-      <c r="AL8" s="12"/>
-      <c r="AM8" s="12"/>
-      <c r="AN8" s="11"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="13"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="13"/>
+      <c r="AL8" s="13"/>
+      <c r="AM8" s="13"/>
+      <c r="AN8" s="12"/>
       <c r="AO8" s="8"/>
-      <c r="AP8" s="10"/>
-      <c r="AQ8" s="12"/>
-      <c r="AR8" s="10"/>
-      <c r="AS8" s="16"/>
-      <c r="AT8" s="17"/>
-      <c r="AU8" s="12"/>
-      <c r="AV8" s="12"/>
-      <c r="AW8" s="10"/>
-      <c r="AX8" s="16"/>
-      <c r="AY8" s="18"/>
-      <c r="AZ8" s="12"/>
-      <c r="BA8" s="12"/>
+      <c r="AP8" s="11"/>
+      <c r="AQ8" s="13"/>
+      <c r="AR8" s="11"/>
+      <c r="AS8" s="17"/>
+      <c r="AT8" s="18"/>
+      <c r="AU8" s="13"/>
+      <c r="AV8" s="13"/>
+      <c r="AW8" s="11"/>
+      <c r="AX8" s="17"/>
+      <c r="AY8" s="19"/>
+      <c r="AZ8" s="13"/>
+      <c r="BA8" s="13"/>
       <c r="BB8" s="8"/>
-      <c r="BC8" s="12"/>
-      <c r="BD8" s="16"/>
-      <c r="BE8" s="16"/>
-      <c r="BF8" s="16"/>
-      <c r="BG8" s="10"/>
-      <c r="BH8" s="10"/>
+      <c r="BC8" s="13"/>
+      <c r="BD8" s="17"/>
+      <c r="BE8" s="17"/>
+      <c r="BF8" s="17"/>
+      <c r="BG8" s="11"/>
+      <c r="BH8" s="11"/>
       <c r="BI8" s="8"/>
-      <c r="BJ8" s="16"/>
-      <c r="BK8" s="13"/>
-      <c r="BL8" s="13"/>
-      <c r="BM8" s="13"/>
-      <c r="BN8" s="13"/>
-      <c r="BO8" s="13"/>
-      <c r="BP8" s="13"/>
-      <c r="BQ8" s="13"/>
-      <c r="BR8" s="13"/>
-      <c r="BS8" s="13"/>
-      <c r="BT8" s="13"/>
-      <c r="BU8" s="13"/>
-      <c r="BV8" s="19"/>
-      <c r="BW8" s="19"/>
-      <c r="BX8" s="19"/>
-      <c r="BY8" s="19"/>
-      <c r="BZ8" s="19"/>
-      <c r="CA8" s="19"/>
+      <c r="BJ8" s="17"/>
+      <c r="BK8" s="14"/>
+      <c r="BL8" s="14"/>
+      <c r="BM8" s="14"/>
+      <c r="BN8" s="14"/>
+      <c r="BO8" s="14"/>
+      <c r="BP8" s="14"/>
+      <c r="BQ8" s="14"/>
+      <c r="BR8" s="14"/>
+      <c r="BS8" s="14"/>
+      <c r="BT8" s="14"/>
+      <c r="BU8" s="14"/>
+      <c r="BV8" s="20"/>
+      <c r="BW8" s="20"/>
+      <c r="BX8" s="20"/>
+      <c r="BY8" s="20"/>
+      <c r="BZ8" s="20"/>
+      <c r="CA8" s="20"/>
     </row>
     <row r="9" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
-      <c r="B9" s="20"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
       <c r="F9" s="8"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="11"/>
-      <c r="Z9" s="11"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="12"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
       <c r="AC9" s="8"/>
-      <c r="AD9" s="10"/>
-      <c r="AE9" s="10"/>
+      <c r="AD9" s="11"/>
+      <c r="AE9" s="11"/>
       <c r="AF9" s="8"/>
-      <c r="AG9" s="15"/>
-      <c r="AH9" s="12"/>
-      <c r="AI9" s="11"/>
-      <c r="AJ9" s="11"/>
-      <c r="AK9" s="12"/>
-      <c r="AL9" s="12"/>
-      <c r="AM9" s="12"/>
-      <c r="AN9" s="11"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="13"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="13"/>
+      <c r="AL9" s="13"/>
+      <c r="AM9" s="13"/>
+      <c r="AN9" s="12"/>
       <c r="AO9" s="8"/>
-      <c r="AP9" s="10"/>
-      <c r="AQ9" s="12"/>
-      <c r="AR9" s="10"/>
-      <c r="AS9" s="16"/>
-      <c r="AT9" s="17"/>
-      <c r="AU9" s="12"/>
-      <c r="AV9" s="12"/>
-      <c r="AW9" s="10"/>
-      <c r="AX9" s="16"/>
-      <c r="AY9" s="18"/>
-      <c r="AZ9" s="12"/>
-      <c r="BA9" s="12"/>
+      <c r="AP9" s="11"/>
+      <c r="AQ9" s="13"/>
+      <c r="AR9" s="11"/>
+      <c r="AS9" s="17"/>
+      <c r="AT9" s="18"/>
+      <c r="AU9" s="13"/>
+      <c r="AV9" s="13"/>
+      <c r="AW9" s="11"/>
+      <c r="AX9" s="17"/>
+      <c r="AY9" s="19"/>
+      <c r="AZ9" s="13"/>
+      <c r="BA9" s="13"/>
       <c r="BB9" s="8"/>
-      <c r="BC9" s="12"/>
-      <c r="BD9" s="16"/>
-      <c r="BE9" s="16"/>
-      <c r="BF9" s="16"/>
-      <c r="BG9" s="10"/>
-      <c r="BH9" s="10"/>
+      <c r="BC9" s="13"/>
+      <c r="BD9" s="17"/>
+      <c r="BE9" s="17"/>
+      <c r="BF9" s="17"/>
+      <c r="BG9" s="11"/>
+      <c r="BH9" s="11"/>
       <c r="BI9" s="8"/>
-      <c r="BJ9" s="16"/>
-      <c r="BK9" s="13"/>
-      <c r="BL9" s="13"/>
-      <c r="BM9" s="13"/>
-      <c r="BN9" s="13"/>
-      <c r="BO9" s="13"/>
-      <c r="BP9" s="13"/>
-      <c r="BQ9" s="13"/>
-      <c r="BR9" s="13"/>
-      <c r="BS9" s="13"/>
-      <c r="BT9" s="13"/>
-      <c r="BU9" s="13"/>
-      <c r="BV9" s="19"/>
-      <c r="BW9" s="19"/>
-      <c r="BX9" s="19"/>
-      <c r="BY9" s="19"/>
-      <c r="BZ9" s="19"/>
-      <c r="CA9" s="19"/>
+      <c r="BJ9" s="17"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="20"/>
+      <c r="BW9" s="20"/>
+      <c r="BX9" s="20"/>
+      <c r="BY9" s="20"/>
+      <c r="BZ9" s="20"/>
+      <c r="CA9" s="20"/>
     </row>
     <row r="10" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
       <c r="F10" s="8"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="11"/>
-      <c r="Z10" s="11"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
       <c r="AC10" s="8"/>
-      <c r="AD10" s="10"/>
-      <c r="AE10" s="10"/>
+      <c r="AD10" s="11"/>
+      <c r="AE10" s="11"/>
       <c r="AF10" s="8"/>
-      <c r="AG10" s="15"/>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="11"/>
-      <c r="AJ10" s="11"/>
-      <c r="AK10" s="12"/>
-      <c r="AL10" s="12"/>
-      <c r="AM10" s="12"/>
-      <c r="AN10" s="11"/>
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="13"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="13"/>
+      <c r="AL10" s="13"/>
+      <c r="AM10" s="13"/>
+      <c r="AN10" s="12"/>
       <c r="AO10" s="8"/>
-      <c r="AP10" s="10"/>
-      <c r="AQ10" s="12"/>
-      <c r="AR10" s="10"/>
-      <c r="AS10" s="16"/>
-      <c r="AT10" s="17"/>
-      <c r="AU10" s="12"/>
-      <c r="AV10" s="12"/>
-      <c r="AW10" s="10"/>
-      <c r="AX10" s="16"/>
-      <c r="AY10" s="18"/>
-      <c r="AZ10" s="12"/>
-      <c r="BA10" s="12"/>
+      <c r="AP10" s="11"/>
+      <c r="AQ10" s="13"/>
+      <c r="AR10" s="11"/>
+      <c r="AS10" s="17"/>
+      <c r="AT10" s="18"/>
+      <c r="AU10" s="13"/>
+      <c r="AV10" s="13"/>
+      <c r="AW10" s="11"/>
+      <c r="AX10" s="17"/>
+      <c r="AY10" s="19"/>
+      <c r="AZ10" s="13"/>
+      <c r="BA10" s="13"/>
       <c r="BB10" s="8"/>
-      <c r="BC10" s="12"/>
-      <c r="BD10" s="16"/>
-      <c r="BE10" s="16"/>
-      <c r="BF10" s="16"/>
-      <c r="BG10" s="10"/>
-      <c r="BH10" s="10"/>
+      <c r="BC10" s="13"/>
+      <c r="BD10" s="17"/>
+      <c r="BE10" s="17"/>
+      <c r="BF10" s="17"/>
+      <c r="BG10" s="11"/>
+      <c r="BH10" s="11"/>
       <c r="BI10" s="8"/>
-      <c r="BJ10" s="16"/>
-      <c r="BK10" s="13"/>
-      <c r="BL10" s="13"/>
-      <c r="BM10" s="13"/>
-      <c r="BN10" s="13"/>
-      <c r="BO10" s="13"/>
-      <c r="BP10" s="13"/>
-      <c r="BQ10" s="13"/>
-      <c r="BR10" s="13"/>
-      <c r="BS10" s="13"/>
-      <c r="BT10" s="13"/>
-      <c r="BU10" s="13"/>
-      <c r="BV10" s="19"/>
-      <c r="BW10" s="19"/>
-      <c r="BX10" s="19"/>
-      <c r="BY10" s="19"/>
-      <c r="BZ10" s="19"/>
-      <c r="CA10" s="19"/>
+      <c r="BJ10" s="17"/>
+      <c r="BK10" s="14"/>
+      <c r="BL10" s="14"/>
+      <c r="BM10" s="14"/>
+      <c r="BN10" s="14"/>
+      <c r="BO10" s="14"/>
+      <c r="BP10" s="14"/>
+      <c r="BQ10" s="14"/>
+      <c r="BR10" s="14"/>
+      <c r="BS10" s="14"/>
+      <c r="BT10" s="14"/>
+      <c r="BU10" s="14"/>
+      <c r="BV10" s="20"/>
+      <c r="BW10" s="20"/>
+      <c r="BX10" s="20"/>
+      <c r="BY10" s="20"/>
+      <c r="BZ10" s="20"/>
+      <c r="CA10" s="20"/>
     </row>
     <row r="11" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11"/>
       <c r="F11" s="8"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="11"/>
-      <c r="Z11" s="11"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="15"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
       <c r="AC11" s="8"/>
-      <c r="AD11" s="10"/>
-      <c r="AE11" s="10"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="11"/>
       <c r="AF11" s="8"/>
-      <c r="AG11" s="15"/>
-      <c r="AH11" s="12"/>
-      <c r="AI11" s="11"/>
-      <c r="AJ11" s="11"/>
-      <c r="AK11" s="12"/>
-      <c r="AL11" s="12"/>
-      <c r="AM11" s="12"/>
-      <c r="AN11" s="11"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="13"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="13"/>
+      <c r="AL11" s="13"/>
+      <c r="AM11" s="13"/>
+      <c r="AN11" s="12"/>
       <c r="AO11" s="8"/>
-      <c r="AP11" s="10"/>
-      <c r="AQ11" s="12"/>
-      <c r="AR11" s="10"/>
-      <c r="AS11" s="16"/>
-      <c r="AT11" s="17"/>
-      <c r="AU11" s="12"/>
-      <c r="AV11" s="12"/>
-      <c r="AW11" s="10"/>
-      <c r="AX11" s="16"/>
-      <c r="AY11" s="18"/>
-      <c r="AZ11" s="12"/>
-      <c r="BA11" s="12"/>
+      <c r="AP11" s="11"/>
+      <c r="AQ11" s="13"/>
+      <c r="AR11" s="11"/>
+      <c r="AS11" s="17"/>
+      <c r="AT11" s="18"/>
+      <c r="AU11" s="13"/>
+      <c r="AV11" s="13"/>
+      <c r="AW11" s="11"/>
+      <c r="AX11" s="17"/>
+      <c r="AY11" s="19"/>
+      <c r="AZ11" s="13"/>
+      <c r="BA11" s="13"/>
       <c r="BB11" s="8"/>
-      <c r="BC11" s="12"/>
-      <c r="BD11" s="16"/>
-      <c r="BE11" s="16"/>
-      <c r="BF11" s="16"/>
-      <c r="BG11" s="10"/>
-      <c r="BH11" s="10"/>
+      <c r="BC11" s="13"/>
+      <c r="BD11" s="17"/>
+      <c r="BE11" s="17"/>
+      <c r="BF11" s="17"/>
+      <c r="BG11" s="11"/>
+      <c r="BH11" s="11"/>
       <c r="BI11" s="8"/>
-      <c r="BJ11" s="16"/>
-      <c r="BK11" s="13"/>
-      <c r="BL11" s="13"/>
-      <c r="BM11" s="13"/>
-      <c r="BN11" s="13"/>
-      <c r="BO11" s="13"/>
-      <c r="BP11" s="13"/>
-      <c r="BQ11" s="13"/>
-      <c r="BR11" s="13"/>
-      <c r="BS11" s="13"/>
-      <c r="BT11" s="13"/>
-      <c r="BU11" s="13"/>
-      <c r="BV11" s="19"/>
-      <c r="BW11" s="19"/>
-      <c r="BX11" s="19"/>
-      <c r="BY11" s="19"/>
-      <c r="BZ11" s="19"/>
-      <c r="CA11" s="19"/>
+      <c r="BJ11" s="17"/>
+      <c r="BK11" s="14"/>
+      <c r="BL11" s="14"/>
+      <c r="BM11" s="14"/>
+      <c r="BN11" s="14"/>
+      <c r="BO11" s="14"/>
+      <c r="BP11" s="14"/>
+      <c r="BQ11" s="14"/>
+      <c r="BR11" s="14"/>
+      <c r="BS11" s="14"/>
+      <c r="BT11" s="14"/>
+      <c r="BU11" s="14"/>
+      <c r="BV11" s="20"/>
+      <c r="BW11" s="20"/>
+      <c r="BX11" s="20"/>
+      <c r="BY11" s="20"/>
+      <c r="BZ11" s="20"/>
+      <c r="CA11" s="20"/>
     </row>
     <row r="12" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
-      <c r="B12" s="20"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
       <c r="F12" s="8"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="12"/>
+      <c r="Z12" s="12"/>
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
       <c r="AC12" s="8"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
+      <c r="AD12" s="11"/>
+      <c r="AE12" s="11"/>
       <c r="AF12" s="8"/>
-      <c r="AG12" s="15"/>
-      <c r="AH12" s="12"/>
-      <c r="AI12" s="11"/>
-      <c r="AJ12" s="11"/>
-      <c r="AK12" s="12"/>
-      <c r="AL12" s="12"/>
-      <c r="AM12" s="12"/>
-      <c r="AN12" s="11"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="13"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="13"/>
+      <c r="AL12" s="13"/>
+      <c r="AM12" s="13"/>
+      <c r="AN12" s="12"/>
       <c r="AO12" s="8"/>
-      <c r="AP12" s="10"/>
-      <c r="AQ12" s="12"/>
-      <c r="AR12" s="10"/>
-      <c r="AS12" s="16"/>
-      <c r="AT12" s="17"/>
-      <c r="AU12" s="12"/>
-      <c r="AV12" s="12"/>
-      <c r="AW12" s="10"/>
-      <c r="AX12" s="16"/>
-      <c r="AY12" s="18"/>
-      <c r="AZ12" s="12"/>
-      <c r="BA12" s="12"/>
+      <c r="AP12" s="11"/>
+      <c r="AQ12" s="13"/>
+      <c r="AR12" s="11"/>
+      <c r="AS12" s="17"/>
+      <c r="AT12" s="18"/>
+      <c r="AU12" s="13"/>
+      <c r="AV12" s="13"/>
+      <c r="AW12" s="11"/>
+      <c r="AX12" s="17"/>
+      <c r="AY12" s="19"/>
+      <c r="AZ12" s="13"/>
+      <c r="BA12" s="13"/>
       <c r="BB12" s="8"/>
-      <c r="BC12" s="12"/>
-      <c r="BD12" s="16"/>
-      <c r="BE12" s="16"/>
-      <c r="BF12" s="16"/>
-      <c r="BG12" s="10"/>
-      <c r="BH12" s="10"/>
+      <c r="BC12" s="13"/>
+      <c r="BD12" s="17"/>
+      <c r="BE12" s="17"/>
+      <c r="BF12" s="17"/>
+      <c r="BG12" s="11"/>
+      <c r="BH12" s="11"/>
       <c r="BI12" s="8"/>
-      <c r="BJ12" s="16"/>
-      <c r="BK12" s="13"/>
-      <c r="BL12" s="13"/>
-      <c r="BM12" s="13"/>
-      <c r="BN12" s="13"/>
-      <c r="BO12" s="13"/>
-      <c r="BP12" s="13"/>
-      <c r="BQ12" s="13"/>
-      <c r="BR12" s="13"/>
-      <c r="BS12" s="13"/>
-      <c r="BT12" s="13"/>
-      <c r="BU12" s="13"/>
-      <c r="BV12" s="19"/>
-      <c r="BW12" s="19"/>
-      <c r="BX12" s="19"/>
-      <c r="BY12" s="19"/>
-      <c r="BZ12" s="19"/>
-      <c r="CA12" s="19"/>
+      <c r="BJ12" s="17"/>
+      <c r="BK12" s="14"/>
+      <c r="BL12" s="14"/>
+      <c r="BM12" s="14"/>
+      <c r="BN12" s="14"/>
+      <c r="BO12" s="14"/>
+      <c r="BP12" s="14"/>
+      <c r="BQ12" s="14"/>
+      <c r="BR12" s="14"/>
+      <c r="BS12" s="14"/>
+      <c r="BT12" s="14"/>
+      <c r="BU12" s="14"/>
+      <c r="BV12" s="20"/>
+      <c r="BW12" s="20"/>
+      <c r="BX12" s="20"/>
+      <c r="BY12" s="20"/>
+      <c r="BZ12" s="20"/>
+      <c r="CA12" s="20"/>
     </row>
     <row r="13" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
-      <c r="B13" s="20"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
       <c r="F13" s="8"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="11"/>
-      <c r="Z13" s="11"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="15"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
       <c r="AC13" s="8"/>
-      <c r="AD13" s="10"/>
-      <c r="AE13" s="10"/>
+      <c r="AD13" s="11"/>
+      <c r="AE13" s="11"/>
       <c r="AF13" s="8"/>
-      <c r="AG13" s="15"/>
-      <c r="AH13" s="12"/>
-      <c r="AI13" s="11"/>
-      <c r="AJ13" s="11"/>
-      <c r="AK13" s="12"/>
-      <c r="AL13" s="12"/>
-      <c r="AM13" s="12"/>
-      <c r="AN13" s="11"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="13"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="13"/>
+      <c r="AL13" s="13"/>
+      <c r="AM13" s="13"/>
+      <c r="AN13" s="12"/>
       <c r="AO13" s="8"/>
-      <c r="AP13" s="10"/>
-      <c r="AQ13" s="12"/>
-      <c r="AR13" s="10"/>
-      <c r="AS13" s="16"/>
-      <c r="AT13" s="17"/>
-      <c r="AU13" s="12"/>
-      <c r="AV13" s="12"/>
-      <c r="AW13" s="10"/>
-      <c r="AX13" s="16"/>
-      <c r="AY13" s="18"/>
-      <c r="AZ13" s="12"/>
-      <c r="BA13" s="12"/>
+      <c r="AP13" s="11"/>
+      <c r="AQ13" s="13"/>
+      <c r="AR13" s="11"/>
+      <c r="AS13" s="17"/>
+      <c r="AT13" s="18"/>
+      <c r="AU13" s="13"/>
+      <c r="AV13" s="13"/>
+      <c r="AW13" s="11"/>
+      <c r="AX13" s="17"/>
+      <c r="AY13" s="19"/>
+      <c r="AZ13" s="13"/>
+      <c r="BA13" s="13"/>
       <c r="BB13" s="8"/>
-      <c r="BC13" s="12"/>
-      <c r="BD13" s="16"/>
-      <c r="BE13" s="16"/>
-      <c r="BF13" s="16"/>
-      <c r="BG13" s="10"/>
-      <c r="BH13" s="10"/>
+      <c r="BC13" s="13"/>
+      <c r="BD13" s="17"/>
+      <c r="BE13" s="17"/>
+      <c r="BF13" s="17"/>
+      <c r="BG13" s="11"/>
+      <c r="BH13" s="11"/>
       <c r="BI13" s="8"/>
-      <c r="BJ13" s="16"/>
-      <c r="BK13" s="13"/>
-      <c r="BL13" s="13"/>
-      <c r="BM13" s="13"/>
-      <c r="BN13" s="13"/>
-      <c r="BO13" s="13"/>
-      <c r="BP13" s="13"/>
-      <c r="BQ13" s="13"/>
-      <c r="BR13" s="13"/>
-      <c r="BS13" s="13"/>
-      <c r="BT13" s="13"/>
-      <c r="BU13" s="13"/>
-      <c r="BV13" s="19"/>
-      <c r="BW13" s="19"/>
-      <c r="BX13" s="19"/>
-      <c r="BY13" s="19"/>
-      <c r="BZ13" s="19"/>
-      <c r="CA13" s="19"/>
+      <c r="BJ13" s="17"/>
+      <c r="BK13" s="14"/>
+      <c r="BL13" s="14"/>
+      <c r="BM13" s="14"/>
+      <c r="BN13" s="14"/>
+      <c r="BO13" s="14"/>
+      <c r="BP13" s="14"/>
+      <c r="BQ13" s="14"/>
+      <c r="BR13" s="14"/>
+      <c r="BS13" s="14"/>
+      <c r="BT13" s="14"/>
+      <c r="BU13" s="14"/>
+      <c r="BV13" s="20"/>
+      <c r="BW13" s="20"/>
+      <c r="BX13" s="20"/>
+      <c r="BY13" s="20"/>
+      <c r="BZ13" s="20"/>
+      <c r="CA13" s="20"/>
     </row>
     <row r="14" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
-      <c r="B14" s="20"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
       <c r="F14" s="8"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="11"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="12"/>
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
       <c r="AC14" s="8"/>
-      <c r="AD14" s="10"/>
-      <c r="AE14" s="10"/>
+      <c r="AD14" s="11"/>
+      <c r="AE14" s="11"/>
       <c r="AF14" s="8"/>
-      <c r="AG14" s="15"/>
-      <c r="AH14" s="12"/>
-      <c r="AI14" s="11"/>
-      <c r="AJ14" s="11"/>
-      <c r="AK14" s="12"/>
-      <c r="AL14" s="12"/>
-      <c r="AM14" s="12"/>
-      <c r="AN14" s="11"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="13"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="13"/>
+      <c r="AL14" s="13"/>
+      <c r="AM14" s="13"/>
+      <c r="AN14" s="12"/>
       <c r="AO14" s="8"/>
-      <c r="AP14" s="10"/>
-      <c r="AQ14" s="12"/>
-      <c r="AR14" s="10"/>
-      <c r="AS14" s="16"/>
-      <c r="AT14" s="17"/>
-      <c r="AU14" s="12"/>
-      <c r="AV14" s="12"/>
-      <c r="AW14" s="10"/>
-      <c r="AX14" s="16"/>
-      <c r="AY14" s="18"/>
-      <c r="AZ14" s="12"/>
-      <c r="BA14" s="12"/>
+      <c r="AP14" s="11"/>
+      <c r="AQ14" s="13"/>
+      <c r="AR14" s="11"/>
+      <c r="AS14" s="17"/>
+      <c r="AT14" s="18"/>
+      <c r="AU14" s="13"/>
+      <c r="AV14" s="13"/>
+      <c r="AW14" s="11"/>
+      <c r="AX14" s="17"/>
+      <c r="AY14" s="19"/>
+      <c r="AZ14" s="13"/>
+      <c r="BA14" s="13"/>
       <c r="BB14" s="8"/>
-      <c r="BC14" s="12"/>
-      <c r="BD14" s="16"/>
-      <c r="BE14" s="16"/>
-      <c r="BF14" s="16"/>
-      <c r="BG14" s="10"/>
-      <c r="BH14" s="10"/>
+      <c r="BC14" s="13"/>
+      <c r="BD14" s="17"/>
+      <c r="BE14" s="17"/>
+      <c r="BF14" s="17"/>
+      <c r="BG14" s="11"/>
+      <c r="BH14" s="11"/>
       <c r="BI14" s="8"/>
-      <c r="BJ14" s="16"/>
-      <c r="BK14" s="13"/>
-      <c r="BL14" s="13"/>
-      <c r="BM14" s="13"/>
-      <c r="BN14" s="13"/>
-      <c r="BO14" s="13"/>
-      <c r="BP14" s="13"/>
-      <c r="BQ14" s="13"/>
-      <c r="BR14" s="13"/>
-      <c r="BS14" s="13"/>
-      <c r="BT14" s="13"/>
-      <c r="BU14" s="13"/>
-      <c r="BV14" s="19"/>
-      <c r="BW14" s="19"/>
-      <c r="BX14" s="19"/>
-      <c r="BY14" s="19"/>
-      <c r="BZ14" s="19"/>
-      <c r="CA14" s="19"/>
+      <c r="BJ14" s="17"/>
+      <c r="BK14" s="14"/>
+      <c r="BL14" s="14"/>
+      <c r="BM14" s="14"/>
+      <c r="BN14" s="14"/>
+      <c r="BO14" s="14"/>
+      <c r="BP14" s="14"/>
+      <c r="BQ14" s="14"/>
+      <c r="BR14" s="14"/>
+      <c r="BS14" s="14"/>
+      <c r="BT14" s="14"/>
+      <c r="BU14" s="14"/>
+      <c r="BV14" s="20"/>
+      <c r="BW14" s="20"/>
+      <c r="BX14" s="20"/>
+      <c r="BY14" s="20"/>
+      <c r="BZ14" s="20"/>
+      <c r="CA14" s="20"/>
     </row>
     <row r="15" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="21"/>
+      <c r="B15" s="9"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
       <c r="F15" s="8"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="12"/>
-      <c r="Y15" s="11"/>
-      <c r="Z15" s="11"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="13"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
       <c r="AC15" s="8"/>
-      <c r="AD15" s="10"/>
-      <c r="AE15" s="10"/>
+      <c r="AD15" s="11"/>
+      <c r="AE15" s="11"/>
       <c r="AF15" s="8"/>
-      <c r="AG15" s="15"/>
-      <c r="AH15" s="12"/>
-      <c r="AI15" s="11"/>
-      <c r="AJ15" s="11"/>
-      <c r="AK15" s="12"/>
-      <c r="AL15" s="12"/>
-      <c r="AM15" s="12"/>
-      <c r="AN15" s="11"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="13"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="13"/>
+      <c r="AL15" s="13"/>
+      <c r="AM15" s="13"/>
+      <c r="AN15" s="12"/>
       <c r="AO15" s="8"/>
-      <c r="AP15" s="10"/>
-      <c r="AQ15" s="12"/>
-      <c r="AR15" s="10"/>
-      <c r="AS15" s="16"/>
-      <c r="AT15" s="17"/>
-      <c r="AU15" s="12"/>
-      <c r="AV15" s="12"/>
-      <c r="AW15" s="10"/>
-      <c r="AX15" s="16"/>
-      <c r="AY15" s="18"/>
-      <c r="AZ15" s="12"/>
-      <c r="BA15" s="12"/>
+      <c r="AP15" s="11"/>
+      <c r="AQ15" s="13"/>
+      <c r="AR15" s="11"/>
+      <c r="AS15" s="17"/>
+      <c r="AT15" s="18"/>
+      <c r="AU15" s="13"/>
+      <c r="AV15" s="13"/>
+      <c r="AW15" s="11"/>
+      <c r="AX15" s="17"/>
+      <c r="AY15" s="19"/>
+      <c r="AZ15" s="13"/>
+      <c r="BA15" s="13"/>
       <c r="BB15" s="8"/>
-      <c r="BC15" s="12"/>
-      <c r="BD15" s="16"/>
-      <c r="BE15" s="16"/>
-      <c r="BF15" s="16"/>
-      <c r="BG15" s="10"/>
-      <c r="BH15" s="10"/>
+      <c r="BC15" s="13"/>
+      <c r="BD15" s="17"/>
+      <c r="BE15" s="17"/>
+      <c r="BF15" s="17"/>
+      <c r="BG15" s="11"/>
+      <c r="BH15" s="11"/>
       <c r="BI15" s="8"/>
-      <c r="BJ15" s="16"/>
-      <c r="BK15" s="13"/>
-      <c r="BL15" s="13"/>
-      <c r="BM15" s="13"/>
-      <c r="BN15" s="13"/>
-      <c r="BO15" s="13"/>
-      <c r="BP15" s="13"/>
-      <c r="BQ15" s="13"/>
-      <c r="BR15" s="13"/>
-      <c r="BS15" s="13"/>
-      <c r="BT15" s="13"/>
-      <c r="BU15" s="13"/>
-      <c r="BV15" s="19"/>
-      <c r="BW15" s="19"/>
-      <c r="BX15" s="19"/>
-      <c r="BY15" s="19"/>
-      <c r="BZ15" s="19"/>
-      <c r="CA15" s="19"/>
+      <c r="BJ15" s="17"/>
+      <c r="BK15" s="14"/>
+      <c r="BL15" s="14"/>
+      <c r="BM15" s="14"/>
+      <c r="BN15" s="14"/>
+      <c r="BO15" s="14"/>
+      <c r="BP15" s="14"/>
+      <c r="BQ15" s="14"/>
+      <c r="BR15" s="14"/>
+      <c r="BS15" s="14"/>
+      <c r="BT15" s="14"/>
+      <c r="BU15" s="14"/>
+      <c r="BV15" s="20"/>
+      <c r="BW15" s="20"/>
+      <c r="BX15" s="20"/>
+      <c r="BY15" s="20"/>
+      <c r="BZ15" s="20"/>
+      <c r="CA15" s="20"/>
     </row>
     <row r="16" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
-      <c r="B16" s="21"/>
+      <c r="B16" s="9"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="11"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="11"/>
-      <c r="Z16" s="11"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="13"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="12"/>
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
       <c r="AC16" s="8"/>
-      <c r="AD16" s="10"/>
-      <c r="AE16" s="10"/>
+      <c r="AD16" s="11"/>
+      <c r="AE16" s="11"/>
       <c r="AF16" s="8"/>
-      <c r="AG16" s="15"/>
-      <c r="AH16" s="12"/>
-      <c r="AI16" s="11"/>
-      <c r="AJ16" s="11"/>
-      <c r="AK16" s="12"/>
-      <c r="AL16" s="12"/>
-      <c r="AM16" s="12"/>
-      <c r="AN16" s="11"/>
+      <c r="AG16" s="16"/>
+      <c r="AH16" s="13"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="13"/>
+      <c r="AL16" s="13"/>
+      <c r="AM16" s="13"/>
+      <c r="AN16" s="12"/>
       <c r="AO16" s="8"/>
-      <c r="AP16" s="10"/>
-      <c r="AQ16" s="12"/>
-      <c r="AR16" s="10"/>
-      <c r="AS16" s="16"/>
-      <c r="AT16" s="17"/>
-      <c r="AU16" s="12"/>
-      <c r="AV16" s="12"/>
-      <c r="AW16" s="10"/>
-      <c r="AX16" s="16"/>
-      <c r="AY16" s="18"/>
-      <c r="AZ16" s="12"/>
-      <c r="BA16" s="12"/>
+      <c r="AP16" s="11"/>
+      <c r="AQ16" s="13"/>
+      <c r="AR16" s="11"/>
+      <c r="AS16" s="17"/>
+      <c r="AT16" s="18"/>
+      <c r="AU16" s="13"/>
+      <c r="AV16" s="13"/>
+      <c r="AW16" s="11"/>
+      <c r="AX16" s="17"/>
+      <c r="AY16" s="19"/>
+      <c r="AZ16" s="13"/>
+      <c r="BA16" s="13"/>
       <c r="BB16" s="8"/>
-      <c r="BC16" s="12"/>
-      <c r="BD16" s="16"/>
-      <c r="BE16" s="16"/>
-      <c r="BF16" s="16"/>
-      <c r="BG16" s="10"/>
-      <c r="BH16" s="10"/>
+      <c r="BC16" s="13"/>
+      <c r="BD16" s="17"/>
+      <c r="BE16" s="17"/>
+      <c r="BF16" s="17"/>
+      <c r="BG16" s="11"/>
+      <c r="BH16" s="11"/>
       <c r="BI16" s="8"/>
-      <c r="BJ16" s="16"/>
-      <c r="BK16" s="13"/>
-      <c r="BL16" s="13"/>
-      <c r="BM16" s="13"/>
-      <c r="BN16" s="13"/>
-      <c r="BO16" s="13"/>
-      <c r="BP16" s="13"/>
-      <c r="BQ16" s="13"/>
-      <c r="BR16" s="13"/>
-      <c r="BS16" s="13"/>
-      <c r="BT16" s="13"/>
-      <c r="BU16" s="13"/>
-      <c r="BV16" s="19"/>
-      <c r="BW16" s="19"/>
-      <c r="BX16" s="19"/>
-      <c r="BY16" s="19"/>
-      <c r="BZ16" s="19"/>
-      <c r="CA16" s="19"/>
+      <c r="BJ16" s="17"/>
+      <c r="BK16" s="14"/>
+      <c r="BL16" s="14"/>
+      <c r="BM16" s="14"/>
+      <c r="BN16" s="14"/>
+      <c r="BO16" s="14"/>
+      <c r="BP16" s="14"/>
+      <c r="BQ16" s="14"/>
+      <c r="BR16" s="14"/>
+      <c r="BS16" s="14"/>
+      <c r="BT16" s="14"/>
+      <c r="BU16" s="14"/>
+      <c r="BV16" s="20"/>
+      <c r="BW16" s="20"/>
+      <c r="BX16" s="20"/>
+      <c r="BY16" s="20"/>
+      <c r="BZ16" s="20"/>
+      <c r="CA16" s="20"/>
     </row>
     <row r="17" spans="46:51" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AT17" s="18"/>
-      <c r="AY17" s="18"/>
+      <c r="AT17" s="19"/>
+      <c r="AY17" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="4">

--- a/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -1,15 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{D0219ECA-2E18-4FF5-8349-A34ADB6F7FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -244,7 +259,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699518</t>
+    <t>10699601</t>
   </si>
   <si>
     <t>Passed</t>
@@ -256,10 +271,10 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>Virgil</t>
-  </si>
-  <si>
-    <t>Walker</t>
+    <t>Lavada</t>
+  </si>
+  <si>
+    <t>Parisian</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -397,22 +412,22 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699519</t>
+    <t>10699602</t>
   </si>
   <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>Garnet</t>
-  </si>
-  <si>
-    <t>Kunde</t>
+    <t>Erick</t>
+  </si>
+  <si>
+    <t>Morissette</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 96981989</t>
+    <t>Auto 20091358</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -448,57 +463,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
-      <family val="2"/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -507,7 +522,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.7999816888943144"/>
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,11 +545,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -552,23 +562,35 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -586,9 +608,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -602,7 +621,7 @@
     <xf numFmtId="14" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
@@ -624,9 +643,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -906,10 +922,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CN17"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:CN4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="109.7265625" style="1" customWidth="1"/>
@@ -990,10 +1006,11 @@
     <col min="77" max="77" width="15" style="1" customWidth="1"/>
     <col min="78" max="78" width="33.6328125" style="1" customWidth="1"/>
     <col min="79" max="79" width="26.90625" style="1" customWidth="1"/>
-    <col min="80" max="16384" width="8.90625" style="1" customWidth="1"/>
+    <col min="80" max="80" width="8.90625" style="1" customWidth="1"/>
+    <col min="81" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:92" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1245,84 +1262,84 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>76</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>79</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="12">
         <v>45597</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="10">
         <v>1</v>
       </c>
-      <c r="O2" s="14">
+      <c r="O2" s="13">
         <v>213111231</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="V2" s="15" t="s">
+      <c r="V2" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="13">
+      <c r="X2" s="12">
         <f t="shared" ref="X2:X3" si="0">K2</f>
         <v>45597</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Y2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="Z2" s="11" t="s">
         <v>92</v>
       </c>
       <c r="AA2" s="8" t="s">
@@ -1334,239 +1351,239 @@
       <c r="AC2" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AD2" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="AE2" s="10" t="s">
         <v>97</v>
       </c>
       <c r="AF2" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AG2" s="16">
+      <c r="AG2" s="15">
         <v>20</v>
       </c>
-      <c r="AH2" s="13" t="s">
+      <c r="AH2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="AI2" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="AJ2" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK2" s="13">
+      <c r="AK2" s="12" t="str">
         <f t="shared" ref="AK2:AK3" si="1">AH2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AL2" s="13">
+        <v>N/A</v>
+      </c>
+      <c r="AL2" s="12">
         <f t="shared" ref="AL2:AL3" si="2">K2</f>
         <v>45597</v>
       </c>
-      <c r="AM2" s="13">
+      <c r="AM2" s="12">
         <f t="shared" ref="AM2:AM3" si="3">K2</f>
         <v>45597</v>
       </c>
-      <c r="AN2" s="12" t="s">
+      <c r="AN2" s="11" t="s">
         <v>102</v>
       </c>
       <c r="AO2" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="AP2" s="11">
+      <c r="AP2" s="10">
         <v>100</v>
       </c>
-      <c r="AQ2" s="13">
+      <c r="AQ2" s="12">
         <f t="shared" ref="AQ2:AQ3" si="4">K2+90</f>
         <v>45687</v>
       </c>
-      <c r="AR2" s="11" t="s">
+      <c r="AR2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AS2" s="17" t="s">
+      <c r="AS2" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="18">
-        <v>9461110901</v>
-      </c>
-      <c r="AU2" s="13" t="s">
+      <c r="AT2" s="17">
+        <v>9461110905</v>
+      </c>
+      <c r="AU2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AV2" s="13" t="s">
+      <c r="AV2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AW2" s="11" t="s">
+      <c r="AW2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AX2" s="17" t="s">
+      <c r="AX2" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="AY2" s="19">
-        <v>142743099</v>
-      </c>
-      <c r="AZ2" s="13" t="s">
+      <c r="AY2" s="18">
+        <v>152733405</v>
+      </c>
+      <c r="AZ2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="BA2" s="13" t="s">
+      <c r="BA2" s="12" t="s">
         <v>106</v>
       </c>
       <c r="BB2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="BC2" s="13">
+      <c r="BC2" s="12">
         <v>34284</v>
       </c>
-      <c r="BD2" s="17" t="s">
+      <c r="BD2" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="BE2" s="17" t="s">
+      <c r="BE2" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="17" t="s">
+      <c r="BF2" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="BG2" s="11" t="s">
+      <c r="BG2" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="11" t="s">
+      <c r="BH2" s="10" t="s">
         <v>112</v>
       </c>
       <c r="BI2" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="BJ2" s="17" t="s">
+      <c r="BJ2" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BK2" s="14" t="s">
+      <c r="BK2" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="BL2" s="14" t="s">
+      <c r="BL2" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="BM2" s="14" t="s">
+      <c r="BM2" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="BN2" s="14" t="s">
+      <c r="BN2" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="BO2" s="14">
+      <c r="BO2" s="13">
         <v>2024</v>
       </c>
-      <c r="BP2" s="14" t="s">
+      <c r="BP2" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="BQ2" s="14">
+      <c r="BQ2" s="13">
         <v>2021</v>
       </c>
-      <c r="BR2" s="14">
+      <c r="BR2" s="13">
         <v>2024</v>
       </c>
-      <c r="BS2" s="14" t="s">
+      <c r="BS2" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="14" t="s">
+      <c r="BT2" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="BU2" s="14" t="s">
+      <c r="BU2" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="BV2" s="20" t="s">
+      <c r="BV2" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="BW2" s="20" t="s">
+      <c r="BW2" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="BX2" s="20">
+      <c r="BX2" s="19">
         <v>213</v>
       </c>
-      <c r="BY2" s="20" t="s">
+      <c r="BY2" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="BZ2" s="20" t="s">
+      <c r="BZ2" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="CA2" s="20" t="s">
+      <c r="CA2" s="19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>127</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>79</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="12">
         <v>45597</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="10">
         <v>1</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="13">
         <v>213111231</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="T3" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="U3" s="13" t="s">
+      <c r="U3" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="V3" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="W3" s="12" t="s">
+      <c r="W3" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="X3" s="13">
+      <c r="X3" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
-      <c r="Y3" s="12" t="s">
+      <c r="Y3" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="Z3" s="12" t="s">
+      <c r="Z3" s="11" t="s">
         <v>132</v>
       </c>
       <c r="AA3" s="8" t="s">
@@ -1578,1258 +1595,175 @@
       <c r="AC3" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="AD3" s="11" t="s">
+      <c r="AD3" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AE3" s="11" t="s">
+      <c r="AE3" s="10" t="s">
         <v>97</v>
       </c>
       <c r="AF3" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="AG3" s="16">
+      <c r="AG3" s="15">
         <v>40</v>
       </c>
-      <c r="AH3" s="13" t="s">
+      <c r="AH3" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AI3" s="12" t="s">
+      <c r="AI3" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AJ3" s="12" t="s">
+      <c r="AJ3" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK3" s="13">
+      <c r="AK3" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>NaN</v>
-      </c>
-      <c r="AL3" s="13">
+        <v>N/A</v>
+      </c>
+      <c r="AL3" s="12">
         <f t="shared" si="2"/>
         <v>45597</v>
       </c>
-      <c r="AM3" s="13">
+      <c r="AM3" s="12">
         <f t="shared" si="3"/>
         <v>45597</v>
       </c>
-      <c r="AN3" s="12" t="s">
+      <c r="AN3" s="11" t="s">
         <v>136</v>
       </c>
       <c r="AO3" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="AP3" s="11">
+      <c r="AP3" s="10">
         <v>100</v>
       </c>
-      <c r="AQ3" s="13">
+      <c r="AQ3" s="12">
         <f t="shared" si="4"/>
         <v>45687</v>
       </c>
-      <c r="AR3" s="11" t="s">
+      <c r="AR3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AS3" s="17" t="s">
+      <c r="AS3" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="AT3" s="18">
-        <v>9461110902</v>
-      </c>
-      <c r="AU3" s="13" t="s">
+      <c r="AT3" s="17">
+        <v>9461110906</v>
+      </c>
+      <c r="AU3" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AV3" s="13" t="s">
+      <c r="AV3" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AW3" s="11" t="s">
+      <c r="AW3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AX3" s="17" t="s">
+      <c r="AX3" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="AY3" s="19">
-        <v>152733400</v>
-      </c>
-      <c r="AZ3" s="13" t="s">
+      <c r="AY3" s="18">
+        <v>152733406</v>
+      </c>
+      <c r="AZ3" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="BA3" s="13" t="s">
+      <c r="BA3" s="12" t="s">
         <v>106</v>
       </c>
       <c r="BB3" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="BC3" s="13">
+      <c r="BC3" s="12">
         <v>34284</v>
       </c>
-      <c r="BD3" s="17" t="s">
+      <c r="BD3" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="BE3" s="17" t="s">
+      <c r="BE3" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="BF3" s="17" t="s">
+      <c r="BF3" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="BG3" s="11" t="s">
+      <c r="BG3" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="BH3" s="11" t="s">
+      <c r="BH3" s="10" t="s">
         <v>112</v>
       </c>
       <c r="BI3" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="BJ3" s="17" t="s">
+      <c r="BJ3" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BK3" s="14" t="s">
+      <c r="BK3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="BL3" s="14" t="s">
+      <c r="BL3" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="BM3" s="14" t="s">
+      <c r="BM3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="BN3" s="14" t="s">
+      <c r="BN3" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="BO3" s="14">
+      <c r="BO3" s="13">
         <v>2000</v>
       </c>
-      <c r="BP3" s="14" t="s">
+      <c r="BP3" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="BQ3" s="14">
+      <c r="BQ3" s="13">
         <v>1995</v>
       </c>
-      <c r="BR3" s="14">
+      <c r="BR3" s="13">
         <v>2000</v>
       </c>
-      <c r="BS3" s="14" t="s">
+      <c r="BS3" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="BT3" s="14" t="s">
+      <c r="BT3" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="BU3" s="14" t="s">
+      <c r="BU3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="BV3" s="20" t="s">
+      <c r="BV3" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="BW3" s="20" t="s">
+      <c r="BW3" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="BX3" s="20">
+      <c r="BX3" s="19">
         <v>201</v>
       </c>
-      <c r="BY3" s="20" t="s">
+      <c r="BY3" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="BZ3" s="20" t="s">
+      <c r="BZ3" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="CA3" s="20" t="s">
+      <c r="CA3" s="19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="8"/>
-      <c r="AD4" s="11"/>
-      <c r="AE4" s="11"/>
-      <c r="AF4" s="8"/>
-      <c r="AG4" s="16"/>
-      <c r="AH4" s="13"/>
-      <c r="AI4" s="12"/>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="13"/>
-      <c r="AL4" s="13"/>
-      <c r="AM4" s="13"/>
-      <c r="AN4" s="12"/>
-      <c r="AO4" s="8"/>
-      <c r="AP4" s="11"/>
-      <c r="AQ4" s="13"/>
-      <c r="AR4" s="11"/>
-      <c r="AS4" s="17"/>
+    <row r="4" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AT4" s="18"/>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="13"/>
-      <c r="AW4" s="11"/>
-      <c r="AX4" s="17"/>
-      <c r="AY4" s="19"/>
-      <c r="AZ4" s="13"/>
-      <c r="BA4" s="13"/>
-      <c r="BB4" s="8"/>
-      <c r="BC4" s="13"/>
-      <c r="BD4" s="17"/>
-      <c r="BE4" s="17"/>
-      <c r="BF4" s="17"/>
-      <c r="BG4" s="11"/>
-      <c r="BH4" s="11"/>
-      <c r="BI4" s="8"/>
-      <c r="BJ4" s="17"/>
-      <c r="BK4" s="14"/>
-      <c r="BL4" s="14"/>
-      <c r="BM4" s="14"/>
-      <c r="BN4" s="14"/>
-      <c r="BO4" s="14"/>
-      <c r="BP4" s="14"/>
-      <c r="BQ4" s="14"/>
-      <c r="BR4" s="14"/>
-      <c r="BS4" s="14"/>
-      <c r="BT4" s="14"/>
-      <c r="BU4" s="14"/>
-      <c r="BV4" s="20"/>
-      <c r="BW4" s="20"/>
-      <c r="BX4" s="20"/>
-      <c r="BY4" s="20"/>
-      <c r="BZ4" s="20"/>
-      <c r="CA4" s="20"/>
-    </row>
-    <row r="5" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="8"/>
-      <c r="AB5" s="8"/>
-      <c r="AC5" s="8"/>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="8"/>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="13"/>
-      <c r="AI5" s="12"/>
-      <c r="AJ5" s="12"/>
-      <c r="AK5" s="13"/>
-      <c r="AL5" s="13"/>
-      <c r="AM5" s="13"/>
-      <c r="AN5" s="12"/>
-      <c r="AO5" s="8"/>
-      <c r="AP5" s="11"/>
-      <c r="AQ5" s="13"/>
-      <c r="AR5" s="11"/>
-      <c r="AS5" s="17"/>
-      <c r="AT5" s="18"/>
-      <c r="AU5" s="13"/>
-      <c r="AV5" s="13"/>
-      <c r="AW5" s="11"/>
-      <c r="AX5" s="17"/>
-      <c r="AY5" s="19"/>
-      <c r="AZ5" s="13"/>
-      <c r="BA5" s="13"/>
-      <c r="BB5" s="8"/>
-      <c r="BC5" s="13"/>
-      <c r="BD5" s="17"/>
-      <c r="BE5" s="17"/>
-      <c r="BF5" s="17"/>
-      <c r="BG5" s="11"/>
-      <c r="BH5" s="11"/>
-      <c r="BI5" s="8"/>
-      <c r="BJ5" s="17"/>
-      <c r="BK5" s="14"/>
-      <c r="BL5" s="14"/>
-      <c r="BM5" s="14"/>
-      <c r="BN5" s="14"/>
-      <c r="BO5" s="14"/>
-      <c r="BP5" s="14"/>
-      <c r="BQ5" s="14"/>
-      <c r="BR5" s="14"/>
-      <c r="BS5" s="14"/>
-      <c r="BT5" s="14"/>
-      <c r="BU5" s="14"/>
-      <c r="BV5" s="20"/>
-      <c r="BW5" s="20"/>
-      <c r="BX5" s="20"/>
-      <c r="BY5" s="20"/>
-      <c r="BZ5" s="20"/>
-      <c r="CA5" s="20"/>
-    </row>
-    <row r="6" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="11"/>
-      <c r="AF6" s="8"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="12"/>
-      <c r="AJ6" s="12"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="8"/>
-      <c r="AP6" s="11"/>
-      <c r="AQ6" s="13"/>
-      <c r="AR6" s="11"/>
-      <c r="AS6" s="17"/>
-      <c r="AT6" s="18"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="11"/>
-      <c r="AX6" s="17"/>
-      <c r="AY6" s="19"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="13"/>
-      <c r="BB6" s="8"/>
-      <c r="BC6" s="13"/>
-      <c r="BD6" s="17"/>
-      <c r="BE6" s="17"/>
-      <c r="BF6" s="17"/>
-      <c r="BG6" s="11"/>
-      <c r="BH6" s="11"/>
-      <c r="BI6" s="8"/>
-      <c r="BJ6" s="17"/>
-      <c r="BK6" s="14"/>
-      <c r="BL6" s="14"/>
-      <c r="BM6" s="14"/>
-      <c r="BN6" s="14"/>
-      <c r="BO6" s="14"/>
-      <c r="BP6" s="14"/>
-      <c r="BQ6" s="14"/>
-      <c r="BR6" s="14"/>
-      <c r="BS6" s="14"/>
-      <c r="BT6" s="14"/>
-      <c r="BU6" s="14"/>
-      <c r="BV6" s="20"/>
-      <c r="BW6" s="20"/>
-      <c r="BX6" s="20"/>
-      <c r="BY6" s="20"/>
-      <c r="BZ6" s="20"/>
-      <c r="CA6" s="20"/>
-    </row>
-    <row r="7" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="8"/>
-      <c r="AG7" s="16"/>
-      <c r="AH7" s="13"/>
-      <c r="AI7" s="12"/>
-      <c r="AJ7" s="12"/>
-      <c r="AK7" s="13"/>
-      <c r="AL7" s="13"/>
-      <c r="AM7" s="13"/>
-      <c r="AN7" s="12"/>
-      <c r="AO7" s="8"/>
-      <c r="AP7" s="11"/>
-      <c r="AQ7" s="13"/>
-      <c r="AR7" s="11"/>
-      <c r="AS7" s="17"/>
-      <c r="AT7" s="18"/>
-      <c r="AU7" s="13"/>
-      <c r="AV7" s="13"/>
-      <c r="AW7" s="11"/>
-      <c r="AX7" s="17"/>
-      <c r="AY7" s="19"/>
-      <c r="AZ7" s="13"/>
-      <c r="BA7" s="13"/>
-      <c r="BB7" s="8"/>
-      <c r="BC7" s="13"/>
-      <c r="BD7" s="17"/>
-      <c r="BE7" s="17"/>
-      <c r="BF7" s="17"/>
-      <c r="BG7" s="11"/>
-      <c r="BH7" s="11"/>
-      <c r="BI7" s="8"/>
-      <c r="BJ7" s="17"/>
-      <c r="BK7" s="14"/>
-      <c r="BL7" s="14"/>
-      <c r="BM7" s="14"/>
-      <c r="BN7" s="14"/>
-      <c r="BO7" s="14"/>
-      <c r="BP7" s="14"/>
-      <c r="BQ7" s="14"/>
-      <c r="BR7" s="14"/>
-      <c r="BS7" s="14"/>
-      <c r="BT7" s="14"/>
-      <c r="BU7" s="14"/>
-      <c r="BV7" s="20"/>
-      <c r="BW7" s="20"/>
-      <c r="BX7" s="20"/>
-      <c r="BY7" s="20"/>
-      <c r="BZ7" s="20"/>
-      <c r="CA7" s="20"/>
-    </row>
-    <row r="8" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="8"/>
-      <c r="AG8" s="16"/>
-      <c r="AH8" s="13"/>
-      <c r="AI8" s="12"/>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="13"/>
-      <c r="AL8" s="13"/>
-      <c r="AM8" s="13"/>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="8"/>
-      <c r="AP8" s="11"/>
-      <c r="AQ8" s="13"/>
-      <c r="AR8" s="11"/>
-      <c r="AS8" s="17"/>
-      <c r="AT8" s="18"/>
-      <c r="AU8" s="13"/>
-      <c r="AV8" s="13"/>
-      <c r="AW8" s="11"/>
-      <c r="AX8" s="17"/>
-      <c r="AY8" s="19"/>
-      <c r="AZ8" s="13"/>
-      <c r="BA8" s="13"/>
-      <c r="BB8" s="8"/>
-      <c r="BC8" s="13"/>
-      <c r="BD8" s="17"/>
-      <c r="BE8" s="17"/>
-      <c r="BF8" s="17"/>
-      <c r="BG8" s="11"/>
-      <c r="BH8" s="11"/>
-      <c r="BI8" s="8"/>
-      <c r="BJ8" s="17"/>
-      <c r="BK8" s="14"/>
-      <c r="BL8" s="14"/>
-      <c r="BM8" s="14"/>
-      <c r="BN8" s="14"/>
-      <c r="BO8" s="14"/>
-      <c r="BP8" s="14"/>
-      <c r="BQ8" s="14"/>
-      <c r="BR8" s="14"/>
-      <c r="BS8" s="14"/>
-      <c r="BT8" s="14"/>
-      <c r="BU8" s="14"/>
-      <c r="BV8" s="20"/>
-      <c r="BW8" s="20"/>
-      <c r="BX8" s="20"/>
-      <c r="BY8" s="20"/>
-      <c r="BZ8" s="20"/>
-      <c r="CA8" s="20"/>
-    </row>
-    <row r="9" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="12"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="8"/>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="13"/>
-      <c r="AI9" s="12"/>
-      <c r="AJ9" s="12"/>
-      <c r="AK9" s="13"/>
-      <c r="AL9" s="13"/>
-      <c r="AM9" s="13"/>
-      <c r="AN9" s="12"/>
-      <c r="AO9" s="8"/>
-      <c r="AP9" s="11"/>
-      <c r="AQ9" s="13"/>
-      <c r="AR9" s="11"/>
-      <c r="AS9" s="17"/>
-      <c r="AT9" s="18"/>
-      <c r="AU9" s="13"/>
-      <c r="AV9" s="13"/>
-      <c r="AW9" s="11"/>
-      <c r="AX9" s="17"/>
-      <c r="AY9" s="19"/>
-      <c r="AZ9" s="13"/>
-      <c r="BA9" s="13"/>
-      <c r="BB9" s="8"/>
-      <c r="BC9" s="13"/>
-      <c r="BD9" s="17"/>
-      <c r="BE9" s="17"/>
-      <c r="BF9" s="17"/>
-      <c r="BG9" s="11"/>
-      <c r="BH9" s="11"/>
-      <c r="BI9" s="8"/>
-      <c r="BJ9" s="17"/>
-      <c r="BK9" s="14"/>
-      <c r="BL9" s="14"/>
-      <c r="BM9" s="14"/>
-      <c r="BN9" s="14"/>
-      <c r="BO9" s="14"/>
-      <c r="BP9" s="14"/>
-      <c r="BQ9" s="14"/>
-      <c r="BR9" s="14"/>
-      <c r="BS9" s="14"/>
-      <c r="BT9" s="14"/>
-      <c r="BU9" s="14"/>
-      <c r="BV9" s="20"/>
-      <c r="BW9" s="20"/>
-      <c r="BX9" s="20"/>
-      <c r="BY9" s="20"/>
-      <c r="BZ9" s="20"/>
-      <c r="CA9" s="20"/>
-    </row>
-    <row r="10" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="8"/>
-      <c r="AG10" s="16"/>
-      <c r="AH10" s="13"/>
-      <c r="AI10" s="12"/>
-      <c r="AJ10" s="12"/>
-      <c r="AK10" s="13"/>
-      <c r="AL10" s="13"/>
-      <c r="AM10" s="13"/>
-      <c r="AN10" s="12"/>
-      <c r="AO10" s="8"/>
-      <c r="AP10" s="11"/>
-      <c r="AQ10" s="13"/>
-      <c r="AR10" s="11"/>
-      <c r="AS10" s="17"/>
-      <c r="AT10" s="18"/>
-      <c r="AU10" s="13"/>
-      <c r="AV10" s="13"/>
-      <c r="AW10" s="11"/>
-      <c r="AX10" s="17"/>
-      <c r="AY10" s="19"/>
-      <c r="AZ10" s="13"/>
-      <c r="BA10" s="13"/>
-      <c r="BB10" s="8"/>
-      <c r="BC10" s="13"/>
-      <c r="BD10" s="17"/>
-      <c r="BE10" s="17"/>
-      <c r="BF10" s="17"/>
-      <c r="BG10" s="11"/>
-      <c r="BH10" s="11"/>
-      <c r="BI10" s="8"/>
-      <c r="BJ10" s="17"/>
-      <c r="BK10" s="14"/>
-      <c r="BL10" s="14"/>
-      <c r="BM10" s="14"/>
-      <c r="BN10" s="14"/>
-      <c r="BO10" s="14"/>
-      <c r="BP10" s="14"/>
-      <c r="BQ10" s="14"/>
-      <c r="BR10" s="14"/>
-      <c r="BS10" s="14"/>
-      <c r="BT10" s="14"/>
-      <c r="BU10" s="14"/>
-      <c r="BV10" s="20"/>
-      <c r="BW10" s="20"/>
-      <c r="BX10" s="20"/>
-      <c r="BY10" s="20"/>
-      <c r="BZ10" s="20"/>
-      <c r="CA10" s="20"/>
-    </row>
-    <row r="11" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="8"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="13"/>
-      <c r="AI11" s="12"/>
-      <c r="AJ11" s="12"/>
-      <c r="AK11" s="13"/>
-      <c r="AL11" s="13"/>
-      <c r="AM11" s="13"/>
-      <c r="AN11" s="12"/>
-      <c r="AO11" s="8"/>
-      <c r="AP11" s="11"/>
-      <c r="AQ11" s="13"/>
-      <c r="AR11" s="11"/>
-      <c r="AS11" s="17"/>
-      <c r="AT11" s="18"/>
-      <c r="AU11" s="13"/>
-      <c r="AV11" s="13"/>
-      <c r="AW11" s="11"/>
-      <c r="AX11" s="17"/>
-      <c r="AY11" s="19"/>
-      <c r="AZ11" s="13"/>
-      <c r="BA11" s="13"/>
-      <c r="BB11" s="8"/>
-      <c r="BC11" s="13"/>
-      <c r="BD11" s="17"/>
-      <c r="BE11" s="17"/>
-      <c r="BF11" s="17"/>
-      <c r="BG11" s="11"/>
-      <c r="BH11" s="11"/>
-      <c r="BI11" s="8"/>
-      <c r="BJ11" s="17"/>
-      <c r="BK11" s="14"/>
-      <c r="BL11" s="14"/>
-      <c r="BM11" s="14"/>
-      <c r="BN11" s="14"/>
-      <c r="BO11" s="14"/>
-      <c r="BP11" s="14"/>
-      <c r="BQ11" s="14"/>
-      <c r="BR11" s="14"/>
-      <c r="BS11" s="14"/>
-      <c r="BT11" s="14"/>
-      <c r="BU11" s="14"/>
-      <c r="BV11" s="20"/>
-      <c r="BW11" s="20"/>
-      <c r="BX11" s="20"/>
-      <c r="BY11" s="20"/>
-      <c r="BZ11" s="20"/>
-      <c r="CA11" s="20"/>
-    </row>
-    <row r="12" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="13"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="12"/>
-      <c r="AJ12" s="12"/>
-      <c r="AK12" s="13"/>
-      <c r="AL12" s="13"/>
-      <c r="AM12" s="13"/>
-      <c r="AN12" s="12"/>
-      <c r="AO12" s="8"/>
-      <c r="AP12" s="11"/>
-      <c r="AQ12" s="13"/>
-      <c r="AR12" s="11"/>
-      <c r="AS12" s="17"/>
-      <c r="AT12" s="18"/>
-      <c r="AU12" s="13"/>
-      <c r="AV12" s="13"/>
-      <c r="AW12" s="11"/>
-      <c r="AX12" s="17"/>
-      <c r="AY12" s="19"/>
-      <c r="AZ12" s="13"/>
-      <c r="BA12" s="13"/>
-      <c r="BB12" s="8"/>
-      <c r="BC12" s="13"/>
-      <c r="BD12" s="17"/>
-      <c r="BE12" s="17"/>
-      <c r="BF12" s="17"/>
-      <c r="BG12" s="11"/>
-      <c r="BH12" s="11"/>
-      <c r="BI12" s="8"/>
-      <c r="BJ12" s="17"/>
-      <c r="BK12" s="14"/>
-      <c r="BL12" s="14"/>
-      <c r="BM12" s="14"/>
-      <c r="BN12" s="14"/>
-      <c r="BO12" s="14"/>
-      <c r="BP12" s="14"/>
-      <c r="BQ12" s="14"/>
-      <c r="BR12" s="14"/>
-      <c r="BS12" s="14"/>
-      <c r="BT12" s="14"/>
-      <c r="BU12" s="14"/>
-      <c r="BV12" s="20"/>
-      <c r="BW12" s="20"/>
-      <c r="BX12" s="20"/>
-      <c r="BY12" s="20"/>
-      <c r="BZ12" s="20"/>
-      <c r="CA12" s="20"/>
-    </row>
-    <row r="13" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="12"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="8"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="13"/>
-      <c r="AI13" s="12"/>
-      <c r="AJ13" s="12"/>
-      <c r="AK13" s="13"/>
-      <c r="AL13" s="13"/>
-      <c r="AM13" s="13"/>
-      <c r="AN13" s="12"/>
-      <c r="AO13" s="8"/>
-      <c r="AP13" s="11"/>
-      <c r="AQ13" s="13"/>
-      <c r="AR13" s="11"/>
-      <c r="AS13" s="17"/>
-      <c r="AT13" s="18"/>
-      <c r="AU13" s="13"/>
-      <c r="AV13" s="13"/>
-      <c r="AW13" s="11"/>
-      <c r="AX13" s="17"/>
-      <c r="AY13" s="19"/>
-      <c r="AZ13" s="13"/>
-      <c r="BA13" s="13"/>
-      <c r="BB13" s="8"/>
-      <c r="BC13" s="13"/>
-      <c r="BD13" s="17"/>
-      <c r="BE13" s="17"/>
-      <c r="BF13" s="17"/>
-      <c r="BG13" s="11"/>
-      <c r="BH13" s="11"/>
-      <c r="BI13" s="8"/>
-      <c r="BJ13" s="17"/>
-      <c r="BK13" s="14"/>
-      <c r="BL13" s="14"/>
-      <c r="BM13" s="14"/>
-      <c r="BN13" s="14"/>
-      <c r="BO13" s="14"/>
-      <c r="BP13" s="14"/>
-      <c r="BQ13" s="14"/>
-      <c r="BR13" s="14"/>
-      <c r="BS13" s="14"/>
-      <c r="BT13" s="14"/>
-      <c r="BU13" s="14"/>
-      <c r="BV13" s="20"/>
-      <c r="BW13" s="20"/>
-      <c r="BX13" s="20"/>
-      <c r="BY13" s="20"/>
-      <c r="BZ13" s="20"/>
-      <c r="CA13" s="20"/>
-    </row>
-    <row r="14" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="8"/>
-      <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="16"/>
-      <c r="AH14" s="13"/>
-      <c r="AI14" s="12"/>
-      <c r="AJ14" s="12"/>
-      <c r="AK14" s="13"/>
-      <c r="AL14" s="13"/>
-      <c r="AM14" s="13"/>
-      <c r="AN14" s="12"/>
-      <c r="AO14" s="8"/>
-      <c r="AP14" s="11"/>
-      <c r="AQ14" s="13"/>
-      <c r="AR14" s="11"/>
-      <c r="AS14" s="17"/>
-      <c r="AT14" s="18"/>
-      <c r="AU14" s="13"/>
-      <c r="AV14" s="13"/>
-      <c r="AW14" s="11"/>
-      <c r="AX14" s="17"/>
-      <c r="AY14" s="19"/>
-      <c r="AZ14" s="13"/>
-      <c r="BA14" s="13"/>
-      <c r="BB14" s="8"/>
-      <c r="BC14" s="13"/>
-      <c r="BD14" s="17"/>
-      <c r="BE14" s="17"/>
-      <c r="BF14" s="17"/>
-      <c r="BG14" s="11"/>
-      <c r="BH14" s="11"/>
-      <c r="BI14" s="8"/>
-      <c r="BJ14" s="17"/>
-      <c r="BK14" s="14"/>
-      <c r="BL14" s="14"/>
-      <c r="BM14" s="14"/>
-      <c r="BN14" s="14"/>
-      <c r="BO14" s="14"/>
-      <c r="BP14" s="14"/>
-      <c r="BQ14" s="14"/>
-      <c r="BR14" s="14"/>
-      <c r="BS14" s="14"/>
-      <c r="BT14" s="14"/>
-      <c r="BU14" s="14"/>
-      <c r="BV14" s="20"/>
-      <c r="BW14" s="20"/>
-      <c r="BX14" s="20"/>
-      <c r="BY14" s="20"/>
-      <c r="BZ14" s="20"/>
-      <c r="CA14" s="20"/>
-    </row>
-    <row r="15" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="12"/>
-      <c r="Z15" s="12"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="8"/>
-      <c r="AG15" s="16"/>
-      <c r="AH15" s="13"/>
-      <c r="AI15" s="12"/>
-      <c r="AJ15" s="12"/>
-      <c r="AK15" s="13"/>
-      <c r="AL15" s="13"/>
-      <c r="AM15" s="13"/>
-      <c r="AN15" s="12"/>
-      <c r="AO15" s="8"/>
-      <c r="AP15" s="11"/>
-      <c r="AQ15" s="13"/>
-      <c r="AR15" s="11"/>
-      <c r="AS15" s="17"/>
-      <c r="AT15" s="18"/>
-      <c r="AU15" s="13"/>
-      <c r="AV15" s="13"/>
-      <c r="AW15" s="11"/>
-      <c r="AX15" s="17"/>
-      <c r="AY15" s="19"/>
-      <c r="AZ15" s="13"/>
-      <c r="BA15" s="13"/>
-      <c r="BB15" s="8"/>
-      <c r="BC15" s="13"/>
-      <c r="BD15" s="17"/>
-      <c r="BE15" s="17"/>
-      <c r="BF15" s="17"/>
-      <c r="BG15" s="11"/>
-      <c r="BH15" s="11"/>
-      <c r="BI15" s="8"/>
-      <c r="BJ15" s="17"/>
-      <c r="BK15" s="14"/>
-      <c r="BL15" s="14"/>
-      <c r="BM15" s="14"/>
-      <c r="BN15" s="14"/>
-      <c r="BO15" s="14"/>
-      <c r="BP15" s="14"/>
-      <c r="BQ15" s="14"/>
-      <c r="BR15" s="14"/>
-      <c r="BS15" s="14"/>
-      <c r="BT15" s="14"/>
-      <c r="BU15" s="14"/>
-      <c r="BV15" s="20"/>
-      <c r="BW15" s="20"/>
-      <c r="BX15" s="20"/>
-      <c r="BY15" s="20"/>
-      <c r="BZ15" s="20"/>
-      <c r="CA15" s="20"/>
-    </row>
-    <row r="16" ht="15.65" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="13"/>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="12"/>
-      <c r="AA16" s="8"/>
-      <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="11"/>
-      <c r="AF16" s="8"/>
-      <c r="AG16" s="16"/>
-      <c r="AH16" s="13"/>
-      <c r="AI16" s="12"/>
-      <c r="AJ16" s="12"/>
-      <c r="AK16" s="13"/>
-      <c r="AL16" s="13"/>
-      <c r="AM16" s="13"/>
-      <c r="AN16" s="12"/>
-      <c r="AO16" s="8"/>
-      <c r="AP16" s="11"/>
-      <c r="AQ16" s="13"/>
-      <c r="AR16" s="11"/>
-      <c r="AS16" s="17"/>
-      <c r="AT16" s="18"/>
-      <c r="AU16" s="13"/>
-      <c r="AV16" s="13"/>
-      <c r="AW16" s="11"/>
-      <c r="AX16" s="17"/>
-      <c r="AY16" s="19"/>
-      <c r="AZ16" s="13"/>
-      <c r="BA16" s="13"/>
-      <c r="BB16" s="8"/>
-      <c r="BC16" s="13"/>
-      <c r="BD16" s="17"/>
-      <c r="BE16" s="17"/>
-      <c r="BF16" s="17"/>
-      <c r="BG16" s="11"/>
-      <c r="BH16" s="11"/>
-      <c r="BI16" s="8"/>
-      <c r="BJ16" s="17"/>
-      <c r="BK16" s="14"/>
-      <c r="BL16" s="14"/>
-      <c r="BM16" s="14"/>
-      <c r="BN16" s="14"/>
-      <c r="BO16" s="14"/>
-      <c r="BP16" s="14"/>
-      <c r="BQ16" s="14"/>
-      <c r="BR16" s="14"/>
-      <c r="BS16" s="14"/>
-      <c r="BT16" s="14"/>
-      <c r="BU16" s="14"/>
-      <c r="BV16" s="20"/>
-      <c r="BW16" s="20"/>
-      <c r="BX16" s="20"/>
-      <c r="BY16" s="20"/>
-      <c r="BZ16" s="20"/>
-      <c r="CA16" s="20"/>
-    </row>
-    <row r="17" ht="15.65" customHeight="1" spans="46:51" x14ac:dyDescent="0.25">
-      <c r="AT17" s="19"/>
-      <c r="AY17" s="19"/>
+      <c r="AY4" s="18"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ3 T2:T3 W2:W3 Y2:Y3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3 J2:J3" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16">
-      <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J16">
-      <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J16">
-      <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W10:W16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y10:Y16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y16">
-      <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -1,30 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{B9455642-526F-4A08-9641-0084BA48857A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -259,7 +244,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699009</t>
+    <t>10699732</t>
   </si>
   <si>
     <t>Passed</t>
@@ -271,10 +256,10 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>Otho</t>
-  </si>
-  <si>
-    <t>Kerluke</t>
+    <t>Alessandro</t>
+  </si>
+  <si>
+    <t>Mayert</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -412,22 +397,22 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699010</t>
+    <t>10699735</t>
   </si>
   <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Trantow</t>
+    <t>Blake</t>
+  </si>
+  <si>
+    <t>Wunsch</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 23256195</t>
+    <t>Auto 7050893</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -463,57 +448,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <u/>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -522,7 +507,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,11 +530,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -567,35 +547,23 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -613,9 +581,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -629,7 +594,7 @@
     <xf numFmtId="14" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
@@ -651,9 +616,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -933,95 +895,94 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CN17"/>
-  <sheetFormatPr defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:CN4"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="109.7265625" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
-    <col min="4" max="4" width="46.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1796875" style="1" customWidth="1"/>
     <col min="11" max="11" width="15" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.453125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.90625" style="1" customWidth="1"/>
     <col min="14" max="14" width="16" style="1" customWidth="1"/>
     <col min="15" max="15" width="20" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.21875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="6.21875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.21875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="12.109375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="15.6640625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.21875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.109375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.5546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="22.21875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="16.5546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.6328125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.1796875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.36328125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.1796875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="12.08984375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15.6328125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.1796875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.08984375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="8.54296875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22.1796875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="16.54296875" style="1" customWidth="1"/>
     <col min="28" max="28" width="37" style="1" customWidth="1"/>
-    <col min="29" max="29" width="11.5546875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="21.44140625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="14.6640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="11.88671875" style="1" customWidth="1"/>
-    <col min="33" max="33" width="26.21875" style="1" customWidth="1"/>
-    <col min="34" max="34" width="23.21875" style="1" customWidth="1"/>
-    <col min="35" max="35" width="23.33203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="7.21875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="18.77734375" style="1" customWidth="1"/>
-    <col min="38" max="38" width="23.33203125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="23.109375" style="1" customWidth="1"/>
-    <col min="40" max="40" width="18.33203125" style="1" customWidth="1"/>
-    <col min="41" max="41" width="23.5546875" style="1" customWidth="1"/>
-    <col min="42" max="42" width="20.6640625" style="1" customWidth="1"/>
-    <col min="43" max="43" width="20.109375" style="1" customWidth="1"/>
-    <col min="44" max="44" width="10.6640625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="11.54296875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="21.453125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="14.6328125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="11.90625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="26.1796875" style="1" customWidth="1"/>
+    <col min="34" max="34" width="23.1796875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="23.36328125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="7.1796875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.81640625" style="1" customWidth="1"/>
+    <col min="38" max="38" width="23.36328125" style="1" customWidth="1"/>
+    <col min="39" max="39" width="23.08984375" style="1" customWidth="1"/>
+    <col min="40" max="40" width="18.36328125" style="1" customWidth="1"/>
+    <col min="41" max="41" width="23.54296875" style="1" customWidth="1"/>
+    <col min="42" max="42" width="20.6328125" style="1" customWidth="1"/>
+    <col min="43" max="43" width="20.08984375" style="1" customWidth="1"/>
+    <col min="44" max="44" width="10.6328125" style="1" customWidth="1"/>
     <col min="45" max="45" width="19" style="1" customWidth="1"/>
-    <col min="46" max="46" width="15.77734375" style="1" customWidth="1"/>
-    <col min="47" max="47" width="13.6640625" style="1" customWidth="1"/>
-    <col min="48" max="48" width="17.77734375" style="1" customWidth="1"/>
-    <col min="49" max="49" width="10.6640625" style="1" customWidth="1"/>
+    <col min="46" max="46" width="15.81640625" style="1" customWidth="1"/>
+    <col min="47" max="47" width="13.6328125" style="1" customWidth="1"/>
+    <col min="48" max="48" width="17.81640625" style="1" customWidth="1"/>
+    <col min="49" max="49" width="10.6328125" style="1" customWidth="1"/>
     <col min="50" max="50" width="19" style="1" customWidth="1"/>
-    <col min="51" max="51" width="14.33203125" style="1" customWidth="1"/>
-    <col min="52" max="52" width="13.6640625" style="1" customWidth="1"/>
-    <col min="53" max="53" width="17.77734375" style="1" customWidth="1"/>
-    <col min="54" max="54" width="8.5546875" style="1" customWidth="1"/>
-    <col min="55" max="55" width="13.6640625" style="1" customWidth="1"/>
-    <col min="56" max="56" width="12.5546875" style="1" customWidth="1"/>
-    <col min="57" max="57" width="14.5546875" style="1" customWidth="1"/>
-    <col min="58" max="58" width="18.88671875" style="1" customWidth="1"/>
-    <col min="59" max="59" width="12.33203125" style="1" customWidth="1"/>
+    <col min="51" max="51" width="14.36328125" style="1" customWidth="1"/>
+    <col min="52" max="52" width="13.6328125" style="1" customWidth="1"/>
+    <col min="53" max="53" width="17.81640625" style="1" customWidth="1"/>
+    <col min="54" max="54" width="8.54296875" style="1" customWidth="1"/>
+    <col min="55" max="55" width="13.6328125" style="1" customWidth="1"/>
+    <col min="56" max="56" width="12.54296875" style="1" customWidth="1"/>
+    <col min="57" max="57" width="14.54296875" style="1" customWidth="1"/>
+    <col min="58" max="58" width="18.90625" style="1" customWidth="1"/>
+    <col min="59" max="59" width="12.36328125" style="1" customWidth="1"/>
     <col min="60" max="60" width="15" style="1" customWidth="1"/>
     <col min="61" max="61" width="26" style="1" customWidth="1"/>
-    <col min="62" max="62" width="25.77734375" style="1" customWidth="1"/>
-    <col min="63" max="63" width="9.44140625" style="1" customWidth="1"/>
-    <col min="64" max="64" width="8.21875" style="1" customWidth="1"/>
-    <col min="65" max="65" width="8.33203125" style="1" customWidth="1"/>
-    <col min="66" max="66" width="17.88671875" style="1" customWidth="1"/>
-    <col min="67" max="67" width="22.88671875" style="1" customWidth="1"/>
-    <col min="68" max="68" width="15.109375" style="1" customWidth="1"/>
-    <col min="69" max="69" width="20.109375" style="1" customWidth="1"/>
-    <col min="70" max="70" width="19.6640625" style="1" customWidth="1"/>
-    <col min="71" max="71" width="29.88671875" style="1" customWidth="1"/>
-    <col min="72" max="72" width="23.44140625" style="1" customWidth="1"/>
-    <col min="73" max="73" width="26.77734375" style="1" customWidth="1"/>
-    <col min="74" max="74" width="30.6640625" style="1" customWidth="1"/>
-    <col min="75" max="75" width="31.5546875" style="1" customWidth="1"/>
-    <col min="76" max="76" width="28.109375" style="1" customWidth="1"/>
+    <col min="62" max="62" width="25.81640625" style="1" customWidth="1"/>
+    <col min="63" max="63" width="9.453125" style="1" customWidth="1"/>
+    <col min="64" max="64" width="8.1796875" style="1" customWidth="1"/>
+    <col min="65" max="65" width="8.36328125" style="1" customWidth="1"/>
+    <col min="66" max="66" width="17.90625" style="1" customWidth="1"/>
+    <col min="67" max="67" width="22.90625" style="1" customWidth="1"/>
+    <col min="68" max="68" width="15.08984375" style="1" customWidth="1"/>
+    <col min="69" max="69" width="20.08984375" style="1" customWidth="1"/>
+    <col min="70" max="70" width="19.6328125" style="1" customWidth="1"/>
+    <col min="71" max="71" width="29.90625" style="1" customWidth="1"/>
+    <col min="72" max="72" width="23.453125" style="1" customWidth="1"/>
+    <col min="73" max="73" width="26.81640625" style="1" customWidth="1"/>
+    <col min="74" max="74" width="30.6328125" style="1" customWidth="1"/>
+    <col min="75" max="75" width="31.54296875" style="1" customWidth="1"/>
+    <col min="76" max="76" width="28.08984375" style="1" customWidth="1"/>
     <col min="77" max="77" width="15" style="1" customWidth="1"/>
-    <col min="78" max="78" width="33.6640625" style="1" customWidth="1"/>
-    <col min="79" max="79" width="26.88671875" style="1" customWidth="1"/>
-    <col min="80" max="80" width="8.88671875" style="1" customWidth="1"/>
-    <col min="81" max="16384" width="8.88671875" style="1"/>
+    <col min="78" max="78" width="33.6328125" style="1" customWidth="1"/>
+    <col min="79" max="79" width="26.90625" style="1" customWidth="1"/>
+    <col min="80" max="16384" width="8.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:92" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1273,84 +1234,84 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>76</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>79</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="12">
         <v>45597</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="10">
         <v>1</v>
       </c>
-      <c r="O2" s="14">
+      <c r="O2" s="13">
         <v>213111231</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="V2" s="15" t="s">
+      <c r="V2" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="13">
+      <c r="X2" s="12">
         <f t="shared" ref="X2:X3" si="0">K2</f>
         <v>45597</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Y2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="Z2" s="11" t="s">
         <v>92</v>
       </c>
       <c r="AA2" s="8" t="s">
@@ -1362,239 +1323,239 @@
       <c r="AC2" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AD2" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="AE2" s="10" t="s">
         <v>97</v>
       </c>
       <c r="AF2" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AG2" s="16">
+      <c r="AG2" s="15">
         <v>20</v>
       </c>
-      <c r="AH2" s="13" t="s">
+      <c r="AH2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="AI2" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="AJ2" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK2" s="13" t="str">
+      <c r="AK2" s="12">
         <f t="shared" ref="AK2:AK3" si="1">AH2</f>
-        <v>N/A</v>
-      </c>
-      <c r="AL2" s="13">
+        <v>NaN</v>
+      </c>
+      <c r="AL2" s="12">
         <f t="shared" ref="AL2:AL3" si="2">K2</f>
         <v>45597</v>
       </c>
-      <c r="AM2" s="13">
+      <c r="AM2" s="12">
         <f t="shared" ref="AM2:AM3" si="3">K2</f>
         <v>45597</v>
       </c>
-      <c r="AN2" s="12" t="s">
+      <c r="AN2" s="11" t="s">
         <v>102</v>
       </c>
       <c r="AO2" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="AP2" s="11">
+      <c r="AP2" s="10">
         <v>100</v>
       </c>
-      <c r="AQ2" s="13">
+      <c r="AQ2" s="12">
         <f t="shared" ref="AQ2:AQ3" si="4">K2+90</f>
         <v>45687</v>
       </c>
-      <c r="AR2" s="11" t="s">
+      <c r="AR2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AS2" s="17" t="s">
+      <c r="AS2" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="18">
-        <v>9361110759</v>
-      </c>
-      <c r="AU2" s="13" t="s">
+      <c r="AT2" s="17">
+        <v>9461110909</v>
+      </c>
+      <c r="AU2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AV2" s="13" t="s">
+      <c r="AV2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AW2" s="11" t="s">
+      <c r="AW2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AX2" s="17" t="s">
+      <c r="AX2" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="AY2" s="19">
-        <v>141743023</v>
-      </c>
-      <c r="AZ2" s="13" t="s">
+      <c r="AY2" s="18">
+        <v>152733408</v>
+      </c>
+      <c r="AZ2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="BA2" s="13" t="s">
+      <c r="BA2" s="12" t="s">
         <v>106</v>
       </c>
       <c r="BB2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="BC2" s="13">
+      <c r="BC2" s="12">
         <v>34284</v>
       </c>
-      <c r="BD2" s="17" t="s">
+      <c r="BD2" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="BE2" s="17" t="s">
+      <c r="BE2" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="17" t="s">
+      <c r="BF2" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="BG2" s="11" t="s">
+      <c r="BG2" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="11" t="s">
+      <c r="BH2" s="10" t="s">
         <v>112</v>
       </c>
       <c r="BI2" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="BJ2" s="17" t="s">
+      <c r="BJ2" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BK2" s="14" t="s">
+      <c r="BK2" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="BL2" s="14" t="s">
+      <c r="BL2" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="BM2" s="14" t="s">
+      <c r="BM2" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="BN2" s="14" t="s">
+      <c r="BN2" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="BO2" s="14">
+      <c r="BO2" s="13">
         <v>2024</v>
       </c>
-      <c r="BP2" s="14" t="s">
+      <c r="BP2" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="BQ2" s="14">
+      <c r="BQ2" s="13">
         <v>2021</v>
       </c>
-      <c r="BR2" s="14">
+      <c r="BR2" s="13">
         <v>2024</v>
       </c>
-      <c r="BS2" s="14" t="s">
+      <c r="BS2" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="14" t="s">
+      <c r="BT2" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="BU2" s="14" t="s">
+      <c r="BU2" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="BV2" s="20" t="s">
+      <c r="BV2" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="BW2" s="20" t="s">
+      <c r="BW2" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="BX2" s="20">
+      <c r="BX2" s="19">
         <v>213</v>
       </c>
-      <c r="BY2" s="20" t="s">
+      <c r="BY2" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="BZ2" s="20" t="s">
+      <c r="BZ2" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="CA2" s="20" t="s">
+      <c r="CA2" s="19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>127</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>79</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="12">
         <v>45597</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="10">
         <v>1</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="13">
         <v>213111231</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="T3" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="U3" s="13" t="s">
+      <c r="U3" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="V3" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="W3" s="12" t="s">
+      <c r="W3" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="X3" s="13">
+      <c r="X3" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
-      <c r="Y3" s="12" t="s">
+      <c r="Y3" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="Z3" s="12" t="s">
+      <c r="Z3" s="11" t="s">
         <v>132</v>
       </c>
       <c r="AA3" s="8" t="s">
@@ -1606,1234 +1567,187 @@
       <c r="AC3" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="AD3" s="11" t="s">
+      <c r="AD3" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AE3" s="11" t="s">
+      <c r="AE3" s="10" t="s">
         <v>97</v>
       </c>
       <c r="AF3" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="AG3" s="16">
+      <c r="AG3" s="15">
         <v>40</v>
       </c>
-      <c r="AH3" s="13" t="s">
+      <c r="AH3" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AI3" s="12" t="s">
+      <c r="AI3" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="AJ3" s="12" t="s">
+      <c r="AJ3" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK3" s="13" t="str">
+      <c r="AK3" s="12">
         <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="AL3" s="13">
+        <v>NaN</v>
+      </c>
+      <c r="AL3" s="12">
         <f t="shared" si="2"/>
         <v>45597</v>
       </c>
-      <c r="AM3" s="13">
+      <c r="AM3" s="12">
         <f t="shared" si="3"/>
         <v>45597</v>
       </c>
-      <c r="AN3" s="12" t="s">
+      <c r="AN3" s="11" t="s">
         <v>136</v>
       </c>
       <c r="AO3" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="AP3" s="11">
+      <c r="AP3" s="10">
         <v>100</v>
       </c>
-      <c r="AQ3" s="13">
+      <c r="AQ3" s="12">
         <f t="shared" si="4"/>
         <v>45687</v>
       </c>
-      <c r="AR3" s="11" t="s">
+      <c r="AR3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AS3" s="17" t="s">
+      <c r="AS3" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="AT3" s="18">
-        <v>9361115170</v>
-      </c>
-      <c r="AU3" s="13" t="s">
+      <c r="AT3" s="17">
+        <v>9461110910</v>
+      </c>
+      <c r="AU3" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AV3" s="13" t="s">
+      <c r="AV3" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AW3" s="11" t="s">
+      <c r="AW3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AX3" s="17" t="s">
+      <c r="AX3" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="AY3" s="19">
-        <v>141733024</v>
-      </c>
-      <c r="AZ3" s="13" t="s">
+      <c r="AY3" s="18">
+        <v>152733409</v>
+      </c>
+      <c r="AZ3" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="BA3" s="13" t="s">
+      <c r="BA3" s="12" t="s">
         <v>106</v>
       </c>
       <c r="BB3" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="BC3" s="13">
+      <c r="BC3" s="12">
         <v>34284</v>
       </c>
-      <c r="BD3" s="17" t="s">
+      <c r="BD3" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="BE3" s="17" t="s">
+      <c r="BE3" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="BF3" s="17" t="s">
+      <c r="BF3" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="BG3" s="11" t="s">
+      <c r="BG3" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="BH3" s="11" t="s">
+      <c r="BH3" s="10" t="s">
         <v>112</v>
       </c>
       <c r="BI3" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="BJ3" s="17" t="s">
+      <c r="BJ3" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BK3" s="14" t="s">
+      <c r="BK3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="BL3" s="14" t="s">
+      <c r="BL3" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="BM3" s="14" t="s">
+      <c r="BM3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="BN3" s="14" t="s">
+      <c r="BN3" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="BO3" s="14">
+      <c r="BO3" s="13">
         <v>2000</v>
       </c>
-      <c r="BP3" s="14" t="s">
+      <c r="BP3" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="BQ3" s="14">
+      <c r="BQ3" s="13">
         <v>1995</v>
       </c>
-      <c r="BR3" s="14">
+      <c r="BR3" s="13">
         <v>2000</v>
       </c>
-      <c r="BS3" s="14" t="s">
+      <c r="BS3" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="BT3" s="14" t="s">
+      <c r="BT3" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="BU3" s="14" t="s">
+      <c r="BU3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="BV3" s="20" t="s">
+      <c r="BV3" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="BW3" s="20" t="s">
+      <c r="BW3" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="BX3" s="20">
+      <c r="BX3" s="19">
         <v>201</v>
       </c>
-      <c r="BY3" s="20" t="s">
+      <c r="BY3" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="BZ3" s="20" t="s">
+      <c r="BZ3" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="CA3" s="20" t="s">
+      <c r="CA3" s="19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="8"/>
-      <c r="AD4" s="11"/>
-      <c r="AE4" s="11"/>
-      <c r="AF4" s="8"/>
-      <c r="AG4" s="16"/>
-      <c r="AH4" s="13"/>
-      <c r="AI4" s="12"/>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="13"/>
-      <c r="AL4" s="13"/>
-      <c r="AM4" s="13"/>
-      <c r="AN4" s="12"/>
-      <c r="AO4" s="8"/>
-      <c r="AP4" s="11"/>
-      <c r="AQ4" s="13"/>
-      <c r="AR4" s="11"/>
-      <c r="AS4" s="17"/>
+    <row r="4" ht="15.65" customHeight="1" spans="46:51" x14ac:dyDescent="0.25">
       <c r="AT4" s="18"/>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="13"/>
-      <c r="AW4" s="11"/>
-      <c r="AX4" s="17"/>
-      <c r="AY4" s="19"/>
-      <c r="AZ4" s="13"/>
-      <c r="BA4" s="13"/>
-      <c r="BB4" s="8"/>
-      <c r="BC4" s="13"/>
-      <c r="BD4" s="17"/>
-      <c r="BE4" s="17"/>
-      <c r="BF4" s="17"/>
-      <c r="BG4" s="11"/>
-      <c r="BH4" s="11"/>
-      <c r="BI4" s="8"/>
-      <c r="BJ4" s="17"/>
-      <c r="BK4" s="14"/>
-      <c r="BL4" s="14"/>
-      <c r="BM4" s="14"/>
-      <c r="BN4" s="14"/>
-      <c r="BO4" s="14"/>
-      <c r="BP4" s="14"/>
-      <c r="BQ4" s="14"/>
-      <c r="BR4" s="14"/>
-      <c r="BS4" s="14"/>
-      <c r="BT4" s="14"/>
-      <c r="BU4" s="14"/>
-      <c r="BV4" s="20"/>
-      <c r="BW4" s="20"/>
-      <c r="BX4" s="20"/>
-      <c r="BY4" s="20"/>
-      <c r="BZ4" s="20"/>
-      <c r="CA4" s="20"/>
-    </row>
-    <row r="5" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="8"/>
-      <c r="AB5" s="8"/>
-      <c r="AC5" s="8"/>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="8"/>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="13"/>
-      <c r="AI5" s="12"/>
-      <c r="AJ5" s="12"/>
-      <c r="AK5" s="13"/>
-      <c r="AL5" s="13"/>
-      <c r="AM5" s="13"/>
-      <c r="AN5" s="12"/>
-      <c r="AO5" s="8"/>
-      <c r="AP5" s="11"/>
-      <c r="AQ5" s="13"/>
-      <c r="AR5" s="11"/>
-      <c r="AS5" s="17"/>
-      <c r="AT5" s="18"/>
-      <c r="AU5" s="13"/>
-      <c r="AV5" s="13"/>
-      <c r="AW5" s="11"/>
-      <c r="AX5" s="17"/>
-      <c r="AY5" s="19"/>
-      <c r="AZ5" s="13"/>
-      <c r="BA5" s="13"/>
-      <c r="BB5" s="8"/>
-      <c r="BC5" s="13"/>
-      <c r="BD5" s="17"/>
-      <c r="BE5" s="17"/>
-      <c r="BF5" s="17"/>
-      <c r="BG5" s="11"/>
-      <c r="BH5" s="11"/>
-      <c r="BI5" s="8"/>
-      <c r="BJ5" s="17"/>
-      <c r="BK5" s="14"/>
-      <c r="BL5" s="14"/>
-      <c r="BM5" s="14"/>
-      <c r="BN5" s="14"/>
-      <c r="BO5" s="14"/>
-      <c r="BP5" s="14"/>
-      <c r="BQ5" s="14"/>
-      <c r="BR5" s="14"/>
-      <c r="BS5" s="14"/>
-      <c r="BT5" s="14"/>
-      <c r="BU5" s="14"/>
-      <c r="BV5" s="20"/>
-      <c r="BW5" s="20"/>
-      <c r="BX5" s="20"/>
-      <c r="BY5" s="20"/>
-      <c r="BZ5" s="20"/>
-      <c r="CA5" s="20"/>
-    </row>
-    <row r="6" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="11"/>
-      <c r="AF6" s="8"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="12"/>
-      <c r="AJ6" s="12"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="8"/>
-      <c r="AP6" s="11"/>
-      <c r="AQ6" s="13"/>
-      <c r="AR6" s="11"/>
-      <c r="AS6" s="17"/>
-      <c r="AT6" s="18"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="11"/>
-      <c r="AX6" s="17"/>
-      <c r="AY6" s="19"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="13"/>
-      <c r="BB6" s="8"/>
-      <c r="BC6" s="13"/>
-      <c r="BD6" s="17"/>
-      <c r="BE6" s="17"/>
-      <c r="BF6" s="17"/>
-      <c r="BG6" s="11"/>
-      <c r="BH6" s="11"/>
-      <c r="BI6" s="8"/>
-      <c r="BJ6" s="17"/>
-      <c r="BK6" s="14"/>
-      <c r="BL6" s="14"/>
-      <c r="BM6" s="14"/>
-      <c r="BN6" s="14"/>
-      <c r="BO6" s="14"/>
-      <c r="BP6" s="14"/>
-      <c r="BQ6" s="14"/>
-      <c r="BR6" s="14"/>
-      <c r="BS6" s="14"/>
-      <c r="BT6" s="14"/>
-      <c r="BU6" s="14"/>
-      <c r="BV6" s="20"/>
-      <c r="BW6" s="20"/>
-      <c r="BX6" s="20"/>
-      <c r="BY6" s="20"/>
-      <c r="BZ6" s="20"/>
-      <c r="CA6" s="20"/>
-    </row>
-    <row r="7" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="8"/>
-      <c r="AG7" s="16"/>
-      <c r="AH7" s="13"/>
-      <c r="AI7" s="12"/>
-      <c r="AJ7" s="12"/>
-      <c r="AK7" s="13"/>
-      <c r="AL7" s="13"/>
-      <c r="AM7" s="13"/>
-      <c r="AN7" s="12"/>
-      <c r="AO7" s="8"/>
-      <c r="AP7" s="11"/>
-      <c r="AQ7" s="13"/>
-      <c r="AR7" s="11"/>
-      <c r="AS7" s="17"/>
-      <c r="AT7" s="18"/>
-      <c r="AU7" s="13"/>
-      <c r="AV7" s="13"/>
-      <c r="AW7" s="11"/>
-      <c r="AX7" s="17"/>
-      <c r="AY7" s="19"/>
-      <c r="AZ7" s="13"/>
-      <c r="BA7" s="13"/>
-      <c r="BB7" s="8"/>
-      <c r="BC7" s="13"/>
-      <c r="BD7" s="17"/>
-      <c r="BE7" s="17"/>
-      <c r="BF7" s="17"/>
-      <c r="BG7" s="11"/>
-      <c r="BH7" s="11"/>
-      <c r="BI7" s="8"/>
-      <c r="BJ7" s="17"/>
-      <c r="BK7" s="14"/>
-      <c r="BL7" s="14"/>
-      <c r="BM7" s="14"/>
-      <c r="BN7" s="14"/>
-      <c r="BO7" s="14"/>
-      <c r="BP7" s="14"/>
-      <c r="BQ7" s="14"/>
-      <c r="BR7" s="14"/>
-      <c r="BS7" s="14"/>
-      <c r="BT7" s="14"/>
-      <c r="BU7" s="14"/>
-      <c r="BV7" s="20"/>
-      <c r="BW7" s="20"/>
-      <c r="BX7" s="20"/>
-      <c r="BY7" s="20"/>
-      <c r="BZ7" s="20"/>
-      <c r="CA7" s="20"/>
-    </row>
-    <row r="8" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="8"/>
-      <c r="AG8" s="16"/>
-      <c r="AH8" s="13"/>
-      <c r="AI8" s="12"/>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="13"/>
-      <c r="AL8" s="13"/>
-      <c r="AM8" s="13"/>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="8"/>
-      <c r="AP8" s="11"/>
-      <c r="AQ8" s="13"/>
-      <c r="AR8" s="11"/>
-      <c r="AS8" s="17"/>
-      <c r="AT8" s="18"/>
-      <c r="AU8" s="13"/>
-      <c r="AV8" s="13"/>
-      <c r="AW8" s="11"/>
-      <c r="AX8" s="17"/>
-      <c r="AY8" s="19"/>
-      <c r="AZ8" s="13"/>
-      <c r="BA8" s="13"/>
-      <c r="BB8" s="8"/>
-      <c r="BC8" s="13"/>
-      <c r="BD8" s="17"/>
-      <c r="BE8" s="17"/>
-      <c r="BF8" s="17"/>
-      <c r="BG8" s="11"/>
-      <c r="BH8" s="11"/>
-      <c r="BI8" s="8"/>
-      <c r="BJ8" s="17"/>
-      <c r="BK8" s="14"/>
-      <c r="BL8" s="14"/>
-      <c r="BM8" s="14"/>
-      <c r="BN8" s="14"/>
-      <c r="BO8" s="14"/>
-      <c r="BP8" s="14"/>
-      <c r="BQ8" s="14"/>
-      <c r="BR8" s="14"/>
-      <c r="BS8" s="14"/>
-      <c r="BT8" s="14"/>
-      <c r="BU8" s="14"/>
-      <c r="BV8" s="20"/>
-      <c r="BW8" s="20"/>
-      <c r="BX8" s="20"/>
-      <c r="BY8" s="20"/>
-      <c r="BZ8" s="20"/>
-      <c r="CA8" s="20"/>
-    </row>
-    <row r="9" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="12"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="8"/>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="13"/>
-      <c r="AI9" s="12"/>
-      <c r="AJ9" s="12"/>
-      <c r="AK9" s="13"/>
-      <c r="AL9" s="13"/>
-      <c r="AM9" s="13"/>
-      <c r="AN9" s="12"/>
-      <c r="AO9" s="8"/>
-      <c r="AP9" s="11"/>
-      <c r="AQ9" s="13"/>
-      <c r="AR9" s="11"/>
-      <c r="AS9" s="17"/>
-      <c r="AT9" s="18"/>
-      <c r="AU9" s="13"/>
-      <c r="AV9" s="13"/>
-      <c r="AW9" s="11"/>
-      <c r="AX9" s="17"/>
-      <c r="AY9" s="19"/>
-      <c r="AZ9" s="13"/>
-      <c r="BA9" s="13"/>
-      <c r="BB9" s="8"/>
-      <c r="BC9" s="13"/>
-      <c r="BD9" s="17"/>
-      <c r="BE9" s="17"/>
-      <c r="BF9" s="17"/>
-      <c r="BG9" s="11"/>
-      <c r="BH9" s="11"/>
-      <c r="BI9" s="8"/>
-      <c r="BJ9" s="17"/>
-      <c r="BK9" s="14"/>
-      <c r="BL9" s="14"/>
-      <c r="BM9" s="14"/>
-      <c r="BN9" s="14"/>
-      <c r="BO9" s="14"/>
-      <c r="BP9" s="14"/>
-      <c r="BQ9" s="14"/>
-      <c r="BR9" s="14"/>
-      <c r="BS9" s="14"/>
-      <c r="BT9" s="14"/>
-      <c r="BU9" s="14"/>
-      <c r="BV9" s="20"/>
-      <c r="BW9" s="20"/>
-      <c r="BX9" s="20"/>
-      <c r="BY9" s="20"/>
-      <c r="BZ9" s="20"/>
-      <c r="CA9" s="20"/>
-    </row>
-    <row r="10" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="8"/>
-      <c r="AG10" s="16"/>
-      <c r="AH10" s="13"/>
-      <c r="AI10" s="12"/>
-      <c r="AJ10" s="12"/>
-      <c r="AK10" s="13"/>
-      <c r="AL10" s="13"/>
-      <c r="AM10" s="13"/>
-      <c r="AN10" s="12"/>
-      <c r="AO10" s="8"/>
-      <c r="AP10" s="11"/>
-      <c r="AQ10" s="13"/>
-      <c r="AR10" s="11"/>
-      <c r="AS10" s="17"/>
-      <c r="AT10" s="18"/>
-      <c r="AU10" s="13"/>
-      <c r="AV10" s="13"/>
-      <c r="AW10" s="11"/>
-      <c r="AX10" s="17"/>
-      <c r="AY10" s="19"/>
-      <c r="AZ10" s="13"/>
-      <c r="BA10" s="13"/>
-      <c r="BB10" s="8"/>
-      <c r="BC10" s="13"/>
-      <c r="BD10" s="17"/>
-      <c r="BE10" s="17"/>
-      <c r="BF10" s="17"/>
-      <c r="BG10" s="11"/>
-      <c r="BH10" s="11"/>
-      <c r="BI10" s="8"/>
-      <c r="BJ10" s="17"/>
-      <c r="BK10" s="14"/>
-      <c r="BL10" s="14"/>
-      <c r="BM10" s="14"/>
-      <c r="BN10" s="14"/>
-      <c r="BO10" s="14"/>
-      <c r="BP10" s="14"/>
-      <c r="BQ10" s="14"/>
-      <c r="BR10" s="14"/>
-      <c r="BS10" s="14"/>
-      <c r="BT10" s="14"/>
-      <c r="BU10" s="14"/>
-      <c r="BV10" s="20"/>
-      <c r="BW10" s="20"/>
-      <c r="BX10" s="20"/>
-      <c r="BY10" s="20"/>
-      <c r="BZ10" s="20"/>
-      <c r="CA10" s="20"/>
-    </row>
-    <row r="11" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="8"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="13"/>
-      <c r="AI11" s="12"/>
-      <c r="AJ11" s="12"/>
-      <c r="AK11" s="13"/>
-      <c r="AL11" s="13"/>
-      <c r="AM11" s="13"/>
-      <c r="AN11" s="12"/>
-      <c r="AO11" s="8"/>
-      <c r="AP11" s="11"/>
-      <c r="AQ11" s="13"/>
-      <c r="AR11" s="11"/>
-      <c r="AS11" s="17"/>
-      <c r="AT11" s="18"/>
-      <c r="AU11" s="13"/>
-      <c r="AV11" s="13"/>
-      <c r="AW11" s="11"/>
-      <c r="AX11" s="17"/>
-      <c r="AY11" s="19"/>
-      <c r="AZ11" s="13"/>
-      <c r="BA11" s="13"/>
-      <c r="BB11" s="8"/>
-      <c r="BC11" s="13"/>
-      <c r="BD11" s="17"/>
-      <c r="BE11" s="17"/>
-      <c r="BF11" s="17"/>
-      <c r="BG11" s="11"/>
-      <c r="BH11" s="11"/>
-      <c r="BI11" s="8"/>
-      <c r="BJ11" s="17"/>
-      <c r="BK11" s="14"/>
-      <c r="BL11" s="14"/>
-      <c r="BM11" s="14"/>
-      <c r="BN11" s="14"/>
-      <c r="BO11" s="14"/>
-      <c r="BP11" s="14"/>
-      <c r="BQ11" s="14"/>
-      <c r="BR11" s="14"/>
-      <c r="BS11" s="14"/>
-      <c r="BT11" s="14"/>
-      <c r="BU11" s="14"/>
-      <c r="BV11" s="20"/>
-      <c r="BW11" s="20"/>
-      <c r="BX11" s="20"/>
-      <c r="BY11" s="20"/>
-      <c r="BZ11" s="20"/>
-      <c r="CA11" s="20"/>
-    </row>
-    <row r="12" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="13"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="12"/>
-      <c r="AJ12" s="12"/>
-      <c r="AK12" s="13"/>
-      <c r="AL12" s="13"/>
-      <c r="AM12" s="13"/>
-      <c r="AN12" s="12"/>
-      <c r="AO12" s="8"/>
-      <c r="AP12" s="11"/>
-      <c r="AQ12" s="13"/>
-      <c r="AR12" s="11"/>
-      <c r="AS12" s="17"/>
-      <c r="AT12" s="18"/>
-      <c r="AU12" s="13"/>
-      <c r="AV12" s="13"/>
-      <c r="AW12" s="11"/>
-      <c r="AX12" s="17"/>
-      <c r="AY12" s="19"/>
-      <c r="AZ12" s="13"/>
-      <c r="BA12" s="13"/>
-      <c r="BB12" s="8"/>
-      <c r="BC12" s="13"/>
-      <c r="BD12" s="17"/>
-      <c r="BE12" s="17"/>
-      <c r="BF12" s="17"/>
-      <c r="BG12" s="11"/>
-      <c r="BH12" s="11"/>
-      <c r="BI12" s="8"/>
-      <c r="BJ12" s="17"/>
-      <c r="BK12" s="14"/>
-      <c r="BL12" s="14"/>
-      <c r="BM12" s="14"/>
-      <c r="BN12" s="14"/>
-      <c r="BO12" s="14"/>
-      <c r="BP12" s="14"/>
-      <c r="BQ12" s="14"/>
-      <c r="BR12" s="14"/>
-      <c r="BS12" s="14"/>
-      <c r="BT12" s="14"/>
-      <c r="BU12" s="14"/>
-      <c r="BV12" s="20"/>
-      <c r="BW12" s="20"/>
-      <c r="BX12" s="20"/>
-      <c r="BY12" s="20"/>
-      <c r="BZ12" s="20"/>
-      <c r="CA12" s="20"/>
-    </row>
-    <row r="13" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="12"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="8"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="13"/>
-      <c r="AI13" s="12"/>
-      <c r="AJ13" s="12"/>
-      <c r="AK13" s="13"/>
-      <c r="AL13" s="13"/>
-      <c r="AM13" s="13"/>
-      <c r="AN13" s="12"/>
-      <c r="AO13" s="8"/>
-      <c r="AP13" s="11"/>
-      <c r="AQ13" s="13"/>
-      <c r="AR13" s="11"/>
-      <c r="AS13" s="17"/>
-      <c r="AT13" s="18"/>
-      <c r="AU13" s="13"/>
-      <c r="AV13" s="13"/>
-      <c r="AW13" s="11"/>
-      <c r="AX13" s="17"/>
-      <c r="AY13" s="19"/>
-      <c r="AZ13" s="13"/>
-      <c r="BA13" s="13"/>
-      <c r="BB13" s="8"/>
-      <c r="BC13" s="13"/>
-      <c r="BD13" s="17"/>
-      <c r="BE13" s="17"/>
-      <c r="BF13" s="17"/>
-      <c r="BG13" s="11"/>
-      <c r="BH13" s="11"/>
-      <c r="BI13" s="8"/>
-      <c r="BJ13" s="17"/>
-      <c r="BK13" s="14"/>
-      <c r="BL13" s="14"/>
-      <c r="BM13" s="14"/>
-      <c r="BN13" s="14"/>
-      <c r="BO13" s="14"/>
-      <c r="BP13" s="14"/>
-      <c r="BQ13" s="14"/>
-      <c r="BR13" s="14"/>
-      <c r="BS13" s="14"/>
-      <c r="BT13" s="14"/>
-      <c r="BU13" s="14"/>
-      <c r="BV13" s="20"/>
-      <c r="BW13" s="20"/>
-      <c r="BX13" s="20"/>
-      <c r="BY13" s="20"/>
-      <c r="BZ13" s="20"/>
-      <c r="CA13" s="20"/>
-    </row>
-    <row r="14" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="8"/>
-      <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="16"/>
-      <c r="AH14" s="13"/>
-      <c r="AI14" s="12"/>
-      <c r="AJ14" s="12"/>
-      <c r="AK14" s="13"/>
-      <c r="AL14" s="13"/>
-      <c r="AM14" s="13"/>
-      <c r="AN14" s="12"/>
-      <c r="AO14" s="8"/>
-      <c r="AP14" s="11"/>
-      <c r="AQ14" s="13"/>
-      <c r="AR14" s="11"/>
-      <c r="AS14" s="17"/>
-      <c r="AT14" s="18"/>
-      <c r="AU14" s="13"/>
-      <c r="AV14" s="13"/>
-      <c r="AW14" s="11"/>
-      <c r="AX14" s="17"/>
-      <c r="AY14" s="19"/>
-      <c r="AZ14" s="13"/>
-      <c r="BA14" s="13"/>
-      <c r="BB14" s="8"/>
-      <c r="BC14" s="13"/>
-      <c r="BD14" s="17"/>
-      <c r="BE14" s="17"/>
-      <c r="BF14" s="17"/>
-      <c r="BG14" s="11"/>
-      <c r="BH14" s="11"/>
-      <c r="BI14" s="8"/>
-      <c r="BJ14" s="17"/>
-      <c r="BK14" s="14"/>
-      <c r="BL14" s="14"/>
-      <c r="BM14" s="14"/>
-      <c r="BN14" s="14"/>
-      <c r="BO14" s="14"/>
-      <c r="BP14" s="14"/>
-      <c r="BQ14" s="14"/>
-      <c r="BR14" s="14"/>
-      <c r="BS14" s="14"/>
-      <c r="BT14" s="14"/>
-      <c r="BU14" s="14"/>
-      <c r="BV14" s="20"/>
-      <c r="BW14" s="20"/>
-      <c r="BX14" s="20"/>
-      <c r="BY14" s="20"/>
-      <c r="BZ14" s="20"/>
-      <c r="CA14" s="20"/>
-    </row>
-    <row r="15" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="12"/>
-      <c r="Z15" s="12"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="8"/>
-      <c r="AG15" s="16"/>
-      <c r="AH15" s="13"/>
-      <c r="AI15" s="12"/>
-      <c r="AJ15" s="12"/>
-      <c r="AK15" s="13"/>
-      <c r="AL15" s="13"/>
-      <c r="AM15" s="13"/>
-      <c r="AN15" s="12"/>
-      <c r="AO15" s="8"/>
-      <c r="AP15" s="11"/>
-      <c r="AQ15" s="13"/>
-      <c r="AR15" s="11"/>
-      <c r="AS15" s="17"/>
-      <c r="AT15" s="18"/>
-      <c r="AU15" s="13"/>
-      <c r="AV15" s="13"/>
-      <c r="AW15" s="11"/>
-      <c r="AX15" s="17"/>
-      <c r="AY15" s="19"/>
-      <c r="AZ15" s="13"/>
-      <c r="BA15" s="13"/>
-      <c r="BB15" s="8"/>
-      <c r="BC15" s="13"/>
-      <c r="BD15" s="17"/>
-      <c r="BE15" s="17"/>
-      <c r="BF15" s="17"/>
-      <c r="BG15" s="11"/>
-      <c r="BH15" s="11"/>
-      <c r="BI15" s="8"/>
-      <c r="BJ15" s="17"/>
-      <c r="BK15" s="14"/>
-      <c r="BL15" s="14"/>
-      <c r="BM15" s="14"/>
-      <c r="BN15" s="14"/>
-      <c r="BO15" s="14"/>
-      <c r="BP15" s="14"/>
-      <c r="BQ15" s="14"/>
-      <c r="BR15" s="14"/>
-      <c r="BS15" s="14"/>
-      <c r="BT15" s="14"/>
-      <c r="BU15" s="14"/>
-      <c r="BV15" s="20"/>
-      <c r="BW15" s="20"/>
-      <c r="BX15" s="20"/>
-      <c r="BY15" s="20"/>
-      <c r="BZ15" s="20"/>
-      <c r="CA15" s="20"/>
-    </row>
-    <row r="16" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="13"/>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="12"/>
-      <c r="AA16" s="8"/>
-      <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="11"/>
-      <c r="AF16" s="8"/>
-      <c r="AG16" s="16"/>
-      <c r="AH16" s="13"/>
-      <c r="AI16" s="12"/>
-      <c r="AJ16" s="12"/>
-      <c r="AK16" s="13"/>
-      <c r="AL16" s="13"/>
-      <c r="AM16" s="13"/>
-      <c r="AN16" s="12"/>
-      <c r="AO16" s="8"/>
-      <c r="AP16" s="11"/>
-      <c r="AQ16" s="13"/>
-      <c r="AR16" s="11"/>
-      <c r="AS16" s="17"/>
-      <c r="AT16" s="18"/>
-      <c r="AU16" s="13"/>
-      <c r="AV16" s="13"/>
-      <c r="AW16" s="11"/>
-      <c r="AX16" s="17"/>
-      <c r="AY16" s="19"/>
-      <c r="AZ16" s="13"/>
-      <c r="BA16" s="13"/>
-      <c r="BB16" s="8"/>
-      <c r="BC16" s="13"/>
-      <c r="BD16" s="17"/>
-      <c r="BE16" s="17"/>
-      <c r="BF16" s="17"/>
-      <c r="BG16" s="11"/>
-      <c r="BH16" s="11"/>
-      <c r="BI16" s="8"/>
-      <c r="BJ16" s="17"/>
-      <c r="BK16" s="14"/>
-      <c r="BL16" s="14"/>
-      <c r="BM16" s="14"/>
-      <c r="BN16" s="14"/>
-      <c r="BO16" s="14"/>
-      <c r="BP16" s="14"/>
-      <c r="BQ16" s="14"/>
-      <c r="BR16" s="14"/>
-      <c r="BS16" s="14"/>
-      <c r="BT16" s="14"/>
-      <c r="BU16" s="14"/>
-      <c r="BV16" s="20"/>
-      <c r="BW16" s="20"/>
-      <c r="BX16" s="20"/>
-      <c r="BY16" s="20"/>
-      <c r="BZ16" s="20"/>
-      <c r="CA16" s="20"/>
-    </row>
-    <row r="17" spans="46:51" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AT17" s="19"/>
-      <c r="AY17" s="19"/>
+      <c r="AY4" s="18"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16 Y10:Y16 W10:W16 T10:T16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ3">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16 Y2:Y16 W2:W16 T2:T16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3">
+      <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
+      <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16 J10:J16" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>INDIRECT($D2)</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
+      <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16 J2:J16" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>INDIRECT($D2)</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y3">
+      <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -1,15 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{ACEAF16D-87D6-4ADA-8F06-7E3B0E9E9B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -244,7 +259,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699732</t>
+    <t>10700311</t>
   </si>
   <si>
     <t>Passed</t>
@@ -256,10 +271,10 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>Alessandro</t>
-  </si>
-  <si>
-    <t>Mayert</t>
+    <t>Lizeth</t>
+  </si>
+  <si>
+    <t>Harvey</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -397,22 +412,22 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699735</t>
+    <t>10700312</t>
   </si>
   <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>Blake</t>
-  </si>
-  <si>
-    <t>Wunsch</t>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Rippin</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 7050893</t>
+    <t>Auto 82117314</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -448,57 +463,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
-      <family val="2"/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -507,7 +522,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.7999816888943144"/>
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,6 +545,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -547,16 +567,28 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -581,6 +613,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -594,7 +629,7 @@
     <xf numFmtId="14" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
@@ -608,14 +643,11 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -895,10 +927,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CN4"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:CN11"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="109.7265625" style="1" customWidth="1"/>
@@ -945,7 +977,7 @@
     <col min="43" max="43" width="20.08984375" style="1" customWidth="1"/>
     <col min="44" max="44" width="10.6328125" style="1" customWidth="1"/>
     <col min="45" max="45" width="19" style="1" customWidth="1"/>
-    <col min="46" max="46" width="15.81640625" style="1" customWidth="1"/>
+    <col min="46" max="46" width="24.81640625" style="1" customWidth="1"/>
     <col min="47" max="47" width="13.6328125" style="1" customWidth="1"/>
     <col min="48" max="48" width="17.81640625" style="1" customWidth="1"/>
     <col min="49" max="49" width="10.6328125" style="1" customWidth="1"/>
@@ -979,10 +1011,11 @@
     <col min="77" max="77" width="15" style="1" customWidth="1"/>
     <col min="78" max="78" width="33.6328125" style="1" customWidth="1"/>
     <col min="79" max="79" width="26.90625" style="1" customWidth="1"/>
-    <col min="80" max="16384" width="8.90625" style="1" customWidth="1"/>
+    <col min="80" max="80" width="8.90625" style="1" customWidth="1"/>
+    <col min="81" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:92" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1234,84 +1267,85 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>76</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="12">
-        <v>45597</v>
-      </c>
-      <c r="L2" s="10" t="s">
+      <c r="K2" s="13">
+        <f ca="1">TODAY()-40</f>
+        <v>45820</v>
+      </c>
+      <c r="L2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="11">
         <v>1</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="14">
         <v>213111231</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="R2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="S2" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="U2" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="V2" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="W2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="12">
-        <f t="shared" ref="X2:X3" si="0">K2</f>
-        <v>45597</v>
-      </c>
-      <c r="Y2" s="11" t="s">
+      <c r="X2" s="13">
+        <f t="shared" ref="X2:X3" ca="1" si="0">K2</f>
+        <v>45820</v>
+      </c>
+      <c r="Y2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="Z2" s="12" t="s">
         <v>92</v>
       </c>
       <c r="AA2" s="8" t="s">
@@ -1323,239 +1357,242 @@
       <c r="AC2" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AD2" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AE2" s="11" t="s">
         <v>97</v>
       </c>
       <c r="AF2" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AG2" s="15">
+      <c r="AG2" s="16">
         <v>20</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AH2" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="AI2" s="11" t="s">
+      <c r="AI2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AJ2" s="11" t="s">
+      <c r="AJ2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AK2" s="12">
+      <c r="AK2" s="13" t="str">
         <f t="shared" ref="AK2:AK3" si="1">AH2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AL2" s="12">
-        <f t="shared" ref="AL2:AL3" si="2">K2</f>
-        <v>45597</v>
-      </c>
-      <c r="AM2" s="12">
-        <f t="shared" ref="AM2:AM3" si="3">K2</f>
-        <v>45597</v>
-      </c>
-      <c r="AN2" s="11" t="s">
+        <v>N/A</v>
+      </c>
+      <c r="AL2" s="13">
+        <f t="shared" ref="AL2:AL3" ca="1" si="2">K2</f>
+        <v>45820</v>
+      </c>
+      <c r="AM2" s="13">
+        <f t="shared" ref="AM2:AM3" ca="1" si="3">K2</f>
+        <v>45820</v>
+      </c>
+      <c r="AN2" s="12" t="s">
         <v>102</v>
       </c>
       <c r="AO2" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="AP2" s="10">
+      <c r="AP2" s="11">
         <v>100</v>
       </c>
-      <c r="AQ2" s="12">
-        <f t="shared" ref="AQ2:AQ3" si="4">K2+90</f>
-        <v>45687</v>
-      </c>
-      <c r="AR2" s="10" t="s">
+      <c r="AQ2" s="13">
+        <f t="shared" ref="AQ2:AQ3" ca="1" si="4">K2+90</f>
+        <v>45910</v>
+      </c>
+      <c r="AR2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AS2" s="16" t="s">
+      <c r="AS2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="17">
-        <v>9461110909</v>
-      </c>
-      <c r="AU2" s="12" t="s">
+      <c r="AT2" s="1">
+        <f t="array" aca="1" ref="AT2:AT3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>527090294</v>
+      </c>
+      <c r="AU2" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AV2" s="12" t="s">
+      <c r="AV2" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="AW2" s="10" t="s">
+      <c r="AW2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AX2" s="16" t="s">
+      <c r="AX2" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="AY2" s="18">
-        <v>152733408</v>
-      </c>
-      <c r="AZ2" s="12" t="s">
+      <c r="AY2" s="1">
+        <f t="array" aca="1" ref="AY2:AY3" ca="1">_xlfn.RANDARRAY(2,1,1234567891,9999999999,TRUE)</f>
+        <v>3199657070</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BA2" s="12" t="s">
+      <c r="BA2" s="13" t="s">
         <v>106</v>
       </c>
       <c r="BB2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="BC2" s="12">
+      <c r="BC2" s="13">
         <v>34284</v>
       </c>
-      <c r="BD2" s="16" t="s">
+      <c r="BD2" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="BE2" s="16" t="s">
+      <c r="BE2" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="16" t="s">
+      <c r="BF2" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="BG2" s="10" t="s">
+      <c r="BG2" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="10" t="s">
+      <c r="BH2" s="11" t="s">
         <v>112</v>
       </c>
       <c r="BI2" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="BJ2" s="16" t="s">
+      <c r="BJ2" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="BK2" s="13" t="s">
+      <c r="BK2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="BL2" s="13" t="s">
+      <c r="BL2" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="BM2" s="13" t="s">
+      <c r="BM2" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="BN2" s="13" t="s">
+      <c r="BN2" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="BO2" s="13">
+      <c r="BO2" s="14">
         <v>2024</v>
       </c>
-      <c r="BP2" s="13" t="s">
+      <c r="BP2" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="BQ2" s="13">
+      <c r="BQ2" s="14">
         <v>2021</v>
       </c>
-      <c r="BR2" s="13">
+      <c r="BR2" s="14">
         <v>2024</v>
       </c>
-      <c r="BS2" s="13" t="s">
+      <c r="BS2" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="13" t="s">
+      <c r="BT2" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="BU2" s="13" t="s">
+      <c r="BU2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="BV2" s="19" t="s">
+      <c r="BV2" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="BW2" s="19" t="s">
+      <c r="BW2" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="BX2" s="19">
+      <c r="BX2" s="18">
         <v>213</v>
       </c>
-      <c r="BY2" s="19" t="s">
+      <c r="BY2" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="BZ2" s="19" t="s">
+      <c r="BZ2" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="CA2" s="19" t="s">
+      <c r="CA2" s="18" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>127</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K3" s="12">
-        <v>45597</v>
-      </c>
-      <c r="L3" s="10" t="s">
+      <c r="K3" s="13">
+        <f ca="1">TODAY()-40</f>
+        <v>45820</v>
+      </c>
+      <c r="L3" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="11">
         <v>1</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="14">
         <v>213111231</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="S3" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="T3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="U3" s="12" t="s">
+      <c r="U3" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="V3" s="14" t="s">
+      <c r="V3" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="W3" s="11" t="s">
+      <c r="W3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="X3" s="12">
-        <f t="shared" si="0"/>
-        <v>45597</v>
-      </c>
-      <c r="Y3" s="11" t="s">
+      <c r="X3" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>45820</v>
+      </c>
+      <c r="Y3" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="Z3" s="11" t="s">
+      <c r="Z3" s="12" t="s">
         <v>132</v>
       </c>
       <c r="AA3" s="8" t="s">
@@ -1567,187 +1604,191 @@
       <c r="AC3" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="AD3" s="10" t="s">
+      <c r="AD3" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AE3" s="10" t="s">
+      <c r="AE3" s="11" t="s">
         <v>97</v>
       </c>
       <c r="AF3" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="AG3" s="15">
+      <c r="AG3" s="16">
         <v>40</v>
       </c>
-      <c r="AH3" s="12" t="s">
+      <c r="AH3" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="AI3" s="11" t="s">
+      <c r="AI3" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AJ3" s="11" t="s">
+      <c r="AJ3" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AK3" s="12">
+      <c r="AK3" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>NaN</v>
-      </c>
-      <c r="AL3" s="12">
-        <f t="shared" si="2"/>
-        <v>45597</v>
-      </c>
-      <c r="AM3" s="12">
-        <f t="shared" si="3"/>
-        <v>45597</v>
-      </c>
-      <c r="AN3" s="11" t="s">
+        <v>N/A</v>
+      </c>
+      <c r="AL3" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>45820</v>
+      </c>
+      <c r="AM3" s="13">
+        <f t="shared" ca="1" si="3"/>
+        <v>45820</v>
+      </c>
+      <c r="AN3" s="12" t="s">
         <v>136</v>
       </c>
       <c r="AO3" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="AP3" s="10">
+      <c r="AP3" s="11">
         <v>100</v>
       </c>
-      <c r="AQ3" s="12">
-        <f t="shared" si="4"/>
-        <v>45687</v>
-      </c>
-      <c r="AR3" s="10" t="s">
+      <c r="AQ3" s="13">
+        <f t="shared" ca="1" si="4"/>
+        <v>45910</v>
+      </c>
+      <c r="AR3" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AS3" s="16" t="s">
+      <c r="AS3" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="AT3" s="17">
-        <v>9461110910</v>
-      </c>
-      <c r="AU3" s="12" t="s">
+      <c r="AT3" s="1">
+        <f ca="1"/>
+        <v>237778441</v>
+      </c>
+      <c r="AU3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AV3" s="12" t="s">
+      <c r="AV3" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="AW3" s="10" t="s">
+      <c r="AW3" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AX3" s="16" t="s">
+      <c r="AX3" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="AY3" s="18">
-        <v>152733409</v>
-      </c>
-      <c r="AZ3" s="12" t="s">
+      <c r="AY3" s="1">
+        <f ca="1"/>
+        <v>4764345306</v>
+      </c>
+      <c r="AZ3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BA3" s="12" t="s">
+      <c r="BA3" s="13" t="s">
         <v>106</v>
       </c>
       <c r="BB3" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="BC3" s="12">
+      <c r="BC3" s="13">
         <v>34284</v>
       </c>
-      <c r="BD3" s="16" t="s">
+      <c r="BD3" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="BE3" s="16" t="s">
+      <c r="BE3" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="BF3" s="16" t="s">
+      <c r="BF3" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="BG3" s="10" t="s">
+      <c r="BG3" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="BH3" s="10" t="s">
+      <c r="BH3" s="11" t="s">
         <v>112</v>
       </c>
       <c r="BI3" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="BJ3" s="16" t="s">
+      <c r="BJ3" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="BK3" s="13" t="s">
+      <c r="BK3" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="BL3" s="13" t="s">
+      <c r="BL3" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="BM3" s="13" t="s">
+      <c r="BM3" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="BN3" s="13" t="s">
+      <c r="BN3" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="BO3" s="13">
+      <c r="BO3" s="14">
         <v>2000</v>
       </c>
-      <c r="BP3" s="13" t="s">
+      <c r="BP3" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="BQ3" s="13">
+      <c r="BQ3" s="14">
         <v>1995</v>
       </c>
-      <c r="BR3" s="13">
+      <c r="BR3" s="14">
         <v>2000</v>
       </c>
-      <c r="BS3" s="13" t="s">
+      <c r="BS3" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="BT3" s="13" t="s">
+      <c r="BT3" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="BU3" s="13" t="s">
+      <c r="BU3" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="BV3" s="19" t="s">
+      <c r="BV3" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="BW3" s="19" t="s">
+      <c r="BW3" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="BX3" s="19">
+      <c r="BX3" s="18">
         <v>201</v>
       </c>
-      <c r="BY3" s="19" t="s">
+      <c r="BY3" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="BZ3" s="19" t="s">
+      <c r="BZ3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="CA3" s="19" t="s">
+      <c r="CA3" s="18" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" ht="15.65" customHeight="1" spans="46:51" x14ac:dyDescent="0.25">
-      <c r="AT4" s="18"/>
-      <c r="AY4" s="18"/>
+    <row r="6" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AT6" s="19"/>
+    </row>
+    <row r="7" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AT7" s="19"/>
+    </row>
+    <row r="8" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AT8" s="19"/>
+    </row>
+    <row r="9" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AT9" s="19"/>
+    </row>
+    <row r="10" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AT10" s="19"/>
+    </row>
+    <row r="11" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AT11" s="19"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ3">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ3 Y2:Y3 W2:W3 T2:T3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3 J2:J3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
-      <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y3">
-      <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{ACEAF16D-87D6-4ADA-8F06-7E3B0E9E9B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{9B464D86-AC80-43A7-A633-ABDD9962DD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="140">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -259,22 +259,16 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10700311</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>895 Retail Team 1 (Sepap Pusube (10573442) (Inherited))</t>
   </si>
   <si>
     <t>Czechia</t>
   </si>
   <si>
-    <t>Lizeth</t>
-  </si>
-  <si>
-    <t>Harvey</t>
+    <t>Hector</t>
+  </si>
+  <si>
+    <t>Sipes</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -412,22 +406,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10700312</t>
-  </si>
-  <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>Jan</t>
-  </si>
-  <si>
-    <t>Rippin</t>
+    <t>Libbie</t>
+  </si>
+  <si>
+    <t>Zulauf</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 82117314</t>
+    <t>Auto 79220054</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -1267,46 +1258,42 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="H2" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="J2" s="12" t="s">
         <v>82</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="K2" s="13">
         <f ca="1">TODAY()-40</f>
-        <v>45820</v>
+        <v>45823</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N2" s="11">
         <v>1</v>
@@ -1315,68 +1302,68 @@
         <v>213111231</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="S2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="T2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="S2" s="12" t="s">
+      <c r="V2" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="T2" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="W2" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="X2" s="13">
         <f t="shared" ref="X2:X3" ca="1" si="0">K2</f>
-        <v>45820</v>
+        <v>45823</v>
       </c>
       <c r="Y2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA2" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="AB2" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AC2" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AD2" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AE2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AF2" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>98</v>
       </c>
       <c r="AG2" s="16">
         <v>20</v>
       </c>
       <c r="AH2" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI2" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="AI2" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ2" s="12" t="s">
-        <v>101</v>
       </c>
       <c r="AK2" s="13" t="str">
         <f t="shared" ref="AK2:AK3" si="1">AH2</f>
@@ -1384,101 +1371,101 @@
       </c>
       <c r="AL2" s="13">
         <f t="shared" ref="AL2:AL3" ca="1" si="2">K2</f>
-        <v>45820</v>
+        <v>45823</v>
       </c>
       <c r="AM2" s="13">
         <f t="shared" ref="AM2:AM3" ca="1" si="3">K2</f>
-        <v>45820</v>
+        <v>45823</v>
       </c>
       <c r="AN2" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AO2" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AP2" s="11">
         <v>100</v>
       </c>
       <c r="AQ2" s="13">
         <f t="shared" ref="AQ2:AQ3" ca="1" si="4">K2+90</f>
-        <v>45910</v>
+        <v>45913</v>
       </c>
       <c r="AR2" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AS2" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AT2" s="1">
         <f t="array" aca="1" ref="AT2:AT3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>527090294</v>
+        <v>170894114</v>
       </c>
       <c r="AU2" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AW2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX2" s="17" t="s">
         <v>105</v>
-      </c>
-      <c r="AV2" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="AW2" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX2" s="17" t="s">
-        <v>107</v>
       </c>
       <c r="AY2" s="1">
         <f t="array" aca="1" ref="AY2:AY3" ca="1">_xlfn.RANDARRAY(2,1,1234567891,9999999999,TRUE)</f>
-        <v>3199657070</v>
+        <v>8661797469</v>
       </c>
       <c r="AZ2" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BA2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB2" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="BB2" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="BC2" s="13">
         <v>34284</v>
       </c>
       <c r="BD2" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="BE2" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF2" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG2" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="17" t="s">
+      <c r="BH2" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="BG2" s="11" t="s">
+      <c r="BI2" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="11" t="s">
+      <c r="BJ2" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="BI2" s="8" t="s">
+      <c r="BK2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="BL2" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="BJ2" s="17" t="s">
+      <c r="BM2" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="BK2" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BL2" s="14" t="s">
+      <c r="BN2" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="BM2" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="BN2" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="BO2" s="14">
         <v>2024</v>
       </c>
       <c r="BP2" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BQ2" s="14">
         <v>2021</v>
@@ -1487,73 +1474,69 @@
         <v>2024</v>
       </c>
       <c r="BS2" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="BT2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="BV2" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="14" t="s">
+      <c r="BW2" s="18" t="s">
         <v>120</v>
-      </c>
-      <c r="BU2" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BV2" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW2" s="18" t="s">
-        <v>122</v>
       </c>
       <c r="BX2" s="18">
         <v>213</v>
       </c>
       <c r="BY2" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BZ2" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="CA2" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="BZ2" s="18" t="s">
+    </row>
+    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="CA2" s="18" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="10" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="E3" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="G3" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="H3" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>131</v>
-      </c>
       <c r="I3" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K3" s="13">
         <f ca="1">TODAY()-40</f>
-        <v>45820</v>
+        <v>45823</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N3" s="11">
         <v>1</v>
@@ -1562,68 +1545,68 @@
         <v>213111231</v>
       </c>
       <c r="P3" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="S3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="T3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="U3" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="R3" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="S3" s="12" t="s">
+      <c r="V3" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="T3" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="U3" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="W3" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="X3" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>45820</v>
+        <v>45823</v>
       </c>
       <c r="Y3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z3" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA3" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="Z3" s="12" t="s">
+      <c r="AB3" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD3" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF3" s="8" t="s">
         <v>132</v>
-      </c>
-      <c r="AA3" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE3" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF3" s="8" t="s">
-        <v>135</v>
       </c>
       <c r="AG3" s="16">
         <v>40</v>
       </c>
       <c r="AH3" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI3" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ3" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="AI3" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ3" s="12" t="s">
-        <v>101</v>
       </c>
       <c r="AK3" s="13" t="str">
         <f t="shared" si="1"/>
@@ -1631,101 +1614,101 @@
       </c>
       <c r="AL3" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>45820</v>
+        <v>45823</v>
       </c>
       <c r="AM3" s="13">
         <f t="shared" ca="1" si="3"/>
-        <v>45820</v>
+        <v>45823</v>
       </c>
       <c r="AN3" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AO3" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AP3" s="11">
         <v>100</v>
       </c>
       <c r="AQ3" s="13">
         <f t="shared" ca="1" si="4"/>
-        <v>45910</v>
+        <v>45913</v>
       </c>
       <c r="AR3" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AS3" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AT3" s="1">
         <f ca="1"/>
-        <v>237778441</v>
+        <v>489566039</v>
       </c>
       <c r="AU3" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV3" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AW3" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX3" s="17" t="s">
         <v>105</v>
-      </c>
-      <c r="AV3" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="AW3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX3" s="17" t="s">
-        <v>107</v>
       </c>
       <c r="AY3" s="1">
         <f ca="1"/>
-        <v>4764345306</v>
+        <v>6311834980</v>
       </c>
       <c r="AZ3" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BA3" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB3" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="BB3" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="BC3" s="13">
         <v>34284</v>
       </c>
       <c r="BD3" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="BE3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG3" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="BF3" s="17" t="s">
+      <c r="BH3" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="BG3" s="11" t="s">
+      <c r="BI3" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="BH3" s="11" t="s">
+      <c r="BJ3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="BI3" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="BJ3" s="17" t="s">
-        <v>114</v>
-      </c>
       <c r="BK3" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BL3" s="14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BM3" s="14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BN3" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="BO3" s="14">
         <v>2000</v>
       </c>
       <c r="BP3" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BQ3" s="14">
         <v>1995</v>
@@ -1734,31 +1717,31 @@
         <v>2000</v>
       </c>
       <c r="BS3" s="14" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="BT3" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="BU3" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BV3" s="18" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="BW3" s="18" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="BX3" s="18">
         <v>201</v>
       </c>
       <c r="BY3" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BZ3" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="CA3" s="18" t="s">
         <v>123</v>
-      </c>
-      <c r="BZ3" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA3" s="18" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">

--- a/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -1,35 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{9B464D86-AC80-43A7-A633-ABDD9962DD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="144">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -259,16 +244,22 @@
     <t>Test1</t>
   </si>
   <si>
+    <t>10700383</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>895 Retail Team 1 (Sepap Pusube (10573442) (Inherited))</t>
   </si>
   <si>
     <t>Czechia</t>
   </si>
   <si>
-    <t>Hector</t>
-  </si>
-  <si>
-    <t>Sipes</t>
+    <t>Maybell</t>
+  </si>
+  <si>
+    <t>Glover</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -406,19 +397,32 @@
     <t>Test2</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Camille Green' Employee:{10700385}Error: locator.click: Element is not visible
+Call log:
+  [2m- waiting for getByLabel('All Items').first()[22m
+[2m  -   locator resolved to &lt;button class="css-2qog38" aria-current="true" aria-labe…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>Libbie</t>
-  </si>
-  <si>
-    <t>Zulauf</t>
+    <t>Camille</t>
+  </si>
+  <si>
+    <t>Green</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 79220054</t>
+    <t>Auto 38684102</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -454,57 +458,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <u/>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,7 +517,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -527,11 +531,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -558,28 +557,16 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -604,7 +591,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -620,7 +607,7 @@
     <xf numFmtId="14" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
@@ -918,10 +905,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CN11"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="109.7265625" style="1" customWidth="1"/>
@@ -1002,11 +989,10 @@
     <col min="77" max="77" width="15" style="1" customWidth="1"/>
     <col min="78" max="78" width="33.6328125" style="1" customWidth="1"/>
     <col min="79" max="79" width="26.90625" style="1" customWidth="1"/>
-    <col min="80" max="80" width="8.90625" style="1" customWidth="1"/>
-    <col min="81" max="16384" width="8.90625" style="1"/>
+    <col min="80" max="16384" width="8.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:92" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1258,42 +1244,46 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="8"/>
+      <c r="B2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D2" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G2" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" s="13">
+        <f>TODAY()-40</f>
+        <v>45826</v>
+      </c>
+      <c r="L2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" s="13">
-        <f ca="1">TODAY()-40</f>
-        <v>45823</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>77</v>
-      </c>
       <c r="M2" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N2" s="11">
         <v>1</v>
@@ -1302,170 +1292,170 @@
         <v>213111231</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="T2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="Q2" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" s="12" t="s">
+      <c r="U2" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="W2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="S2" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>82</v>
-      </c>
       <c r="X2" s="13">
-        <f t="shared" ref="X2:X3" ca="1" si="0">K2</f>
-        <v>45823</v>
+        <f t="shared" ref="X2:X3" si="0">K2</f>
+        <v>45826</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AA2" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AF2" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AG2" s="16">
         <v>20</v>
       </c>
       <c r="AH2" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AI2" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AJ2" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK2" s="13" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK2" s="13">
         <f t="shared" ref="AK2:AK3" si="1">AH2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL2" s="13">
-        <f t="shared" ref="AL2:AL3" ca="1" si="2">K2</f>
-        <v>45823</v>
+        <f t="shared" ref="AL2:AL3" si="2">K2</f>
+        <v>45826</v>
       </c>
       <c r="AM2" s="13">
-        <f t="shared" ref="AM2:AM3" ca="1" si="3">K2</f>
-        <v>45823</v>
+        <f t="shared" ref="AM2:AM3" si="3">K2</f>
+        <v>45826</v>
       </c>
       <c r="AN2" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AO2" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AP2" s="11">
         <v>100</v>
       </c>
       <c r="AQ2" s="13">
-        <f t="shared" ref="AQ2:AQ3" ca="1" si="4">K2+90</f>
-        <v>45913</v>
+        <f t="shared" ref="AQ2:AQ3" si="4">K2+90</f>
+        <v>45916</v>
       </c>
       <c r="AR2" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AS2" s="17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AT2" s="1">
-        <f t="array" aca="1" ref="AT2:AT3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>170894114</v>
+        <f t="array" ref="AT2:AT3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>141339042</v>
       </c>
       <c r="AU2" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AV2" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AW2" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX2" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY2" s="1">
+        <f t="array" ref="AY2:AY3">_xlfn.RANDARRAY(2,1,1234567891,9999999999,TRUE)</f>
+        <v>5809444761</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AY2" s="1">
-        <f t="array" aca="1" ref="AY2:AY3" ca="1">_xlfn.RANDARRAY(2,1,1234567891,9999999999,TRUE)</f>
-        <v>8661797469</v>
-      </c>
-      <c r="AZ2" s="13" t="s">
-        <v>103</v>
-      </c>
       <c r="BA2" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BB2" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BC2" s="13">
         <v>34284</v>
       </c>
       <c r="BD2" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="BE2" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BF2" s="17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BG2" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BH2" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BI2" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BJ2" s="17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BK2" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BL2" s="14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BM2" s="14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BN2" s="14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BO2" s="14">
         <v>2024</v>
       </c>
       <c r="BP2" s="14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BQ2" s="14">
         <v>2021</v>
@@ -1474,69 +1464,73 @@
         <v>2024</v>
       </c>
       <c r="BS2" s="14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BT2" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BU2" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BV2" s="18" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BW2" s="18" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BX2" s="18">
         <v>213</v>
       </c>
       <c r="BY2" s="18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BZ2" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="CA2" s="18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="8"/>
+        <v>126</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="D3" s="10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K3" s="13">
-        <f ca="1">TODAY()-40</f>
-        <v>45823</v>
+        <f>TODAY()-40</f>
+        <v>45826</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N3" s="11">
         <v>1</v>
@@ -1545,170 +1539,168 @@
         <v>213111231</v>
       </c>
       <c r="P3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="T3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="Q3" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="R3" s="12" t="s">
+      <c r="U3" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="V3" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="W3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="S3" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="T3" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="U3" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="W3" s="12" t="s">
-        <v>82</v>
-      </c>
       <c r="X3" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>45823</v>
+        <f t="shared" si="0"/>
+        <v>45826</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Z3" s="12" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AG3" s="16">
         <v>40</v>
       </c>
       <c r="AH3" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AI3" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AJ3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK3" s="13" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK3" s="13">
         <f t="shared" si="1"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL3" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>45823</v>
+        <f t="shared" si="2"/>
+        <v>45826</v>
       </c>
       <c r="AM3" s="13">
-        <f t="shared" ca="1" si="3"/>
-        <v>45823</v>
+        <f t="shared" si="3"/>
+        <v>45826</v>
       </c>
       <c r="AN3" s="12" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AO3" s="8" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="AP3" s="11">
         <v>100</v>
       </c>
       <c r="AQ3" s="13">
-        <f t="shared" ca="1" si="4"/>
-        <v>45913</v>
+        <f t="shared" si="4"/>
+        <v>45916</v>
       </c>
       <c r="AR3" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AS3" s="17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AT3" s="1">
-        <f ca="1"/>
-        <v>489566039</v>
+        <v>621499496</v>
       </c>
       <c r="AU3" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AV3" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AW3" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AX3" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>7105135880</v>
+      </c>
+      <c r="AZ3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AY3" s="1">
-        <f ca="1"/>
-        <v>6311834980</v>
-      </c>
-      <c r="AZ3" s="13" t="s">
-        <v>103</v>
-      </c>
       <c r="BA3" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BB3" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BC3" s="13">
         <v>34284</v>
       </c>
       <c r="BD3" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="BE3" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BF3" s="17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BG3" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BH3" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BI3" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BJ3" s="17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BK3" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BL3" s="14" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="BM3" s="14" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BN3" s="14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BO3" s="14">
         <v>2000</v>
       </c>
       <c r="BP3" s="14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BQ3" s="14">
         <v>1995</v>
@@ -1717,61 +1709,73 @@
         <v>2000</v>
       </c>
       <c r="BS3" s="14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="BT3" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BU3" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BV3" s="18" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="BW3" s="18" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="BX3" s="18">
         <v>201</v>
       </c>
       <c r="BY3" s="18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BZ3" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="CA3" s="18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.65" customHeight="1" spans="46:46" x14ac:dyDescent="0.25">
       <c r="AT6" s="19"/>
     </row>
-    <row r="7" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.65" customHeight="1" spans="46:46" x14ac:dyDescent="0.25">
       <c r="AT7" s="19"/>
     </row>
-    <row r="8" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.65" customHeight="1" spans="46:46" x14ac:dyDescent="0.25">
       <c r="AT8" s="19"/>
     </row>
-    <row r="9" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.65" customHeight="1" spans="46:46" x14ac:dyDescent="0.25">
       <c r="AT9" s="19"/>
     </row>
-    <row r="10" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.65" customHeight="1" spans="46:46" x14ac:dyDescent="0.25">
       <c r="AT10" s="19"/>
     </row>
-    <row r="11" spans="1:92" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.65" customHeight="1" spans="46:46" x14ac:dyDescent="0.25">
       <c r="AT11" s="19"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ3 Y2:Y3 W2:W3 T2:T3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ3">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3 J2:J3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3">
       <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
+      <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y3">
+      <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Czechia_Regression_PK17.xlsx
@@ -244,7 +244,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10700239</t>
+    <t>10700447</t>
   </si>
   <si>
     <t>Passed</t>
@@ -256,10 +256,10 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>Audie</t>
-  </si>
-  <si>
-    <t>Quigley</t>
+    <t>Jaycee</t>
+  </si>
+  <si>
+    <t>Kling</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -397,22 +397,22 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10700271</t>
+    <t>10700448</t>
   </si>
   <si>
     <t>895 Store Management (Sepap Pusube (10573442))</t>
   </si>
   <si>
-    <t>Reese</t>
-  </si>
-  <si>
-    <t>Schmidt</t>
+    <t>Genevieve</t>
+  </si>
+  <si>
+    <t>Mertz</t>
   </si>
   <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 81078454</t>
+    <t>Auto 1253949</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -1382,7 +1382,7 @@
         <v>104</v>
       </c>
       <c r="AT2" s="18">
-        <v>9461110922</v>
+        <v>9461110965</v>
       </c>
       <c r="AU2" s="13" t="s">
         <v>105</v>
@@ -1397,7 +1397,7 @@
         <v>107</v>
       </c>
       <c r="AY2" s="19">
-        <v>152733424</v>
+        <v>152733449</v>
       </c>
       <c r="AZ2" s="13" t="s">
         <v>105</v>
@@ -1626,7 +1626,7 @@
         <v>104</v>
       </c>
       <c r="AT3" s="18">
-        <v>9461110924</v>
+        <v>9461110966</v>
       </c>
       <c r="AU3" s="13" t="s">
         <v>105</v>
@@ -1641,7 +1641,7 @@
         <v>107</v>
       </c>
       <c r="AY3" s="19">
-        <v>152733426</v>
+        <v>152733451</v>
       </c>
       <c r="AZ3" s="13" t="s">
         <v>105</v>
